--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6822A65C-14CD-D34E-9BE9-DE20CBCA263F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{781EE849-22B3-0F49-9405-5EAD6A6C3A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="205">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -66,577 +66,589 @@
     <t>DASH</t>
   </si>
   <si>
-    <t>NOKIA</t>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>PUBP</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Manticore Master Fund</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
+  </si>
+  <si>
+    <t>SITIME ORD (NMS)</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>CINTAS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>7751</t>
   </si>
   <si>
     <t>FICO</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Manticore Master Fund</t>
-  </si>
-  <si>
-    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
-  </si>
-  <si>
-    <t>NOKIA ADR REPSG 1 SER A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>Instrument</t>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>LAMR</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>CSU</t>
+  </si>
+  <si>
+    <t>GEV</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>EXLS</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>RHI</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>ALAB</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>BBY</t>
+  </si>
+  <si>
+    <t>GLW</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>TTAN</t>
+  </si>
+  <si>
+    <t>CHYM</t>
+  </si>
+  <si>
+    <t>SOFI</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>SEZL</t>
+  </si>
+  <si>
+    <t>CRWV</t>
+  </si>
+  <si>
+    <t>3034</t>
+  </si>
+  <si>
+    <t>CNXC</t>
+  </si>
+  <si>
+    <t>DAVE</t>
+  </si>
+  <si>
+    <t>TEPRF</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>META</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>TRMB</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>AG1G</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>ZETA</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>PCOR</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>SAPG</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>NOD</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>SPHR</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>6857</t>
+  </si>
+  <si>
+    <t>ACM</t>
+  </si>
+  <si>
+    <t>CART</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>STM</t>
+  </si>
+  <si>
+    <t>000660</t>
+  </si>
+  <si>
+    <t>CHKP</t>
+  </si>
+  <si>
+    <t>RBLX</t>
+  </si>
+  <si>
+    <t>RRX</t>
+  </si>
+  <si>
+    <t>LION</t>
+  </si>
+  <si>
+    <t>CANON ORD (TYO) CFD</t>
   </si>
   <si>
     <t>FAIR ISAAC ORD (NYS)</t>
   </si>
   <si>
-    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>PUBP</t>
-  </si>
-  <si>
-    <t>CTAS</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t>7751</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>LAMR</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>CSU</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>6098</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>PINS</t>
-  </si>
-  <si>
-    <t>GRMN</t>
-  </si>
-  <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>EXLS</t>
-  </si>
-  <si>
-    <t>TTAN</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>BKNG</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>ADP</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>RHI</t>
-  </si>
-  <si>
-    <t>CIEN</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>GEV</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>ALAB</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>FAF</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>SYM</t>
-  </si>
-  <si>
-    <t>NBIS</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>CRWV</t>
-  </si>
-  <si>
-    <t>CHYM</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>3034</t>
-  </si>
-  <si>
-    <t>TEPRF</t>
-  </si>
-  <si>
-    <t>CNXC</t>
-  </si>
-  <si>
-    <t>SITM</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>TRMB</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>INTU</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>RACE</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>005930</t>
-  </si>
-  <si>
-    <t>AG1G</t>
-  </si>
-  <si>
-    <t>6752</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>000660</t>
-  </si>
-  <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>SAPG</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>ZETA</t>
-  </si>
-  <si>
-    <t>PCOR</t>
-  </si>
-  <si>
-    <t>6857</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>SPHR</t>
-  </si>
-  <si>
-    <t>STM</t>
-  </si>
-  <si>
-    <t>CART</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>ACM</t>
-  </si>
-  <si>
-    <t>NXPI</t>
-  </si>
-  <si>
-    <t>RBLX</t>
-  </si>
-  <si>
-    <t>LION</t>
-  </si>
-  <si>
-    <t>META</t>
-  </si>
-  <si>
-    <t>CINTAS ORD (NMS)</t>
-  </si>
-  <si>
     <t>HEALTHEQUITY ORD (NMS)</t>
   </si>
   <si>
+    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>APPLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
+  </si>
+  <si>
     <t>AUTODESK ORD (NMS)</t>
   </si>
   <si>
-    <t>CANON ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>APPLE ORD (NMS)</t>
+    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
+  </si>
+  <si>
+    <t>SERVICENOW ORD (NYS)</t>
+  </si>
+  <si>
+    <t>EQUIFAX ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
+  </si>
+  <si>
+    <t>GE VERNOVA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ARAMARK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SALESFORCE ORD (NYS)</t>
+  </si>
+  <si>
+    <t>WILLIAMS SONOMA ORD (NYS)</t>
   </si>
   <si>
     <t>EXPEDIA GROUP ORD (NMS)</t>
   </si>
   <si>
-    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
-  </si>
-  <si>
-    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
+    <t>VERISK ANALYTICS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GARMIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SANRIO ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>LOGITECH N ORD (NMS)</t>
   </si>
   <si>
     <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
   </si>
   <si>
-    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>ARAMARK ORD (NYS)</t>
+    <t>ATLASSIAN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GARTNER ORD (NYS)</t>
   </si>
   <si>
     <t>PINTEREST CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>GARMIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EQUIFAX ORD (NYS)</t>
-  </si>
-  <si>
-    <t>VERISK ANALYTICS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SANRIO ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>LOGITECH N ORD (NMS)</t>
-  </si>
-  <si>
-    <t>WILLIAMS SONOMA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
+    <t>REA GROUP ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SAMSARA CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ADOBE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>COINBASE GLOBAL CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ARISTA NETWORKS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>EBAY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROBERT HALF ORD (NYS)</t>
+  </si>
+  <si>
+    <t>DUOLINGO CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CARGURUS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ASTERA LABS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SYMBOTIC CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>BEST BUY ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CORNING ORD (NYS)</t>
+  </si>
+  <si>
+    <t>META US 01/15/27 C720 OTC (META 1/15/27 C720 OTC)</t>
+  </si>
+  <si>
+    <t>CIENA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>QUALYS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
   </si>
   <si>
     <t>SERVICETITAN CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>SERVICENOW ORD (NYS)</t>
-  </si>
-  <si>
-    <t>REA GROUP ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>BOOKING HOLDINGS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GARTNER ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SAMSARA CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>AUTOMATIC DATA PROCESSING ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DUOLINGO CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ROBERT HALF ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CIENA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ARISTA NETWORKS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>GE VERNOVA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CARGURUS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ASTERA LABS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>COINBASE GLOBAL CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>EBAY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ADOBE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SYMBOTIC CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NEBIUS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>QUALYS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
+    <t>CHIME FINANCIAL CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>H&amp;R BLOCK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SLM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SEZZLE INC (NMS)</t>
   </si>
   <si>
     <t>COREWEAVE CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>CHIME FINANCIAL CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SLM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SEZZLE INC (NMS)</t>
+    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
+    <t>CONCENTRIX ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DAVE CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
   </si>
   <si>
     <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
   </si>
   <si>
-    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
-    <t>META US 01/15/27 C720 OTC (META 1/15/27 C720 OTC)</t>
-  </si>
-  <si>
-    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>CONCENTRIX ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SITIME ORD (NMS)</t>
-  </si>
-  <si>
     <t>BLOCK CL A ORD (NYS)</t>
   </si>
   <si>
+    <t>TRIMBLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>IRON MOUNTAIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>WAYFAIR CL A ORD (NYS)</t>
+  </si>
+  <si>
     <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
   </si>
   <si>
-    <t>TRIMBLE ORD (NMS)</t>
-  </si>
-  <si>
     <t>EATON ORD (NYS)</t>
   </si>
   <si>
+    <t>LYFT CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AUTO1 GROUP ORD (GER)</t>
+  </si>
+  <si>
+    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
     <t>ALPHABET CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>INTUIT ORD (NMS)</t>
-  </si>
-  <si>
-    <t>IRON MOUNTAIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>WAYFAIR CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LYFT CL A ORD (NMS)</t>
+    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GLOBAL E ONLINE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>PROCORE TECHNOLOGIES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>APPLOVIN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AMAZON COM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>HEWLETT PACKARD ENTERPRISE ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TESLA ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SAP ORD (GER)</t>
   </si>
   <si>
     <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>AUTO1 GROUP ORD (GER)</t>
-  </si>
-  <si>
-    <t>PANASONIC HLDG ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>AMAZON COM ORD (NMS)</t>
+    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ZILLOW GROUP CL C ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (MIL)</t>
+  </si>
+  <si>
+    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>APPLIED MATERIAL ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ADVANTEST ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>AECOM ORD (NYS)</t>
+  </si>
+  <si>
+    <t>MAPLEBEAR ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TERADYNE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>STMICROELECTRONICS ADR (NYS)</t>
   </si>
   <si>
     <t>SK HYNIX ORD (KSC) CFD_USD</t>
   </si>
   <si>
-    <t>HEWLETT PACKARD ENTERPRISE ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SAP ORD (GER)</t>
-  </si>
-  <si>
-    <t>GLOBAL E ONLINE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>PROCORE TECHNOLOGIES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ADVANTEST ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>TESLA ORD (NMS)</t>
-  </si>
-  <si>
-    <t>APPLOVIN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
-  </si>
-  <si>
-    <t>ZILLOW GROUP CL C ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (MIL)</t>
-  </si>
-  <si>
-    <t>APPLIED MATERIAL ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>STMICROELECTRONICS ADR (NYS)</t>
-  </si>
-  <si>
-    <t>MAPLEBEAR ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TERADYNE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>AECOM ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NXP SEMICONDUCTORS ORD (NMS)</t>
+    <t>CHECK POINT SOFTWARE TECHNOLOGIS ORD (NMS)</t>
   </si>
   <si>
     <t>ROBLOX CL A ORD (NYS)</t>
   </si>
   <si>
     <t>META US 01/15/27 P620 OTC (META 1/15/27 P620 OTC)</t>
+  </si>
+  <si>
+    <t>REGAL REXNORD ORD (NYS)</t>
   </si>
   <si>
     <t>LIONSGATE STUDIOS ORD (NYS)</t>
@@ -1152,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D6D00E-F3A7-4FD6-86F3-70A35F8FFA0A}">
-  <dimension ref="A1:Q195"/>
+  <dimension ref="A1:Q199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1263,24 +1275,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C11" s="10">
-        <v>10.60053269172059</v>
+        <v>10.032656621227209</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D47" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10600532691720589</v>
+        <f t="shared" ref="D11:D45" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10032656621227209</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="10">
-        <v>-5.0054151943538239</v>
+        <v>-5.1704988081845586</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-5.0054151943538239E-2</v>
+        <v>-5.1704988081845586E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -1301,24 +1313,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C12" s="10">
-        <v>6.7844756079551178</v>
+        <v>6.5645846909600483</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>6.7844756079551177E-2</v>
+        <v>6.5645846909600486E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="10">
-        <v>-4.9463269302548794</v>
+        <v>-4.5072716016839154</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-4.9463269302548796E-2</v>
+        <v>-4.5072716016839154E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -1329,791 +1341,771 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C13" s="10">
-        <v>6.4573998275179303</v>
+        <v>4.9922384134675024</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>6.4573998275179303E-2</v>
+        <v>4.9922384134675021E-2</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="10">
-        <v>-4.8087289281268024</v>
+        <v>-3.8342330644920741</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-4.8087289281268021E-2</v>
+        <v>-3.8342330644920743E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C14" s="10">
-        <v>4.8587037343202066</v>
+        <v>4.7916088472466889</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.8587037343202064E-2</v>
+        <v>4.7916088472466888E-2</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.0106536504313821</v>
+        <v>-3.432968433269576</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.0106536504313818E-2</v>
+        <v>-3.4329684332695759E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C15" s="10">
-        <v>4.5069452256091758</v>
+        <v>4.4429121029125751</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.5069452256091755E-2</v>
+        <v>4.4429121029125752E-2</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="10">
-        <v>-4.0030845661530599</v>
+        <v>-3.4186706210816249</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-4.0030845661530597E-2</v>
+        <v>-3.4186706210816251E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C16" s="10">
-        <v>4.4580940752424443</v>
+        <v>4.288895898514375</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.4580940752424442E-2</v>
+        <v>4.2888958985143749E-2</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.9800354346337636</v>
+        <v>-3.3953542191112787</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.9800354346337635E-2</v>
+        <v>-3.3953542191112789E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C17" s="10">
-        <v>4.4215116009348474</v>
+        <v>3.8064092987500033</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>4.4215116009348472E-2</v>
+        <v>3.8064092987500034E-2</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.5531379569530239</v>
+        <v>-3.3205937108620782</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5531379569530237E-2</v>
+        <v>-3.3205937108620784E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C18" s="10">
-        <v>4.3288574508265407</v>
+        <v>3.7435246533950188</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>4.3288574508265405E-2</v>
+        <v>3.7435246533950188E-2</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.4040470371501215</v>
+        <v>-3.305152152253104</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4040470371501215E-2</v>
+        <v>-3.305152152253104E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C19" s="10">
-        <v>4.1932859182301261</v>
+        <v>3.0688986018070477</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>4.193285918230126E-2</v>
+        <v>3.0688986018070477E-2</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.3727638478001238</v>
+        <v>-3.1295440683041695</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.372763847800124E-2</v>
+        <v>-3.1295440683041693E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C20" s="10">
-        <v>3.8087184165930399</v>
+        <v>2.974535595805587</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.8087184165930398E-2</v>
+        <v>2.9745355958055872E-2</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.0221043907620477</v>
+        <v>-2.8489805574986744</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0221043907620478E-2</v>
+        <v>-2.8489805574986746E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C21" s="10">
-        <v>3.7355789472986665</v>
+        <v>2.6597141564846702</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>3.7355789472986664E-2</v>
+        <v>2.6597141564846702E-2</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.8069162750713996</v>
+        <v>-2.8465368730952396</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8069162750713996E-2</v>
+        <v>-2.8465368730952397E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C22" s="10">
-        <v>3.6504778755407252</v>
+        <v>2.534463384052581</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>3.6504778755407252E-2</v>
+        <v>2.5344633840525811E-2</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.7677477078642045</v>
+        <v>-2.7632198690417806</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7677477078642047E-2</v>
+        <v>-2.7632198690417806E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C23" s="10">
-        <v>3.4418984053326156</v>
+        <v>2.5274959704581641</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>3.4418984053326156E-2</v>
+        <v>2.5274959704581643E-2</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.5823036218207527</v>
+        <v>-2.5298056841944709</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5823036218207526E-2</v>
+        <v>-2.5298056841944708E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C24" s="10">
-        <v>3.2214229707359503</v>
+        <v>2.4518662620613929</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>3.2214229707359501E-2</v>
+        <v>2.4518662620613928E-2</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.4841451521405262</v>
+        <v>-2.454110615658279</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4841451521405263E-2</v>
+        <v>-2.4541106156582792E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C25" s="10">
-        <v>3.1877111794494297</v>
+        <v>2.327973295734207</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>3.1877111794494296E-2</v>
+        <v>2.3279732957342071E-2</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.4816840753667027</v>
+        <v>-2.2702908225579899</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4816840753667028E-2</v>
+        <v>-2.2702908225579899E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C26" s="10">
-        <v>2.7433610231173611</v>
+        <v>2.2621840484749103</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>2.7433610231173612E-2</v>
+        <v>2.2621840484749103E-2</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.4209693576546143</v>
+        <v>-2.2192043988824128</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4209693576546142E-2</v>
+        <v>-2.2192043988824128E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C27" s="10">
-        <v>2.7049612145847077</v>
+        <v>2.218799976641737</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.7049612145847078E-2</v>
+        <v>2.218799976641737E-2</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.2248305999880249</v>
+        <v>-2.2125510049526969</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2248305999880248E-2</v>
+        <v>-2.2125510049526967E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C28" s="10">
-        <v>2.557088351759325</v>
+        <v>2.0979262992440884</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.5570883517593249E-2</v>
+        <v>2.0979262992440885E-2</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>34</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.1748398540068625</v>
+        <v>-2.1734866837248878</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1748398540068624E-2</v>
+        <v>-2.173486683724888E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C29" s="10">
-        <v>2.5271323125377014</v>
+        <v>1.9968619267310121</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.5271323125377013E-2</v>
+        <v>1.9968619267310122E-2</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.171844364431843</v>
+        <v>-2.1534764237528137</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1718443644318429E-2</v>
+        <v>-2.1534764237528137E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C30" s="10">
-        <v>2.4113228097518418</v>
+        <v>1.986472098938951</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.4113228097518417E-2</v>
+        <v>1.986472098938951E-2</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.0659730878226759</v>
+        <v>-2.1391396618670315</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.065973087822676E-2</v>
+        <v>-2.1391396618670316E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C31" s="10">
-        <v>2.3533343910082296</v>
+        <v>1.9679910923984449</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.3533343910082296E-2</v>
+        <v>1.967991092398445E-2</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0436052664847062</v>
+        <v>-2.0454718574419917</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0436052664847063E-2</v>
+        <v>-2.0454718574419918E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C32" s="10">
-        <v>2.0970622879714469</v>
+        <v>1.9307280114811938</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.0970622879714469E-2</v>
+        <v>1.9307280114811937E-2</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.007008042912918</v>
+        <v>-2.033411263528131</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0070080429129181E-2</v>
+        <v>-2.0334112635281308E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C33" s="10">
-        <v>2.0260836036066894</v>
+        <v>1.6640148823011673</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.0260836036066893E-2</v>
+        <v>1.6640148823011673E-2</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G33" s="10">
-        <v>-2.0059792982706162</v>
+        <v>-1.9741664165062998</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0059792982706163E-2</v>
+        <v>-1.9741664165062997E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C34" s="10">
-        <v>2.0007870281536517</v>
+        <v>1.5499138700087787</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>2.0007870281536517E-2</v>
+        <v>1.5499138700087787E-2</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.8043046060173829</v>
+        <v>-1.929297673838144</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.8043046060173828E-2</v>
+        <v>-1.9292976738381439E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C35" s="10">
-        <v>1.9706840987942496</v>
+        <v>1.5162825406658633</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.9706840987942495E-2</v>
+        <v>1.5162825406658633E-2</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.7191258856667928</v>
+        <v>-1.6379702994790253</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7191258856667928E-2</v>
+        <v>-1.6379702994790253E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C36" s="10">
-        <v>1.9322991175116953</v>
+        <v>1.4198630546469748</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.9322991175116953E-2</v>
+        <v>1.4198630546469748E-2</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.5428259465808316</v>
+        <v>-1.5474968939695712</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5428259465808315E-2</v>
+        <v>-1.5474968939695712E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C37" s="10">
-        <v>1.6604767924836827</v>
+        <v>1.3616945285188287</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.6604767924836828E-2</v>
+        <v>1.3616945285188286E-2</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.4780023351977669</v>
+        <v>-1.5376735183298007</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4780023351977669E-2</v>
+        <v>-1.5376735183298008E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C38" s="10">
-        <v>1.6445098872439958</v>
+        <v>1.3511011926338614</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.6445098872439959E-2</v>
+        <v>1.3511011926338613E-2</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>44</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.4558245346491336</v>
+        <v>-1.5215067098010393</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4558245346491337E-2</v>
+        <v>-1.5215067098010394E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C39" s="10">
-        <v>1.4901618137897266</v>
+        <v>1.3056266021448164</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.4901618137897265E-2</v>
+        <v>1.3056266021448165E-2</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.4135991109142569</v>
+        <v>-1.4898873451015626</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4135991109142569E-2</v>
+        <v>-1.4898873451015626E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C40" s="10">
-        <v>1.4354222015801164</v>
+        <v>1.0144456000955313</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>1.4354222015801164E-2</v>
+        <v>1.0144456000955314E-2</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.3705227935299515</v>
+        <v>-1.2536474121179391</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.3705227935299515E-2</v>
+        <v>-1.253647412117939E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C41" s="10">
-        <v>1.3572438259438038</v>
+        <v>0.62192586338377553</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>1.3572438259438038E-2</v>
+        <v>6.2192586338377549E-3</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.3447737529812482</v>
+        <v>-1.1839464368861896</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.3447737529812482E-2</v>
+        <v>-1.1839464368861897E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C42" s="10">
-        <v>1.264754695629926</v>
+        <v>0.46883194855321542</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>1.2647546956299261E-2</v>
+        <v>4.6883194855321542E-3</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.1920275951266028</v>
+        <v>-1.1038327999980688</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1920275951266029E-2</v>
+        <v>-1.1038327999980689E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C43" s="10">
-        <v>0.83052147628999951</v>
+        <v>0.43950969956230901</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>8.3052147628999949E-3</v>
+        <v>4.3950969956230903E-3</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.1627162435045821</v>
+        <v>-1.0732978734402292</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.1627162435045822E-2</v>
+        <v>-1.0732978734402291E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C44" s="10">
-        <v>0.73327653502686652</v>
+        <v>0.38619037808332551</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>7.3327653502686654E-3</v>
+        <v>3.8619037808332551E-3</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.0914495185768041</v>
+        <v>-1.0505283383197708</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0914495185768041E-2</v>
+        <v>-1.0505283383197707E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="C45" s="10">
-        <v>0.41365323369863061</v>
+        <v>0.14305569396678564</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>4.1365323369863061E-3</v>
+        <v>1.4305569396678563E-3</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.0548534855285827</v>
+        <v>-1.0233135625590861</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0548534855285827E-2</v>
+        <v>-1.0233135625590861E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C46" s="10">
-        <v>0.31347907533904246</v>
-      </c>
-      <c r="D46" s="10">
-        <f t="shared" si="0"/>
-        <v>3.1347907533904244E-3</v>
-      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
       <c r="F46" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.0288980875615958</v>
+        <v>-1.0124649915953887</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0288980875615958E-2</v>
+        <v>-1.0124649915953887E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="10">
-        <v>0.1047909426122946</v>
-      </c>
-      <c r="D47" s="10">
-        <f t="shared" si="0"/>
-        <v>1.047909426122946E-3</v>
-      </c>
       <c r="F47" s="11" t="s">
         <v>53</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.0210247583717018</v>
+        <v>-0.98365098706492349</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0210247583717018E-2</v>
+        <v>-9.8365098706492352E-3</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="9"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
       <c r="F48" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G48" s="10">
-        <v>-1.0065331102521475</v>
+        <v>-0.94381664013024091</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0065331102521476E-2</v>
+        <v>-9.4381664013024093E-3</v>
       </c>
     </row>
     <row r="49" spans="4:8" x14ac:dyDescent="0.2">
@@ -2121,11 +2113,11 @@
         <v>55</v>
       </c>
       <c r="G49" s="10">
-        <v>-1.0027899057368415</v>
+        <v>-0.926678118467684</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0027899057368415E-2</v>
+        <v>-9.2667811846768398E-3</v>
       </c>
     </row>
     <row r="50" spans="4:8" x14ac:dyDescent="0.2">
@@ -2133,35 +2125,37 @@
         <v>56</v>
       </c>
       <c r="G50" s="10">
-        <v>-0.89886116674786209</v>
+        <v>-0.84580676266797039</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-8.9886116674786215E-3</v>
+        <v>-8.4580676266797043E-3</v>
       </c>
     </row>
     <row r="51" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D51" s="1"/>
       <c r="F51" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G51" s="10">
-        <v>-0.87744232497320407</v>
+        <v>-0.78224890759350829</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-8.7744232497320405E-3</v>
+        <v>-7.8224890759350831E-3</v>
       </c>
     </row>
     <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D52" s="1"/>
       <c r="F52" s="11" t="s">
         <v>58</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.8406649355016067</v>
+        <v>-0.77747557302802051</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-8.4066493550160673E-3</v>
+        <v>-7.7747557302802047E-3</v>
       </c>
     </row>
     <row r="53" spans="4:8" x14ac:dyDescent="0.2">
@@ -2170,11 +2164,11 @@
         <v>59</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.82422221767630077</v>
+        <v>-0.75649150514848595</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-8.2422221767630074E-3</v>
+        <v>-7.56491505148486E-3</v>
       </c>
     </row>
     <row r="54" spans="4:8" x14ac:dyDescent="0.2">
@@ -2183,11 +2177,11 @@
         <v>60</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.77806337021618732</v>
+        <v>-0.71720860738108261</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-7.7806337021618733E-3</v>
+        <v>-7.1720860738108258E-3</v>
       </c>
     </row>
     <row r="55" spans="4:8" x14ac:dyDescent="0.2">
@@ -2196,11 +2190,11 @@
         <v>61</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.71626659886207356</v>
+        <v>-0.65754618032149303</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-7.162665988620736E-3</v>
+        <v>-6.5754618032149307E-3</v>
       </c>
     </row>
     <row r="56" spans="4:8" x14ac:dyDescent="0.2">
@@ -2209,11 +2203,11 @@
         <v>62</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.6398799611941266</v>
+        <v>-0.62313755902555368</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-6.398799611941266E-3</v>
+        <v>-6.2313755902555371E-3</v>
       </c>
     </row>
     <row r="57" spans="4:8" x14ac:dyDescent="0.2">
@@ -2222,11 +2216,11 @@
         <v>63</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.62728422185505217</v>
+        <v>-0.59141221187096971</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-6.2728422185505221E-3</v>
+        <v>-5.9141221187096974E-3</v>
       </c>
     </row>
     <row r="58" spans="4:8" x14ac:dyDescent="0.2">
@@ -2235,11 +2229,11 @@
         <v>64</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.57783913250877372</v>
+        <v>-0.55113135083728282</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-5.778391325087737E-3</v>
+        <v>-5.5113135083728285E-3</v>
       </c>
     </row>
     <row r="59" spans="4:8" x14ac:dyDescent="0.2">
@@ -2248,11 +2242,11 @@
         <v>65</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.55063037778650714</v>
+        <v>-0.53187612584804311</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-5.5063037778650716E-3</v>
+        <v>-5.3187612584804315E-3</v>
       </c>
     </row>
     <row r="60" spans="4:8" x14ac:dyDescent="0.2">
@@ -2261,11 +2255,11 @@
         <v>66</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.51724082154546047</v>
+        <v>-0.50047808707859631</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-5.1724082154546045E-3</v>
+        <v>-5.0047808707859628E-3</v>
       </c>
     </row>
     <row r="61" spans="4:8" x14ac:dyDescent="0.2">
@@ -2274,11 +2268,11 @@
         <v>67</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.50750167736525298</v>
+        <v>-0.49314703386829195</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-5.07501677365253E-3</v>
+        <v>-4.9314703386829197E-3</v>
       </c>
     </row>
     <row r="62" spans="4:8" x14ac:dyDescent="0.2">
@@ -2287,11 +2281,11 @@
         <v>68</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.40397903919302397</v>
+        <v>-0.46170906347585844</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-4.0397903919302397E-3</v>
+        <v>-4.6170906347585841E-3</v>
       </c>
     </row>
     <row r="63" spans="4:8" x14ac:dyDescent="0.2">
@@ -2300,11 +2294,11 @@
         <v>69</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.38088235287124544</v>
+        <v>-0.45695785495720603</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-3.8088235287124543E-3</v>
+        <v>-4.5695785495720601E-3</v>
       </c>
     </row>
     <row r="64" spans="4:8" x14ac:dyDescent="0.2">
@@ -2313,11 +2307,11 @@
         <v>70</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.31176710244966732</v>
+        <v>-0.45286715475976053</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-3.1176710244966732E-3</v>
+        <v>-4.528671547597605E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
@@ -2326,11 +2320,11 @@
         <v>71</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.30613718264142664</v>
+        <v>-0.40637620627318749</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-3.0613718264142662E-3</v>
+        <v>-4.0637620627318747E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
@@ -2339,62 +2333,98 @@
         <v>72</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.27818329244660178</v>
+        <v>-0.36077501290077152</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-2.7818329244660178E-3</v>
+        <v>-3.6077501290077154E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.22417558766991635</v>
+        <v>-0.34724375695081222</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-2.2417558766991636E-3</v>
+        <v>-3.4724375695081222E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="13"/>
+      <c r="F68" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G68" s="10">
+        <v>-0.30292024459061806</v>
+      </c>
+      <c r="H68" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.0292024459061804E-3</v>
+      </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
+      <c r="F69" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G69" s="10">
+        <v>-0.28449775759484458</v>
+      </c>
+      <c r="H69" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.8449775759484459E-3</v>
+      </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
+      <c r="F70" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G70" s="10">
+        <v>-0.22294826677158472</v>
+      </c>
+      <c r="H70" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.2294826677158471E-3</v>
+      </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
-      <c r="G71" t="s">
-        <v>5</v>
+      <c r="F71" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G71" s="10">
+        <v>-0.21228573789399938</v>
+      </c>
+      <c r="H71" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.1228573789399937E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="13"/>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
-      <c r="H73" s="1"/>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
-      <c r="H74" s="1"/>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
-      <c r="H75" s="1"/>
+      <c r="G75" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
-      <c r="H76" s="1"/>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
@@ -2789,11 +2819,9 @@
       <c r="H174" s="1"/>
     </row>
     <row r="175" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
     <row r="176" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
     <row r="177" spans="8:8" x14ac:dyDescent="0.2">
@@ -2852,6 +2880,18 @@
     </row>
     <row r="195" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H195" s="1"/>
+    </row>
+    <row r="196" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H196" s="1"/>
+    </row>
+    <row r="197" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H197" s="1"/>
+    </row>
+    <row r="198" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H198" s="1"/>
+    </row>
+    <row r="199" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H199" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2861,7 +2901,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
-  <dimension ref="A1:Q196"/>
+  <dimension ref="A1:Q199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" customWidth="1"/>
@@ -2976,24 +3016,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C11" s="10">
-        <v>10.60053269172059</v>
+        <v>10.032656621227209</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D48" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10600532691720589</v>
+        <f t="shared" ref="D11:D47" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10032656621227209</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <v>-5.0054151943538239</v>
+        <v>-5.1704988081845586</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-5.0054151943538239E-2</v>
+        <v>-5.1704988081845586E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -3014,24 +3054,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C12" s="10">
-        <v>6.7844756079551178</v>
+        <v>6.5645846909600483</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>6.7844756079551177E-2</v>
+        <v>6.5645846909600486E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="10">
-        <v>-4.9463269302548794</v>
+        <v>-4.5072716016839154</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-4.9463269302548796E-2</v>
+        <v>-4.5072716016839154E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -3042,1090 +3082,1108 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C13" s="10">
-        <v>6.4573998275179303</v>
+        <v>4.9922384134675024</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>6.4573998275179303E-2</v>
+        <v>4.9922384134675021E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G13" s="10">
-        <v>-4.8087289281268024</v>
+        <v>-3.8342330644920741</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-4.8087289281268021E-2</v>
+        <v>-3.8342330644920743E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C14" s="10">
-        <v>4.8587037343202066</v>
+        <v>4.7916088472466889</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.8587037343202064E-2</v>
+        <v>4.7916088472466888E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.0106536504313821</v>
+        <v>-3.432968433269576</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.0106536504313818E-2</v>
+        <v>-3.4329684332695759E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C15" s="10">
-        <v>4.5069452256091758</v>
+        <v>4.4429121029125751</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.5069452256091755E-2</v>
+        <v>4.4429121029125752E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G15" s="10">
-        <v>-4.0030845661530599</v>
+        <v>-3.4186706210816249</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-4.0030845661530597E-2</v>
+        <v>-3.4186706210816251E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C16" s="10">
-        <v>4.4580940752424443</v>
+        <v>4.288895898514375</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.4580940752424442E-2</v>
+        <v>4.2888958985143749E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.9800354346337636</v>
+        <v>-3.3953542191112787</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.9800354346337635E-2</v>
+        <v>-3.3953542191112789E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C17" s="10">
-        <v>4.4215116009348474</v>
+        <v>3.8064092987500033</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>4.4215116009348472E-2</v>
+        <v>3.8064092987500034E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.5531379569530239</v>
+        <v>-3.3205937108620782</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5531379569530237E-2</v>
+        <v>-3.3205937108620784E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C18" s="10">
-        <v>4.3288574508265407</v>
+        <v>3.0688986018070477</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>4.3288574508265405E-2</v>
+        <v>3.0688986018070477E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.4040470371501215</v>
+        <v>-3.305152152253104</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4040470371501215E-2</v>
+        <v>-3.305152152253104E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C19" s="10">
-        <v>4.1932859182301261</v>
+        <v>2.974535595805587</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>4.193285918230126E-2</v>
+        <v>2.9745355958055872E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.3727638478001238</v>
+        <v>-3.1295440683041695</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.372763847800124E-2</v>
+        <v>-3.1295440683041693E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C20" s="10">
-        <v>3.7355789472986665</v>
+        <v>2.6597141564846702</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.7355789472986664E-2</v>
+        <v>2.6597141564846702E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.0221043907620477</v>
+        <v>-2.8489805574986744</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.0221043907620478E-2</v>
+        <v>-2.8489805574986746E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C21" s="10">
-        <v>3.6504778755407252</v>
+        <v>2.534463384052581</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>3.6504778755407252E-2</v>
+        <v>2.5344633840525811E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.8069162750713996</v>
+        <v>-2.8465368730952396</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8069162750713996E-2</v>
+        <v>-2.8465368730952397E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C22" s="10">
-        <v>3.4418984053326156</v>
+        <v>2.5274959704581641</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>3.4418984053326156E-2</v>
+        <v>2.5274959704581643E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.7677477078642045</v>
+        <v>-2.7632198690417806</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7677477078642047E-2</v>
+        <v>-2.7632198690417806E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C23" s="10">
-        <v>3.2214229707359503</v>
+        <v>2.4518662620613929</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>3.2214229707359501E-2</v>
+        <v>2.4518662620613928E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.5823036218207527</v>
+        <v>-2.5298056841944709</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5823036218207526E-2</v>
+        <v>-2.5298056841944708E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C24" s="10">
-        <v>3.1877111794494297</v>
+        <v>2.327973295734207</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>3.1877111794494296E-2</v>
+        <v>2.3279732957342071E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.4841451521405262</v>
+        <v>-2.454110615658279</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4841451521405263E-2</v>
+        <v>-2.4541106156582792E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C25" s="10">
-        <v>2.7433610231173611</v>
+        <v>2.2621840484749103</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>2.7433610231173612E-2</v>
+        <v>2.2621840484749103E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.4816840753667027</v>
+        <v>-2.2702908225579899</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4816840753667028E-2</v>
+        <v>-2.2702908225579899E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C26" s="10">
-        <v>2.7049612145847077</v>
+        <v>2.218799976641737</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>2.7049612145847078E-2</v>
+        <v>2.218799976641737E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.4209693576546143</v>
+        <v>-2.2192043988824128</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4209693576546142E-2</v>
+        <v>-2.2192043988824128E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C27" s="10">
-        <v>2.557088351759325</v>
+        <v>2.0979262992440884</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.5570883517593249E-2</v>
+        <v>2.0979262992440885E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.2248305999880249</v>
+        <v>-2.2125510049526969</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2248305999880248E-2</v>
+        <v>-2.2125510049526967E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C28" s="10">
-        <v>2.5271323125377014</v>
+        <v>1.9968619267310121</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.5271323125377013E-2</v>
+        <v>1.9968619267310122E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.1748398540068625</v>
+        <v>-2.1734866837248878</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1748398540068624E-2</v>
+        <v>-2.173486683724888E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C29" s="10">
-        <v>2.4113228097518418</v>
+        <v>1.986472098938951</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.4113228097518417E-2</v>
+        <v>1.986472098938951E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.171844364431843</v>
+        <v>-2.1534764237528137</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1718443644318429E-2</v>
+        <v>-2.1534764237528137E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C30" s="10">
-        <v>2.3533343910082296</v>
+        <v>1.9679910923984449</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.3533343910082296E-2</v>
+        <v>1.967991092398445E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.0659730878226759</v>
+        <v>-2.1391396618670315</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.065973087822676E-2</v>
+        <v>-2.1391396618670316E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C31" s="10">
-        <v>2.0970622879714469</v>
+        <v>1.9488561827770516</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.0970622879714469E-2</v>
+        <v>1.9488561827770517E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0436052664847062</v>
+        <v>-2.0454718574419917</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0436052664847063E-2</v>
+        <v>-2.0454718574419918E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C32" s="10">
-        <v>2.0260836036066894</v>
+        <v>1.9307280114811938</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.0260836036066893E-2</v>
+        <v>1.9307280114811937E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.007008042912918</v>
+        <v>-2.033411263528131</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0070080429129181E-2</v>
+        <v>-2.0334112635281308E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C33" s="10">
-        <v>2.0007870281536517</v>
+        <v>1.7946684706179672</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.0007870281536517E-2</v>
+        <v>1.7946684706179671E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G33" s="10">
-        <v>-2.0059792982706162</v>
+        <v>-1.9741664165062998</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0059792982706163E-2</v>
+        <v>-1.9741664165062997E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C34" s="10">
-        <v>1.9810424593554132</v>
+        <v>1.6640148823011673</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>1.9810424593554133E-2</v>
+        <v>1.6640148823011673E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.8043046060173829</v>
+        <v>-1.929297673838144</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.8043046060173828E-2</v>
+        <v>-1.9292976738381439E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C35" s="10">
-        <v>1.9706840987942496</v>
+        <v>1.5499138700087787</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.9706840987942495E-2</v>
+        <v>1.5499138700087787E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.7191258856667928</v>
+        <v>-1.6379702994790253</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.7191258856667928E-2</v>
+        <v>-1.6379702994790253E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C36" s="10">
-        <v>1.9322991175116953</v>
+        <v>1.5162825406658633</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.9322991175116953E-2</v>
+        <v>1.5162825406658633E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.5428259465808316</v>
+        <v>-1.5474968939695712</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5428259465808315E-2</v>
+        <v>-1.5474968939695712E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C37" s="10">
-        <v>1.8276759572376262</v>
+        <v>1.4198630546469748</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.8276759572376261E-2</v>
+        <v>1.4198630546469748E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.4780023351977669</v>
+        <v>-1.5376735183298007</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4780023351977669E-2</v>
+        <v>-1.5376735183298008E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C38" s="10">
-        <v>1.6604767924836827</v>
+        <v>1.3616945285188287</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.6604767924836828E-2</v>
+        <v>1.3616945285188286E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.4558245346491336</v>
+        <v>-1.5215067098010393</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4558245346491337E-2</v>
+        <v>-1.5215067098010394E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C39" s="10">
-        <v>1.6445098872439958</v>
+        <v>1.3511011926338614</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.6445098872439959E-2</v>
+        <v>1.3511011926338613E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.4135991109142569</v>
+        <v>-1.4898873451015626</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4135991109142569E-2</v>
+        <v>-1.4898873451015626E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C40" s="10">
-        <v>1.4901618137897266</v>
+        <v>1.3056266021448164</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>1.4901618137897265E-2</v>
+        <v>1.3056266021448165E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.3705227935299515</v>
+        <v>-1.2536474121179391</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.3705227935299515E-2</v>
+        <v>-1.253647412117939E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C41" s="10">
-        <v>1.4354222015801164</v>
+        <v>1.0144456000955313</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>1.4354222015801164E-2</v>
+        <v>1.0144456000955314E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.3447737529812482</v>
+        <v>-1.1839464368861896</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.3447737529812482E-2</v>
+        <v>-1.1839464368861897E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C42" s="10">
-        <v>1.3572438259438038</v>
+        <v>0.62192586338377553</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>1.3572438259438038E-2</v>
+        <v>6.2192586338377549E-3</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.1920275951266028</v>
+        <v>-1.1038327999980688</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1920275951266029E-2</v>
+        <v>-1.1038327999980689E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C43" s="10">
-        <v>1.264754695629926</v>
+        <v>0.46883194855321542</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>1.2647546956299261E-2</v>
+        <v>4.6883194855321542E-3</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.1627162435045821</v>
+        <v>-1.0732978734402292</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.1627162435045822E-2</v>
+        <v>-1.0732978734402291E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C44" s="10">
-        <v>0.83052147628999951</v>
+        <v>0.44721761564726037</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>8.3052147628999949E-3</v>
+        <v>4.4721761564726036E-3</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.0914495185768041</v>
+        <v>-1.0505283383197708</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0914495185768041E-2</v>
+        <v>-1.0505283383197707E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C45" s="10">
-        <v>0.73327653502686652</v>
+        <v>0.43950969956230901</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>7.3327653502686654E-3</v>
+        <v>4.3950969956230903E-3</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.0548534855285827</v>
+        <v>-1.0233135625590861</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0548534855285827E-2</v>
+        <v>-1.0233135625590861E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C46" s="10">
-        <v>0.67216782015429244</v>
+        <v>0.38619037808332551</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="0"/>
-        <v>6.7216782015429247E-3</v>
+        <v>3.8619037808332551E-3</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.0288980875615958</v>
+        <v>-1.0124649915953887</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0288980875615958E-2</v>
+        <v>-1.0124649915953887E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="C47" s="10">
-        <v>0.41365323369863061</v>
+        <v>0.14305569396678564</v>
       </c>
       <c r="D47" s="10">
         <f t="shared" si="0"/>
-        <v>4.1365323369863061E-3</v>
+        <v>1.4305569396678563E-3</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.0210247583717018</v>
+        <v>-0.98365098706492349</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0210247583717018E-2</v>
+        <v>-9.8365098706492352E-3</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="10">
-        <v>0.1047909426122946</v>
-      </c>
-      <c r="D48" s="10">
-        <f t="shared" si="0"/>
-        <v>1.047909426122946E-3</v>
-      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
       <c r="F48" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G48" s="10">
-        <v>-1.0065331102521475</v>
+        <v>-0.94381664013024091</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0065331102521476E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B49" s="9"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
+        <v>-9.4381664013024093E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F49" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G49" s="10">
-        <v>-1.0027899057368415</v>
+        <v>-0.926678118467684</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0027899057368415E-2</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-9.2667811846768398E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F50" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G50" s="10">
-        <v>-0.89886116674786209</v>
+        <v>-0.84580676266797039</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-8.9886116674786215E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-8.4580676266797043E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F51" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G51" s="10">
-        <v>-0.87744232497320407</v>
+        <v>-0.78224890759350829</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-8.7744232497320405E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.8224890759350831E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.8406649355016067</v>
+        <v>-0.77747557302802051</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-8.4066493550160673E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.7747557302802047E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D53" s="1"/>
       <c r="F53" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.82422221767630077</v>
+        <v>-0.75649150514848595</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-8.2422221767630074E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.56491505148486E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D54" s="1"/>
       <c r="F54" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.77806337021618732</v>
+        <v>-0.71720860738108261</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-7.7806337021618733E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-7.1720860738108258E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.71626659886207356</v>
+        <v>-0.67016588241884512</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-7.162665988620736E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-6.7016588241884511E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.6398799611941266</v>
+        <v>-0.65754618032149303</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-6.398799611941266E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-6.5754618032149307E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.62728422185505217</v>
+        <v>-0.62313755902555368</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-6.2728422185505221E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-6.2313755902555371E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.57783913250877372</v>
+        <v>-0.59141221187096971</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-5.778391325087737E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-5.9141221187096974E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.55063037778650714</v>
+        <v>-0.55113135083728282</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-5.5063037778650716E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-5.5113135083728285E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.51724082154546047</v>
+        <v>-0.53187612584804311</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-5.1724082154546045E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-5.3187612584804315E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.50750167736525298</v>
+        <v>-0.50047808707859631</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-5.07501677365253E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-5.0047808707859628E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.40397903919302397</v>
+        <v>-0.49314703386829195</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-4.0397903919302397E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-4.9314703386829197E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.38088235287124544</v>
+        <v>-0.46170906347585844</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-3.8088235287124543E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
+        <v>-4.6170906347585841E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.35868874481524993</v>
+        <v>-0.45695785495720603</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-3.5868874481524995E-3</v>
+        <v>-4.5695785495720601E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.31176710244966732</v>
+        <v>-0.45286715475976053</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-3.1176710244966732E-3</v>
+        <v>-4.528671547597605E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.30613718264142664</v>
+        <v>-0.40637620627318749</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-3.0613718264142662E-3</v>
+        <v>-4.0637620627318747E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.27818329244660178</v>
+        <v>-0.36077501290077152</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-2.7818329244660178E-3</v>
+        <v>-3.6077501290077154E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.22417558766991635</v>
+        <v>-0.34724375695081222</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-2.2417558766991636E-3</v>
+        <v>-3.4724375695081222E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="13"/>
+      <c r="F69" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G69" s="10">
+        <v>-0.30292024459061806</v>
+      </c>
+      <c r="H69" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.0292024459061804E-3</v>
+      </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
+      <c r="F70" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="G70" s="10">
+        <v>-0.28449775759484458</v>
+      </c>
+      <c r="H70" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.8449775759484459E-3</v>
+      </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
+      <c r="F71" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="10">
+        <v>-0.21228573789399938</v>
+      </c>
+      <c r="H71" s="12">
+        <f t="shared" si="2"/>
+        <v>-2.1228573789399937E-3</v>
+      </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
-      <c r="G72" t="s">
-        <v>5</v>
-      </c>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="13"/>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
-      <c r="H74" s="1"/>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
-      <c r="H75" s="1"/>
+      <c r="G75" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
-      <c r="H76" s="1"/>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
@@ -4527,53 +4585,52 @@
       <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D177" s="1"/>
+    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -4587,6 +4644,15 @@
     </row>
     <row r="196" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H196" s="1"/>
+    </row>
+    <row r="197" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H197" s="1"/>
+    </row>
+    <row r="198" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H198" s="1"/>
+    </row>
+    <row r="199" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H199" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{781EE849-22B3-0F49-9405-5EAD6A6C3A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A75269B-1B23-F14B-8C4D-A9235F379105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="224">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -63,477 +63,528 @@
     <t>SERIES: Trading (non-additive)</t>
   </si>
   <si>
+    <t>STM</t>
+  </si>
+  <si>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>PUBP</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Manticore Master Fund</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
+  </si>
+  <si>
+    <t>SITIME ORD (NMS)</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>CINTAS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>7751</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>LAMR</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>GEV</t>
+  </si>
+  <si>
+    <t>CSU</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>EXLS</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>BBY</t>
+  </si>
+  <si>
+    <t>PINS</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>ACN</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>FOXA</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>ALAB</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>RNG</t>
+  </si>
+  <si>
+    <t>RHI</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>BWA</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>SYF</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>GLW</t>
+  </si>
+  <si>
+    <t>SOFI</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>META</t>
+  </si>
+  <si>
+    <t>BFH</t>
+  </si>
+  <si>
+    <t>CRWV</t>
+  </si>
+  <si>
+    <t>CVSA</t>
+  </si>
+  <si>
+    <t>CHYM</t>
+  </si>
+  <si>
+    <t>SEZL</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>3034</t>
+  </si>
+  <si>
+    <t>ESLT</t>
+  </si>
+  <si>
+    <t>CNXC</t>
+  </si>
+  <si>
+    <t>DAVE</t>
+  </si>
+  <si>
+    <t>TEPRF</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>TRMB</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>AG1G</t>
+  </si>
+  <si>
+    <t>6857</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>ZETA</t>
+  </si>
+  <si>
+    <t>PCOR</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>NOD</t>
+  </si>
+  <si>
+    <t>SAPG</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>CART</t>
+  </si>
+  <si>
     <t>DASH</t>
   </si>
   <si>
-    <t>SITM</t>
-  </si>
-  <si>
-    <t>PUBP</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Manticore Master Fund</t>
-  </si>
-  <si>
-    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
-  </si>
-  <si>
-    <t>SITIME ORD (NMS)</t>
-  </si>
-  <si>
-    <t>Instrument</t>
-  </si>
-  <si>
-    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>CINTAS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CTAS</t>
-  </si>
-  <si>
-    <t>7751</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>6098</t>
-  </si>
-  <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t>LAMR</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>CSU</t>
-  </si>
-  <si>
-    <t>GEV</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>GRMN</t>
-  </si>
-  <si>
-    <t>EXLS</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>TEAM</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>PINS</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>FAF</t>
-  </si>
-  <si>
-    <t>RHI</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>ALAB</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>SYM</t>
-  </si>
-  <si>
-    <t>BBY</t>
-  </si>
-  <si>
-    <t>GLW</t>
-  </si>
-  <si>
-    <t>CIEN</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>TTAN</t>
-  </si>
-  <si>
-    <t>CHYM</t>
-  </si>
-  <si>
-    <t>SOFI</t>
-  </si>
-  <si>
-    <t>HRB</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>CRWV</t>
-  </si>
-  <si>
-    <t>3034</t>
-  </si>
-  <si>
-    <t>CNXC</t>
-  </si>
-  <si>
-    <t>DAVE</t>
-  </si>
-  <si>
-    <t>TEPRF</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>META</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
-    <t>TRMB</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>RACE</t>
-  </si>
-  <si>
-    <t>AG1G</t>
-  </si>
-  <si>
-    <t>005930</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>ZETA</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>PCOR</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>SAPG</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>Z</t>
+    <t>CHKP</t>
   </si>
   <si>
     <t>SPHR</t>
   </si>
   <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>6857</t>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>SHOP</t>
   </si>
   <si>
     <t>ACM</t>
   </si>
   <si>
-    <t>CART</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>STM</t>
-  </si>
-  <si>
-    <t>000660</t>
-  </si>
-  <si>
-    <t>CHKP</t>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>RRX</t>
   </si>
   <si>
     <t>RBLX</t>
   </si>
   <si>
-    <t>RRX</t>
-  </si>
-  <si>
     <t>LION</t>
   </si>
   <si>
     <t>CANON ORD (TYO) CFD</t>
   </si>
   <si>
+    <t>APPLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>HEALTHEQUITY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>AUTODESK ORD (NMS)</t>
+  </si>
+  <si>
+    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
+  </si>
+  <si>
+    <t>SERVICENOW ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GE VERNOVA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
+  </si>
+  <si>
+    <t>EXPEDIA GROUP ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WILLIAMS SONOMA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LOGITECH N ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GARMIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ARAMARK ORD (NYS)</t>
+  </si>
+  <si>
     <t>FAIR ISAAC ORD (NYS)</t>
   </si>
   <si>
-    <t>HEALTHEQUITY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>APPLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>AUTODESK ORD (NMS)</t>
-  </si>
-  <si>
-    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
-  </si>
-  <si>
-    <t>SERVICENOW ORD (NYS)</t>
-  </si>
-  <si>
     <t>EQUIFAX ORD (NYS)</t>
   </si>
   <si>
-    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
-  </si>
-  <si>
-    <t>GE VERNOVA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ARAMARK ORD (NYS)</t>
+    <t>ATLASSIAN CL A ORD (NMS)</t>
   </si>
   <si>
     <t>SALESFORCE ORD (NYS)</t>
   </si>
   <si>
-    <t>WILLIAMS SONOMA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EXPEDIA GROUP ORD (NMS)</t>
+    <t>SANRIO ORD (TYO) CFD</t>
   </si>
   <si>
     <t>VERISK ANALYTICS ORD (NMS)</t>
   </si>
   <si>
-    <t>GARMIN ORD (NYS)</t>
-  </si>
-  <si>
     <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
   </si>
   <si>
-    <t>SANRIO ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>LOGITECH N ORD (NMS)</t>
-  </si>
-  <si>
     <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
   </si>
   <si>
-    <t>ATLASSIAN CL A ORD (NMS)</t>
+    <t>BEST BUY ORD (NYS)</t>
+  </si>
+  <si>
+    <t>PINTEREST CL A ORD (NYS)</t>
   </si>
   <si>
     <t>GARTNER ORD (NYS)</t>
   </si>
   <si>
-    <t>PINTEREST CL A ORD (NYS)</t>
+    <t>ACCENTURE CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
   </si>
   <si>
     <t>REA GROUP ORD (ASX) CFD</t>
   </si>
   <si>
-    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
+    <t>ADOBE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>COINBASE GLOBAL CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FOX CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DUOLINGO CL A ORD (NMS)</t>
   </si>
   <si>
     <t>SAMSARA CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>ADOBE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>COINBASE GLOBAL CL A ORD (NMS)</t>
-  </si>
-  <si>
     <t>ARISTA NETWORKS ORD (NYS)</t>
   </si>
   <si>
+    <t>ASTERA LABS ORD (NMS)</t>
+  </si>
+  <si>
     <t>EBAY ORD (NMS)</t>
   </si>
   <si>
+    <t>RINGCENTRAL CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROBERT HALF ORD (NYS)</t>
+  </si>
+  <si>
     <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
   </si>
   <si>
-    <t>ROBERT HALF ORD (NYS)</t>
-  </si>
-  <si>
-    <t>DUOLINGO CL A ORD (NMS)</t>
+    <t>BORGWARNER ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
+  </si>
+  <si>
+    <t>META US 01/15/27 C720 OTC (META 1/15/27 C720 OTC)</t>
   </si>
   <si>
     <t>CARGURUS CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ASTERA LABS ORD (NMS)</t>
-  </si>
-  <si>
     <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
   </si>
   <si>
+    <t>SYNCHRONY FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
     <t>SYMBOTIC CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>BEST BUY ORD (NYS)</t>
-  </si>
-  <si>
     <t>CORNING ORD (NYS)</t>
   </si>
   <si>
-    <t>META US 01/15/27 C720 OTC (META 1/15/27 C720 OTC)</t>
+    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NEW YORK TIMES CL A ORD (NYS)</t>
   </si>
   <si>
     <t>CIENA ORD (NYS)</t>
   </si>
   <si>
+    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
+  </si>
+  <si>
     <t>QUALYS ORD (NMS)</t>
   </si>
   <si>
-    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SERVICETITAN CL A ORD (NMS)</t>
+    <t>H&amp;R BLOCK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>BREAD FINANCIAL HOLDINGS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>COREWEAVE CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>COVISTA ORD (NYS)</t>
   </si>
   <si>
     <t>CHIME FINANCIAL CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>H&amp;R BLOCK ORD (NYS)</t>
+    <t>SEZZLE INC (NMS)</t>
   </si>
   <si>
     <t>SLM ORD (NMS)</t>
   </si>
   <si>
-    <t>SEZZLE INC (NMS)</t>
-  </si>
-  <si>
-    <t>COREWEAVE CL A ORD (NMS)</t>
-  </si>
-  <si>
     <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
   </si>
   <si>
+    <t>ELBIT SYSTEMS ORD (NMS)</t>
+  </si>
+  <si>
     <t>CONCENTRIX ORD (NMS)</t>
   </si>
   <si>
@@ -555,103 +606,109 @@
     <t>IRON MOUNTAIN ORD (NYS)</t>
   </si>
   <si>
+    <t>EATON ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
     <t>WAYFAIR CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
-    <t>EATON ORD (NYS)</t>
+    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
+    <t>ALPHABET CL A ORD (NMS)</t>
   </si>
   <si>
     <t>LYFT CL A ORD (NMS)</t>
   </si>
   <si>
+    <t>GLOBAL E ONLINE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TESLA ORD (NMS)</t>
+  </si>
+  <si>
     <t>AUTO1 GROUP ORD (GER)</t>
   </si>
   <si>
-    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>ALPHABET CL A ORD (NMS)</t>
+    <t>ADVANTEST ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>HEWLETT PACKARD ENTERPRISE ORD (NYS)</t>
   </si>
   <si>
     <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>GLOBAL E ONLINE ORD (NMS)</t>
-  </si>
-  <si>
     <t>PROCORE TECHNOLOGIES ORD (NYS)</t>
   </si>
   <si>
+    <t>AMAZON COM ORD (NMS)</t>
+  </si>
+  <si>
     <t>APPLOVIN CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>AMAZON COM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>HEWLETT PACKARD ENTERPRISE ORD (NYS)</t>
-  </si>
-  <si>
-    <t>TESLA ORD (NMS)</t>
+    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
   </si>
   <si>
     <t>SAP ORD (GER)</t>
   </si>
   <si>
-    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
-  </si>
-  <si>
     <t>FERRARI ORD (NYS)</t>
   </si>
   <si>
+    <t>APPLIED MATERIAL ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (MIL)</t>
+  </si>
+  <si>
     <t>ZILLOW GROUP CL C ORD (NMS)</t>
   </si>
   <si>
-    <t>FERRARI ORD (MIL)</t>
+    <t>MAPLEBEAR ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CHECK POINT SOFTWARE TECHNOLOGIS ORD (NMS)</t>
   </si>
   <si>
     <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>APPLIED MATERIAL ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ADVANTEST ORD (TYO) CFD</t>
+    <t>TERADYNE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SHOPIFY CL A SUB VTG ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DOORDASH CL A ORD (NMS)</t>
   </si>
   <si>
     <t>AECOM ORD (NYS)</t>
   </si>
   <si>
-    <t>MAPLEBEAR ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TERADYNE ORD (NMS)</t>
+    <t>UBER TECHNOLOGIES INC. (NYS)</t>
+  </si>
+  <si>
+    <t>REGAL REXNORD ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ROBLOX CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>LIONSGATE STUDIOS ORD (NYS)</t>
   </si>
   <si>
     <t>STMICROELECTRONICS ADR (NYS)</t>
   </si>
   <si>
-    <t>SK HYNIX ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>CHECK POINT SOFTWARE TECHNOLOGIS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ROBLOX CL A ORD (NYS)</t>
-  </si>
-  <si>
     <t>META US 01/15/27 P620 OTC (META 1/15/27 P620 OTC)</t>
-  </si>
-  <si>
-    <t>REGAL REXNORD ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LIONSGATE STUDIOS ORD (NYS)</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D6D00E-F3A7-4FD6-86F3-70A35F8FFA0A}">
-  <dimension ref="A1:Q199"/>
+  <dimension ref="A1:Q207"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1275,24 +1332,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C11" s="10">
-        <v>10.032656621227209</v>
+        <v>9.3330323861757591</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D45" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10032656621227209</v>
+        <f t="shared" ref="D11:D46" si="0">IF(B11="","",(C11/100))</f>
+        <v>9.3330323861757589E-2</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="10">
-        <v>-5.1704988081845586</v>
+        <v>-5.1912406363108454</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-5.1704988081845586E-2</v>
+        <v>-5.1912406363108454E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -1313,24 +1370,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C12" s="10">
-        <v>6.5645846909600483</v>
+        <v>6.4045242162012643</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>6.5645846909600486E-2</v>
+        <v>6.4045242162012642E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="10">
-        <v>-4.5072716016839154</v>
+        <v>-4.4074558610953831</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-4.5072716016839154E-2</v>
+        <v>-4.4074558610953829E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -1341,759 +1398,769 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C13" s="10">
-        <v>4.9922384134675024</v>
+        <v>4.997669521653024</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>4.9922384134675021E-2</v>
+        <v>4.997669521653024E-2</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="10">
-        <v>-3.8342330644920741</v>
+        <v>-3.8199867307816526</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8342330644920743E-2</v>
+        <v>-3.8199867307816528E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C14" s="10">
-        <v>4.7916088472466889</v>
+        <v>4.5228622884551761</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.7916088472466888E-2</v>
+        <v>4.5228622884551761E-2</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="10">
-        <v>-3.432968433269576</v>
+        <v>-3.2871115750711666</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4329684332695759E-2</v>
+        <v>-3.2871115750711666E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C15" s="10">
-        <v>4.4429121029125751</v>
+        <v>4.4962824334879059</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.4429121029125752E-2</v>
+        <v>4.496282433487906E-2</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="10">
-        <v>-3.4186706210816249</v>
+        <v>-3.0677890059608321</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4186706210816251E-2</v>
+        <v>-3.0677890059608321E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C16" s="10">
-        <v>4.288895898514375</v>
+        <v>4.4512791012972119</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.2888958985143749E-2</v>
+        <v>4.4512791012972119E-2</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.3953542191112787</v>
+        <v>-3.0625077139746351</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.3953542191112789E-2</v>
+        <v>-3.062507713974635E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C17" s="10">
-        <v>3.8064092987500033</v>
+        <v>3.7796117220447774</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>3.8064092987500034E-2</v>
+        <v>3.7796117220447775E-2</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.3205937108620782</v>
+        <v>-3.0616223426238007</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.3205937108620784E-2</v>
+        <v>-3.0616223426238008E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C18" s="10">
-        <v>3.7435246533950188</v>
+        <v>3.7635363980862118</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>3.7435246533950188E-2</v>
+        <v>3.7635363980862119E-2</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.305152152253104</v>
+        <v>-2.8619239031503954</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.305152152253104E-2</v>
+        <v>-2.8619239031503953E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C19" s="10">
-        <v>3.0688986018070477</v>
+        <v>3.5145585031378617</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>3.0688986018070477E-2</v>
+        <v>3.5145585031378615E-2</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.1295440683041695</v>
+        <v>-2.723387379997857</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.1295440683041693E-2</v>
+        <v>-2.7233873799978568E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C20" s="10">
-        <v>2.974535595805587</v>
+        <v>3.5102488349797465</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>2.9745355958055872E-2</v>
+        <v>3.5102488349797463E-2</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="10">
-        <v>-2.8489805574986744</v>
+        <v>-2.6022591074043917</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8489805574986746E-2</v>
+        <v>-2.6022591074043918E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C21" s="10">
-        <v>2.6597141564846702</v>
+        <v>2.9104089491074694</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>2.6597141564846702E-2</v>
+        <v>2.9104089491074694E-2</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.8465368730952396</v>
+        <v>-2.4500278773865265</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8465368730952397E-2</v>
+        <v>-2.4500278773865264E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C22" s="10">
-        <v>2.534463384052581</v>
+        <v>2.8207296601561871</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>2.5344633840525811E-2</v>
+        <v>2.820729660156187E-2</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.7632198690417806</v>
+        <v>-2.447182322630443</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7632198690417806E-2</v>
+        <v>-2.447182322630443E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C23" s="10">
-        <v>2.5274959704581641</v>
+        <v>2.8068459906903556</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>2.5274959704581643E-2</v>
+        <v>2.8068459906903556E-2</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.5298056841944709</v>
+        <v>-2.3664960280935099</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5298056841944708E-2</v>
+        <v>-2.36649602809351E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C24" s="10">
-        <v>2.4518662620613929</v>
+        <v>2.6739247272246121</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>2.4518662620613928E-2</v>
+        <v>2.6739247272246122E-2</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.454110615658279</v>
+        <v>-2.2779770982158025</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4541106156582792E-2</v>
+        <v>-2.2779770982158026E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C25" s="10">
-        <v>2.327973295734207</v>
+        <v>2.384037889585461</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>2.3279732957342071E-2</v>
+        <v>2.3840378895854612E-2</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.2702908225579899</v>
+        <v>-2.2097160428286378</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2702908225579899E-2</v>
+        <v>-2.2097160428286376E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C26" s="10">
-        <v>2.2621840484749103</v>
+        <v>2.3159090447307342</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>2.2621840484749103E-2</v>
+        <v>2.3159090447307341E-2</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.2192043988824128</v>
+        <v>-2.2086797465031229</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2192043988824128E-2</v>
+        <v>-2.2086797465031231E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C27" s="10">
-        <v>2.218799976641737</v>
+        <v>2.2506814476600554</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.218799976641737E-2</v>
+        <v>2.2506814476600554E-2</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.2125510049526969</v>
+        <v>-2.0792458262098337</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2125510049526967E-2</v>
+        <v>-2.0792458262098336E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C28" s="10">
-        <v>2.0979262992440884</v>
+        <v>2.2014342655908568</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.0979262992440885E-2</v>
+        <v>2.2014342655908566E-2</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>34</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.1734866837248878</v>
+        <v>-2.0179485802828219</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.173486683724888E-2</v>
+        <v>-2.0179485802828218E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C29" s="10">
-        <v>1.9968619267310121</v>
+        <v>2.1367141863705053</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>1.9968619267310122E-2</v>
+        <v>2.1367141863705051E-2</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.1534764237528137</v>
+        <v>-2.0127371173549222</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1534764237528137E-2</v>
+        <v>-2.0127371173549222E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C30" s="10">
-        <v>1.986472098938951</v>
+        <v>2.1053895837492105</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>1.986472098938951E-2</v>
+        <v>2.1053895837492106E-2</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.1391396618670315</v>
+        <v>-1.9945375132381833</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1391396618670316E-2</v>
+        <v>-1.9945375132381832E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C31" s="10">
-        <v>1.9679910923984449</v>
+        <v>2.0150379053149194</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>1.967991092398445E-2</v>
+        <v>2.0150379053149193E-2</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0454718574419917</v>
+        <v>-1.9575135354448203</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0454718574419918E-2</v>
+        <v>-1.9575135354448204E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C32" s="10">
-        <v>1.9307280114811938</v>
+        <v>1.8976035049838567</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>1.9307280114811937E-2</v>
+        <v>1.8976035049838566E-2</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.033411263528131</v>
+        <v>-1.9426358084806181</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0334112635281308E-2</v>
+        <v>-1.9426358084806181E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C33" s="10">
-        <v>1.6640148823011673</v>
+        <v>1.7661162878516576</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>1.6640148823011673E-2</v>
+        <v>1.7661162878516577E-2</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9741664165062998</v>
+        <v>-1.9329580866225344</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9741664165062997E-2</v>
+        <v>-1.9329580866225344E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C34" s="10">
-        <v>1.5499138700087787</v>
+        <v>1.6453737619248152</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>1.5499138700087787E-2</v>
+        <v>1.6453737619248152E-2</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.929297673838144</v>
+        <v>-1.9196536458979772</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9292976738381439E-2</v>
+        <v>-1.9196536458979771E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C35" s="10">
-        <v>1.5162825406658633</v>
+        <v>1.6318126023378006</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.5162825406658633E-2</v>
+        <v>1.6318126023378007E-2</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.6379702994790253</v>
+        <v>-1.7862311305336349</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6379702994790253E-2</v>
+        <v>-1.7862311305336349E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C36" s="10">
-        <v>1.4198630546469748</v>
+        <v>1.6246065236015479</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.4198630546469748E-2</v>
+        <v>1.6246065236015479E-2</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.5474968939695712</v>
+        <v>-1.4823041327024635</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5474968939695712E-2</v>
+        <v>-1.4823041327024635E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C37" s="10">
-        <v>1.3616945285188287</v>
+        <v>1.6045820067479428</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.3616945285188286E-2</v>
+        <v>1.6045820067479427E-2</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.5376735183298007</v>
+        <v>-1.4759835526261758</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5376735183298008E-2</v>
+        <v>-1.4759835526261757E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C38" s="10">
-        <v>1.3511011926338614</v>
+        <v>1.5541083921662326</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.3511011926338613E-2</v>
+        <v>1.5541083921662327E-2</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>44</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.5215067098010393</v>
+        <v>-1.4589042052067787</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5215067098010394E-2</v>
+        <v>-1.4589042052067786E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C39" s="10">
-        <v>1.3056266021448164</v>
+        <v>1.545446915445547</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.3056266021448165E-2</v>
+        <v>1.5454469154455469E-2</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.4898873451015626</v>
+        <v>-1.4326497523780857</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4898873451015626E-2</v>
+        <v>-1.4326497523780856E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C40" s="10">
-        <v>1.0144456000955313</v>
+        <v>1.5217043990786141</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>1.0144456000955314E-2</v>
+        <v>1.521704399078614E-2</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.2536474121179391</v>
+        <v>-1.3834258678798415</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.253647412117939E-2</v>
+        <v>-1.3834258678798415E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C41" s="10">
-        <v>0.62192586338377553</v>
+        <v>1.3061490344607001</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>6.2192586338377549E-3</v>
+        <v>1.3061490344607001E-2</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.1839464368861896</v>
+        <v>-1.3752605784968333</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1839464368861897E-2</v>
+        <v>-1.3752605784968333E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C42" s="10">
-        <v>0.46883194855321542</v>
+        <v>0.73323948559305707</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>4.6883194855321542E-3</v>
+        <v>7.3323948559305711E-3</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.1038327999980688</v>
+        <v>-1.29696699070377</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1038327999980689E-2</v>
+        <v>-1.29696699070377E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C43" s="10">
-        <v>0.43950969956230901</v>
+        <v>0.44822998806776171</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>4.3950969956230903E-3</v>
+        <v>4.4822998806776171E-3</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.0732978734402292</v>
+        <v>-1.2513516835208465</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.0732978734402291E-2</v>
+        <v>-1.2513516835208465E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C44" s="10">
-        <v>0.38619037808332551</v>
+        <v>0.40235159656583624</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>3.8619037808332551E-3</v>
+        <v>4.0235159656583624E-3</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.0505283383197708</v>
+        <v>-1.2403435812448727</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0505283383197707E-2</v>
+        <v>-1.2403435812448727E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="C45" s="10">
-        <v>0.14305569396678564</v>
+        <v>0.36424020783090294</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>1.4305569396678563E-3</v>
+        <v>3.6424020783090293E-3</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.0233135625590861</v>
+        <v>-1.2395771802768629</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0233135625590861E-2</v>
+        <v>-1.2395771802768629E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B46" s="9"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
+      <c r="B46" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="10">
+        <v>0.31853903063918826</v>
+      </c>
+      <c r="D46" s="10">
+        <f t="shared" si="0"/>
+        <v>3.1853903063918825E-3</v>
+      </c>
       <c r="F46" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.0124649915953887</v>
+        <v>-1.1371907213886341</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0124649915953887E-2</v>
+        <v>-1.1371907213886341E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="9"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
       <c r="F47" s="11" t="s">
         <v>53</v>
       </c>
       <c r="G47" s="10">
-        <v>-0.98365098706492349</v>
+        <v>-1.0826597648051857</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="2"/>
-        <v>-9.8365098706492352E-3</v>
+        <v>-1.0826597648051857E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
@@ -2101,11 +2168,11 @@
         <v>54</v>
       </c>
       <c r="G48" s="10">
-        <v>-0.94381664013024091</v>
+        <v>-1.0733992986236223</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4381664013024093E-3</v>
+        <v>-1.0733992986236222E-2</v>
       </c>
     </row>
     <row r="49" spans="4:8" x14ac:dyDescent="0.2">
@@ -2113,11 +2180,11 @@
         <v>55</v>
       </c>
       <c r="G49" s="10">
-        <v>-0.926678118467684</v>
+        <v>-1.0042169707107096</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-9.2667811846768398E-3</v>
+        <v>-1.0042169707107095E-2</v>
       </c>
     </row>
     <row r="50" spans="4:8" x14ac:dyDescent="0.2">
@@ -2125,24 +2192,23 @@
         <v>56</v>
       </c>
       <c r="G50" s="10">
-        <v>-0.84580676266797039</v>
+        <v>-1.0031265680045631</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-8.4580676266797043E-3</v>
+        <v>-1.0031265680045632E-2</v>
       </c>
     </row>
     <row r="51" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D51" s="1"/>
       <c r="F51" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G51" s="10">
-        <v>-0.78224890759350829</v>
+        <v>-0.97575574140702037</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-7.8224890759350831E-3</v>
+        <v>-9.7575574140702035E-3</v>
       </c>
     </row>
     <row r="52" spans="4:8" x14ac:dyDescent="0.2">
@@ -2151,11 +2217,11 @@
         <v>58</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.77747557302802051</v>
+        <v>-0.90564704860312406</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-7.7747557302802047E-3</v>
+        <v>-9.0564704860312401E-3</v>
       </c>
     </row>
     <row r="53" spans="4:8" x14ac:dyDescent="0.2">
@@ -2164,11 +2230,11 @@
         <v>59</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.75649150514848595</v>
+        <v>-0.90256903209082329</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-7.56491505148486E-3</v>
+        <v>-9.0256903209082334E-3</v>
       </c>
     </row>
     <row r="54" spans="4:8" x14ac:dyDescent="0.2">
@@ -2177,11 +2243,11 @@
         <v>60</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.71720860738108261</v>
+        <v>-0.8573506111234761</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-7.1720860738108258E-3</v>
+        <v>-8.5735061112347608E-3</v>
       </c>
     </row>
     <row r="55" spans="4:8" x14ac:dyDescent="0.2">
@@ -2190,11 +2256,11 @@
         <v>61</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.65754618032149303</v>
+        <v>-0.81487742060026069</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-6.5754618032149307E-3</v>
+        <v>-8.1487742060026066E-3</v>
       </c>
     </row>
     <row r="56" spans="4:8" x14ac:dyDescent="0.2">
@@ -2203,11 +2269,11 @@
         <v>62</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.62313755902555368</v>
+        <v>-0.79791634336346862</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-6.2313755902555371E-3</v>
+        <v>-7.9791634336346864E-3</v>
       </c>
     </row>
     <row r="57" spans="4:8" x14ac:dyDescent="0.2">
@@ -2216,11 +2282,11 @@
         <v>63</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.59141221187096971</v>
+        <v>-0.7564239423846959</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-5.9141221187096974E-3</v>
+        <v>-7.5642394238469588E-3</v>
       </c>
     </row>
     <row r="58" spans="4:8" x14ac:dyDescent="0.2">
@@ -2229,11 +2295,11 @@
         <v>64</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.55113135083728282</v>
+        <v>-0.73654697681380243</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-5.5113135083728285E-3</v>
+        <v>-7.365469768138024E-3</v>
       </c>
     </row>
     <row r="59" spans="4:8" x14ac:dyDescent="0.2">
@@ -2242,11 +2308,11 @@
         <v>65</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.53187612584804311</v>
+        <v>-0.73335406381086576</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-5.3187612584804315E-3</v>
+        <v>-7.3335406381086574E-3</v>
       </c>
     </row>
     <row r="60" spans="4:8" x14ac:dyDescent="0.2">
@@ -2255,11 +2321,11 @@
         <v>66</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.50047808707859631</v>
+        <v>-0.69764385259381079</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-5.0047808707859628E-3</v>
+        <v>-6.9764385259381079E-3</v>
       </c>
     </row>
     <row r="61" spans="4:8" x14ac:dyDescent="0.2">
@@ -2268,11 +2334,11 @@
         <v>67</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.49314703386829195</v>
+        <v>-0.69440128902982368</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-4.9314703386829197E-3</v>
+        <v>-6.9440128902982364E-3</v>
       </c>
     </row>
     <row r="62" spans="4:8" x14ac:dyDescent="0.2">
@@ -2281,11 +2347,11 @@
         <v>68</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.46170906347585844</v>
+        <v>-0.64632331401879772</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-4.6170906347585841E-3</v>
+        <v>-6.4632331401879772E-3</v>
       </c>
     </row>
     <row r="63" spans="4:8" x14ac:dyDescent="0.2">
@@ -2294,11 +2360,11 @@
         <v>69</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.45695785495720603</v>
+        <v>-0.63331009293117091</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-4.5695785495720601E-3</v>
+        <v>-6.3331009293117087E-3</v>
       </c>
     </row>
     <row r="64" spans="4:8" x14ac:dyDescent="0.2">
@@ -2307,11 +2373,11 @@
         <v>70</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.45286715475976053</v>
+        <v>-0.57538380182665716</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-4.528671547597605E-3</v>
+        <v>-5.7538380182665712E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
@@ -2320,11 +2386,11 @@
         <v>71</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.40637620627318749</v>
+        <v>-0.54437893608761412</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-4.0637620627318747E-3</v>
+        <v>-5.4437893608761416E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
@@ -2333,11 +2399,11 @@
         <v>72</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.36077501290077152</v>
+        <v>-0.52788037292337664</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-3.6077501290077154E-3</v>
+        <v>-5.2788037292337666E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
@@ -2346,11 +2412,11 @@
         <v>73</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.34724375695081222</v>
+        <v>-0.51560198013929648</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-3.4724375695081222E-3</v>
+        <v>-5.1560198013929645E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
@@ -2359,11 +2425,11 @@
         <v>74</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.30292024459061806</v>
+        <v>-0.4494527922700427</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-3.0292024459061804E-3</v>
+        <v>-4.4945279227004272E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
@@ -2372,11 +2438,11 @@
         <v>75</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.28449775759484458</v>
+        <v>-0.44775569790059905</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-2.8449775759484459E-3</v>
+        <v>-4.4775569790059906E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
@@ -2385,78 +2451,150 @@
         <v>76</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.22294826677158472</v>
+        <v>-0.44172449147884374</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-2.2294826677158471E-3</v>
+        <v>-4.4172449147884376E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.21228573789399938</v>
+        <v>-0.41018047157044513</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-2.1228573789399937E-3</v>
+        <v>-4.1018047157044511E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="13"/>
+      <c r="F72" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-0.40669538411209616</v>
+      </c>
+      <c r="H72" s="12">
+        <f t="shared" si="2"/>
+        <v>-4.0669538411209618E-3</v>
+      </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
+      <c r="F73" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G73" s="10">
+        <v>-0.39186380670784482</v>
+      </c>
+      <c r="H73" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.9186380670784482E-3</v>
+      </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
+      <c r="F74" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-0.3660817980639165</v>
+      </c>
+      <c r="H74" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.6608179806391652E-3</v>
+      </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
-      <c r="G75" t="s">
-        <v>5</v>
+      <c r="F75" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-0.30618164253938557</v>
+      </c>
+      <c r="H75" s="12">
+        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
+        <v>-3.0618164253938557E-3</v>
       </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
+      <c r="F76" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G76" s="10">
+        <v>-0.29600327752404315</v>
+      </c>
+      <c r="H76" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.9600327752404313E-3</v>
+      </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
-      <c r="H77" s="1"/>
+      <c r="F77" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-0.2952482070686836</v>
+      </c>
+      <c r="H77" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.9524820706868359E-3</v>
+      </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
-      <c r="H78" s="1"/>
+      <c r="F78" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-0.25955403680212186</v>
+      </c>
+      <c r="H78" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.5955403680212184E-3</v>
+      </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
-      <c r="H79" s="1"/>
+      <c r="F79" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G79" s="10">
+        <v>-0.24694712280575792</v>
+      </c>
+      <c r="H79" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.4694712280575793E-3</v>
+      </c>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
-      <c r="H80" s="1"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="13"/>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
-      <c r="H81" s="1"/>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
-      <c r="H82" s="1"/>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
-      <c r="H83" s="1"/>
+      <c r="G83" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
-      <c r="H84" s="1"/>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
@@ -2819,6 +2957,7 @@
       <c r="H174" s="1"/>
     </row>
     <row r="175" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
     <row r="176" spans="4:8" x14ac:dyDescent="0.2">
@@ -2892,6 +3031,30 @@
     </row>
     <row r="199" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H199" s="1"/>
+    </row>
+    <row r="200" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H200" s="1"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H201" s="1"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H202" s="1"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H203" s="1"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H204" s="1"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H205" s="1"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H206" s="1"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H207" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2901,7 +3064,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
-  <dimension ref="A1:Q199"/>
+  <dimension ref="A1:Q207"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" customWidth="1"/>
@@ -3016,24 +3179,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="C11" s="10">
-        <v>10.032656621227209</v>
+        <v>9.3330323861757591</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D47" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10032656621227209</v>
+        <f t="shared" ref="D11:D49" si="0">IF(B11="","",(C11/100))</f>
+        <v>9.3330323861757589E-2</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <v>-5.1704988081845586</v>
+        <v>-5.1912406363108454</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-5.1704988081845586E-2</v>
+        <v>-5.1912406363108454E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -3054,24 +3217,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C12" s="10">
-        <v>6.5645846909600483</v>
+        <v>6.4045242162012643</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>6.5645846909600486E-2</v>
+        <v>6.4045242162012642E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="10">
-        <v>-4.5072716016839154</v>
+        <v>-4.4074558610953831</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-4.5072716016839154E-2</v>
+        <v>-4.4074558610953829E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -3082,1140 +3245,1230 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="C13" s="10">
-        <v>4.9922384134675024</v>
+        <v>4.997669521653024</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>4.9922384134675021E-2</v>
+        <v>4.997669521653024E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G13" s="10">
-        <v>-3.8342330644920741</v>
+        <v>-3.8199867307816526</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8342330644920743E-2</v>
+        <v>-3.8199867307816528E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="C14" s="10">
-        <v>4.7916088472466889</v>
+        <v>4.5228622884551761</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>4.7916088472466888E-2</v>
+        <v>4.5228622884551761E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G14" s="10">
-        <v>-3.432968433269576</v>
+        <v>-3.2871115750711666</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4329684332695759E-2</v>
+        <v>-3.2871115750711666E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C15" s="10">
-        <v>4.4429121029125751</v>
+        <v>4.4962824334879059</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.4429121029125752E-2</v>
+        <v>4.496282433487906E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G15" s="10">
-        <v>-3.4186706210816249</v>
+        <v>-3.0677890059608321</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-3.4186706210816251E-2</v>
+        <v>-3.0677890059608321E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C16" s="10">
-        <v>4.288895898514375</v>
+        <v>4.4512791012972119</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.2888958985143749E-2</v>
+        <v>4.4512791012972119E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.3953542191112787</v>
+        <v>-3.0625077139746351</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-3.3953542191112789E-2</v>
+        <v>-3.062507713974635E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="C17" s="10">
-        <v>3.8064092987500033</v>
+        <v>3.7796117220447774</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>3.8064092987500034E-2</v>
+        <v>3.7796117220447775E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.3205937108620782</v>
+        <v>-3.0616223426238007</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.3205937108620784E-2</v>
+        <v>-3.0616223426238008E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C18" s="10">
-        <v>3.0688986018070477</v>
+        <v>3.7635363980862118</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>3.0688986018070477E-2</v>
+        <v>3.7635363980862119E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.305152152253104</v>
+        <v>-2.8619239031503954</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.305152152253104E-2</v>
+        <v>-2.8619239031503953E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="C19" s="10">
-        <v>2.974535595805587</v>
+        <v>3.5102488349797465</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>2.9745355958055872E-2</v>
+        <v>3.5102488349797463E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.1295440683041695</v>
+        <v>-2.723387379997857</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.1295440683041693E-2</v>
+        <v>-2.7233873799978568E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="C20" s="10">
-        <v>2.6597141564846702</v>
+        <v>2.9104089491074694</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>2.6597141564846702E-2</v>
+        <v>2.9104089491074694E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G20" s="10">
-        <v>-2.8489805574986744</v>
+        <v>-2.6022591074043917</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8489805574986746E-2</v>
+        <v>-2.6022591074043918E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="C21" s="10">
-        <v>2.534463384052581</v>
+        <v>2.8207296601561871</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>2.5344633840525811E-2</v>
+        <v>2.820729660156187E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.8465368730952396</v>
+        <v>-2.4500278773865265</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-2.8465368730952397E-2</v>
+        <v>-2.4500278773865264E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C22" s="10">
-        <v>2.5274959704581641</v>
+        <v>2.8068459906903556</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>2.5274959704581643E-2</v>
+        <v>2.8068459906903556E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.7632198690417806</v>
+        <v>-2.447182322630443</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7632198690417806E-2</v>
+        <v>-2.447182322630443E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="C23" s="10">
-        <v>2.4518662620613929</v>
+        <v>2.6739247272246121</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>2.4518662620613928E-2</v>
+        <v>2.6739247272246122E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.5298056841944709</v>
+        <v>-2.3664960280935099</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.5298056841944708E-2</v>
+        <v>-2.36649602809351E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="C24" s="10">
-        <v>2.327973295734207</v>
+        <v>2.384037889585461</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>2.3279732957342071E-2</v>
+        <v>2.3840378895854612E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.454110615658279</v>
+        <v>-2.2779770982158025</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4541106156582792E-2</v>
+        <v>-2.2779770982158026E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="C25" s="10">
-        <v>2.2621840484749103</v>
+        <v>2.3159090447307342</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>2.2621840484749103E-2</v>
+        <v>2.3159090447307341E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.2702908225579899</v>
+        <v>-2.2097160428286378</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2702908225579899E-2</v>
+        <v>-2.2097160428286376E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="C26" s="10">
-        <v>2.218799976641737</v>
+        <v>2.2506814476600554</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>2.218799976641737E-2</v>
+        <v>2.2506814476600554E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.2192043988824128</v>
+        <v>-2.2086797465031229</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2192043988824128E-2</v>
+        <v>-2.2086797465031231E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="C27" s="10">
-        <v>2.0979262992440884</v>
+        <v>2.2014342655908568</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.0979262992440885E-2</v>
+        <v>2.2014342655908566E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.2125510049526969</v>
+        <v>-2.0792458262098337</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2125510049526967E-2</v>
+        <v>-2.0792458262098336E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="C28" s="10">
-        <v>1.9968619267310121</v>
+        <v>2.1367141863705053</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>1.9968619267310122E-2</v>
+        <v>2.1367141863705051E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.1734866837248878</v>
+        <v>-2.0179485802828219</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.173486683724888E-2</v>
+        <v>-2.0179485802828218E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C29" s="10">
-        <v>1.986472098938951</v>
+        <v>2.1053895837492105</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>1.986472098938951E-2</v>
+        <v>2.1053895837492106E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.1534764237528137</v>
+        <v>-2.0127371173549222</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1534764237528137E-2</v>
+        <v>-2.0127371173549222E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C30" s="10">
-        <v>1.9679910923984449</v>
+        <v>2.0150379053149194</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>1.967991092398445E-2</v>
+        <v>2.0150379053149193E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.1391396618670315</v>
+        <v>-1.9945375132381833</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.1391396618670316E-2</v>
+        <v>-1.9945375132381832E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C31" s="10">
-        <v>1.9488561827770516</v>
+        <v>1.8976035049838567</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>1.9488561827770517E-2</v>
+        <v>1.8976035049838566E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0454718574419917</v>
+        <v>-1.9575135354448203</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0454718574419918E-2</v>
+        <v>-1.9575135354448204E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="C32" s="10">
-        <v>1.9307280114811938</v>
+        <v>1.8291521309247862</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>1.9307280114811937E-2</v>
+        <v>1.8291521309247862E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.033411263528131</v>
+        <v>-1.9426358084806181</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0334112635281308E-2</v>
+        <v>-1.9426358084806181E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="C33" s="10">
-        <v>1.7946684706179672</v>
+        <v>1.7661162878516576</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>1.7946684706179671E-2</v>
+        <v>1.7661162878516577E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9741664165062998</v>
+        <v>-1.9329580866225344</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9741664165062997E-2</v>
+        <v>-1.9329580866225344E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C34" s="10">
-        <v>1.6640148823011673</v>
+        <v>1.6854063722130754</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>1.6640148823011673E-2</v>
+        <v>1.6854063722130753E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.929297673838144</v>
+        <v>-1.9196536458979772</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-1.9292976738381439E-2</v>
+        <v>-1.9196536458979771E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C35" s="10">
-        <v>1.5499138700087787</v>
+        <v>1.6453737619248152</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.5499138700087787E-2</v>
+        <v>1.6453737619248152E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.6379702994790253</v>
+        <v>-1.7862311305336349</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6379702994790253E-2</v>
+        <v>-1.7862311305336349E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C36" s="10">
-        <v>1.5162825406658633</v>
+        <v>1.6318126023378006</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.5162825406658633E-2</v>
+        <v>1.6318126023378007E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.5474968939695712</v>
+        <v>-1.4823041327024635</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5474968939695712E-2</v>
+        <v>-1.4823041327024635E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C37" s="10">
-        <v>1.4198630546469748</v>
+        <v>1.6045820067479428</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.4198630546469748E-2</v>
+        <v>1.6045820067479427E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.5376735183298007</v>
+        <v>-1.4759835526261758</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5376735183298008E-2</v>
+        <v>-1.4759835526261757E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C38" s="10">
-        <v>1.3616945285188287</v>
+        <v>1.5541083921662326</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.3616945285188286E-2</v>
+        <v>1.5541083921662327E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.5215067098010393</v>
+        <v>-1.4589042052067787</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5215067098010394E-2</v>
+        <v>-1.4589042052067786E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="C39" s="10">
-        <v>1.3511011926338614</v>
+        <v>1.545446915445547</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.3511011926338613E-2</v>
+        <v>1.5454469154455469E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.4898873451015626</v>
+        <v>-1.4326497523780857</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4898873451015626E-2</v>
+        <v>-1.4326497523780856E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="C40" s="10">
-        <v>1.3056266021448164</v>
+        <v>1.5217043990786141</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>1.3056266021448165E-2</v>
+        <v>1.521704399078614E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.2536474121179391</v>
+        <v>-1.3834258678798415</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.253647412117939E-2</v>
+        <v>-1.3834258678798415E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C41" s="10">
-        <v>1.0144456000955313</v>
+        <v>1.4194172413124861</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>1.0144456000955314E-2</v>
+        <v>1.4194172413124862E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.1839464368861896</v>
+        <v>-1.3752605784968333</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1839464368861897E-2</v>
+        <v>-1.3752605784968333E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="C42" s="10">
-        <v>0.62192586338377553</v>
+        <v>1.3061490344607001</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>6.2192586338377549E-3</v>
+        <v>1.3061490344607001E-2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.1038327999980688</v>
+        <v>-1.29696699070377</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.1038327999980689E-2</v>
+        <v>-1.29696699070377E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="C43" s="10">
-        <v>0.46883194855321542</v>
+        <v>0.73323948559305707</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>4.6883194855321542E-3</v>
+        <v>7.3323948559305711E-3</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.0732978734402292</v>
+        <v>-1.2513516835208465</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.0732978734402291E-2</v>
+        <v>-1.2513516835208465E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C44" s="10">
-        <v>0.44721761564726037</v>
+        <v>0.44822998806776171</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>4.4721761564726036E-3</v>
+        <v>4.4822998806776171E-3</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.0505283383197708</v>
+        <v>-1.2403435812448727</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0505283383197707E-2</v>
+        <v>-1.2403435812448727E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="C45" s="10">
-        <v>0.43950969956230901</v>
+        <v>0.40235159656583624</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>4.3950969956230903E-3</v>
+        <v>4.0235159656583624E-3</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.0233135625590861</v>
+        <v>-1.2395771802768629</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0233135625590861E-2</v>
+        <v>-1.2395771802768629E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="C46" s="10">
-        <v>0.38619037808332551</v>
+        <v>0.36424020783090294</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="0"/>
-        <v>3.8619037808332551E-3</v>
+        <v>3.6424020783090293E-3</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.0124649915953887</v>
+        <v>-1.1371907213886341</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0124649915953887E-2</v>
+        <v>-1.1371907213886341E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.31853903063918826</v>
+      </c>
+      <c r="D47" s="10">
+        <f t="shared" si="0"/>
+        <v>3.1853903063918825E-3</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="G47" s="10">
+        <v>-1.0826597648051857</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.0826597648051857E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C48" s="10">
+        <v>0.31475623077823295</v>
+      </c>
+      <c r="D48" s="10">
+        <f t="shared" si="0"/>
+        <v>3.1475623077823296E-3</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="G48" s="10">
+        <v>-1.0733992986236223</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.0733992986236222E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="10">
-        <v>0.14305569396678564</v>
-      </c>
-      <c r="D47" s="10">
-        <f t="shared" si="0"/>
-        <v>1.4305569396678563E-3</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G47" s="10">
-        <v>-0.98365098706492349</v>
-      </c>
-      <c r="H47" s="12">
-        <f t="shared" si="2"/>
-        <v>-9.8365098706492352E-3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="9"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="F48" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G48" s="10">
-        <v>-0.94381664013024091</v>
-      </c>
-      <c r="H48" s="12">
-        <f t="shared" si="2"/>
-        <v>-9.4381664013024093E-3</v>
-      </c>
-    </row>
-    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="C49" s="10">
+        <v>0.20518928228906169</v>
+      </c>
+      <c r="D49" s="10">
+        <f t="shared" si="0"/>
+        <v>2.0518928228906168E-3</v>
+      </c>
       <c r="F49" s="11" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G49" s="10">
-        <v>-0.926678118467684</v>
+        <v>-1.0042169707107096</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-9.2667811846768398E-3</v>
-      </c>
-    </row>
-    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.0042169707107095E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="9"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
       <c r="F50" s="11" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G50" s="10">
-        <v>-0.84580676266797039</v>
+        <v>-1.0031265680045631</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-8.4580676266797043E-3</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-1.0031265680045632E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F51" s="11" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="G51" s="10">
-        <v>-0.78224890759350829</v>
+        <v>-0.97575574140702037</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-7.8224890759350831E-3</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-9.7575574140702035E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.77747557302802051</v>
+        <v>-0.90564704860312406</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-7.7747557302802047E-3</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D53" s="1"/>
+        <v>-9.0564704860312401E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.75649150514848595</v>
+        <v>-0.90256903209082329</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-7.56491505148486E-3</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D54" s="1"/>
+        <v>-9.0256903209082334E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F54" s="11" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.71720860738108261</v>
+        <v>-0.8573506111234761</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-7.1720860738108258E-3</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.5735061112347608E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.67016588241884512</v>
+        <v>-0.84263660370160964</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-6.7016588241884511E-3</v>
-      </c>
-    </row>
-    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.4263660370160962E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.65754618032149303</v>
+        <v>-0.81487742060026069</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-6.5754618032149307E-3</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-8.1487742060026066E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.62313755902555368</v>
+        <v>-0.79791634336346862</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-6.2313755902555371E-3</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.9791634336346864E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.59141221187096971</v>
+        <v>-0.7564239423846959</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-5.9141221187096974E-3</v>
-      </c>
-    </row>
-    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.5642394238469588E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.55113135083728282</v>
+        <v>-0.73654697681380243</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-5.5113135083728285E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.365469768138024E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.53187612584804311</v>
+        <v>-0.73335406381086576</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-5.3187612584804315E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-7.3335406381086574E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.50047808707859631</v>
+        <v>-0.69764385259381079</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-5.0047808707859628E-3</v>
-      </c>
-    </row>
-    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-6.9764385259381079E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.49314703386829195</v>
+        <v>-0.69440128902982368</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-4.9314703386829197E-3</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-6.9440128902982364E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.46170906347585844</v>
+        <v>-0.64632331401879772</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-4.6170906347585841E-3</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
+        <v>-6.4632331401879772E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.45695785495720603</v>
+        <v>-0.63331009293117091</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-4.5695785495720601E-3</v>
+        <v>-6.3331009293117087E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.45286715475976053</v>
+        <v>-0.57538380182665716</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-4.528671547597605E-3</v>
+        <v>-5.7538380182665712E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.40637620627318749</v>
+        <v>-0.54437893608761412</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-4.0637620627318747E-3</v>
+        <v>-5.4437893608761416E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.36077501290077152</v>
+        <v>-0.51560198013929648</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-3.6077501290077154E-3</v>
+        <v>-5.1560198013929645E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.34724375695081222</v>
+        <v>-0.4494527922700427</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-3.4724375695081222E-3</v>
+        <v>-4.4945279227004272E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.30292024459061806</v>
+        <v>-0.44775569790059905</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-3.0292024459061804E-3</v>
+        <v>-4.4775569790059906E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.28449775759484458</v>
+        <v>-0.44172449147884374</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-2.8449775759484459E-3</v>
+        <v>-4.4172449147884376E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>14</v>
+        <v>178</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.21228573789399938</v>
+        <v>-0.41018047157044513</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-2.1228573789399937E-3</v>
+        <v>-4.1018047157044511E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="13"/>
+      <c r="F72" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-0.40669538411209616</v>
+      </c>
+      <c r="H72" s="12">
+        <f t="shared" si="2"/>
+        <v>-4.0669538411209618E-3</v>
+      </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
+      <c r="F73" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="G73" s="10">
+        <v>-0.39186380670784482</v>
+      </c>
+      <c r="H73" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.9186380670784482E-3</v>
+      </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
+      <c r="F74" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-0.3660817980639165</v>
+      </c>
+      <c r="H74" s="12">
+        <f t="shared" si="2"/>
+        <v>-3.6608179806391652E-3</v>
+      </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
-      <c r="G75" t="s">
-        <v>5</v>
+      <c r="F75" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-0.30618164253938557</v>
+      </c>
+      <c r="H75" s="12">
+        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
+        <v>-3.0618164253938557E-3</v>
       </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
+      <c r="F76" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="G76" s="10">
+        <v>-0.29600327752404315</v>
+      </c>
+      <c r="H76" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.9600327752404313E-3</v>
+      </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
-      <c r="H77" s="1"/>
+      <c r="F77" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-0.2952482070686836</v>
+      </c>
+      <c r="H77" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.9524820706868359E-3</v>
+      </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
-      <c r="H78" s="1"/>
+      <c r="F78" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-0.25955403680212186</v>
+      </c>
+      <c r="H78" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.5955403680212184E-3</v>
+      </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
-      <c r="H79" s="1"/>
+      <c r="F79" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" s="10">
+        <v>-0.24694712280575792</v>
+      </c>
+      <c r="H79" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.4694712280575793E-3</v>
+      </c>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
-      <c r="H80" s="1"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="13"/>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
-      <c r="H81" s="1"/>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
-      <c r="H82" s="1"/>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
-      <c r="H83" s="1"/>
+      <c r="G83" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
-      <c r="H84" s="1"/>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
@@ -4585,52 +4838,54 @@
       <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.2">
@@ -4653,6 +4908,30 @@
     </row>
     <row r="199" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H199" s="1"/>
+    </row>
+    <row r="200" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H200" s="1"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H201" s="1"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H202" s="1"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H203" s="1"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H204" s="1"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H205" s="1"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H206" s="1"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H207" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LucaBasile\Documents\Client work\Client report work\client_Contour\Delta Adjusted Report Backups\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BEBF5D6-FB02-B540-BFE8-33A7CE52766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Issuer" sheetId="1" r:id="rId3"/>
-    <sheet name="Instrument" sheetId="2" r:id="rId4"/>
+    <sheet name="Issuer" sheetId="1" r:id="rId1"/>
+    <sheet name="Instrument" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="237">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -61,487 +63,574 @@
     <t>SERIES: Trading (non-additive)</t>
   </si>
   <si>
+    <t>LION</t>
+  </si>
+  <si>
+    <t>SITM</t>
+  </si>
+  <si>
+    <t>PUBP</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Manticore Master Fund</t>
+  </si>
+  <si>
+    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
+  </si>
+  <si>
+    <t>SITIME ORD (NMS)</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>CINTAS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CTAS</t>
+  </si>
+  <si>
+    <t>ACN</t>
+  </si>
+  <si>
+    <t>ADSK</t>
+  </si>
+  <si>
+    <t>7751</t>
+  </si>
+  <si>
+    <t>GEV</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>HQY</t>
+  </si>
+  <si>
+    <t>FICO</t>
+  </si>
+  <si>
+    <t>CSU</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>LOGI</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>EXLS</t>
+  </si>
+  <si>
+    <t>LAMR</t>
+  </si>
+  <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>MANH</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>BBY</t>
+  </si>
+  <si>
+    <t>ADBE</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>ANET</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
+    <t>NYT</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>RNG</t>
+  </si>
+  <si>
+    <t>SYF</t>
+  </si>
+  <si>
+    <t>CVSA</t>
+  </si>
+  <si>
+    <t>LOPE</t>
+  </si>
+  <si>
+    <t>RHI</t>
+  </si>
+  <si>
+    <t>ALAB</t>
+  </si>
+  <si>
+    <t>TTAN</t>
+  </si>
+  <si>
+    <t>GM</t>
+  </si>
+  <si>
+    <t>BFH</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>WDC</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>SOFI</t>
+  </si>
+  <si>
+    <t>QLYS</t>
+  </si>
+  <si>
+    <t>HRB</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>FDS</t>
+  </si>
+  <si>
+    <t>ESLT</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>SEZL</t>
+  </si>
+  <si>
+    <t>SGI</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>CHYM</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>CRWV</t>
+  </si>
+  <si>
+    <t>3034</t>
+  </si>
+  <si>
+    <t>SLM</t>
+  </si>
+  <si>
+    <t>CNXC</t>
+  </si>
+  <si>
+    <t>DAVE</t>
+  </si>
+  <si>
+    <t>HUT</t>
+  </si>
+  <si>
+    <t>TEPRF</t>
+  </si>
+  <si>
+    <t>CHH</t>
+  </si>
+  <si>
+    <t>NBIS</t>
+  </si>
+  <si>
+    <t>XYZ</t>
+  </si>
+  <si>
+    <t>TRMB</t>
+  </si>
+  <si>
+    <t>IRM</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>ETN</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>GLBE</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>LYFT</t>
+  </si>
+  <si>
+    <t>AG1G</t>
+  </si>
+  <si>
+    <t>SPOT</t>
+  </si>
+  <si>
+    <t>SHOP</t>
+  </si>
+  <si>
+    <t>005930</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>SAPG</t>
+  </si>
+  <si>
+    <t>PCOR</t>
+  </si>
+  <si>
+    <t>NOD</t>
+  </si>
+  <si>
+    <t>DOCS</t>
+  </si>
+  <si>
+    <t>6857</t>
+  </si>
+  <si>
+    <t>CART</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>ZETA</t>
+  </si>
+  <si>
     <t>DASH</t>
   </si>
   <si>
-    <t>SITM</t>
-  </si>
-  <si>
-    <t>PUBP</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Manticore Master Fund</t>
-  </si>
-  <si>
-    <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
-  </si>
-  <si>
-    <t>SITIME ORD (NMS)</t>
-  </si>
-  <si>
-    <t>Instrument</t>
-  </si>
-  <si>
-    <t>PUBLICIS GROUPE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>CINTAS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CTAS</t>
-  </si>
-  <si>
-    <t>7751</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>HQY</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>6098</t>
-  </si>
-  <si>
-    <t>ADSK</t>
-  </si>
-  <si>
-    <t>LAMR</t>
-  </si>
-  <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>CSU</t>
-  </si>
-  <si>
-    <t>GEV</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>GRMN</t>
-  </si>
-  <si>
-    <t>EXLS</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t>LOGI</t>
-  </si>
-  <si>
-    <t>MANH</t>
-  </si>
-  <si>
-    <t>TEAM</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>PINS</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>IOT</t>
-  </si>
-  <si>
-    <t>ADBE</t>
-  </si>
-  <si>
-    <t>COIN</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>FAF</t>
-  </si>
-  <si>
-    <t>RHI</t>
-  </si>
-  <si>
-    <t>DUOL</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>LOPE</t>
-  </si>
-  <si>
-    <t>ALAB</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>SYM</t>
-  </si>
-  <si>
-    <t>BBY</t>
-  </si>
-  <si>
-    <t>GLW</t>
-  </si>
-  <si>
-    <t>CIEN</t>
-  </si>
-  <si>
-    <t>QLYS</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>TTAN</t>
-  </si>
-  <si>
-    <t>CHYM</t>
-  </si>
-  <si>
-    <t>SOFI</t>
-  </si>
-  <si>
-    <t>HRB</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>CRWV</t>
-  </si>
-  <si>
-    <t>3034</t>
-  </si>
-  <si>
-    <t>CNXC</t>
-  </si>
-  <si>
-    <t>DAVE</t>
-  </si>
-  <si>
-    <t>TEPRF</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>META</t>
-  </si>
-  <si>
-    <t>XYZ</t>
-  </si>
-  <si>
-    <t>TRMB</t>
-  </si>
-  <si>
-    <t>IRM</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>TSM</t>
-  </si>
-  <si>
-    <t>ETN</t>
-  </si>
-  <si>
-    <t>LYFT</t>
-  </si>
-  <si>
-    <t>RACE</t>
-  </si>
-  <si>
-    <t>AG1G</t>
-  </si>
-  <si>
-    <t>005930</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>ZETA</t>
-  </si>
-  <si>
-    <t>GLBE</t>
-  </si>
-  <si>
-    <t>PCOR</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
-    <t>AMZN</t>
+    <t>UBER</t>
+  </si>
+  <si>
+    <t>SPHR</t>
+  </si>
+  <si>
+    <t>RRX</t>
+  </si>
+  <si>
+    <t>5802</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>TER</t>
   </si>
   <si>
     <t>HPE</t>
   </si>
   <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>SAPG</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>SPHR</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>6857</t>
-  </si>
-  <si>
     <t>ACM</t>
   </si>
   <si>
-    <t>CART</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>STM</t>
-  </si>
-  <si>
-    <t>000660</t>
-  </si>
-  <si>
-    <t>CHKP</t>
+    <t>DKNG</t>
   </si>
   <si>
     <t>RBLX</t>
   </si>
   <si>
-    <t>RRX</t>
-  </si>
-  <si>
-    <t>LION</t>
+    <t>ACCENTURE CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>AUTODESK ORD (NMS)</t>
   </si>
   <si>
     <t>CANON ORD (TYO) CFD</t>
   </si>
   <si>
+    <t>GE VERNOVA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>APPLE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>EQUIFAX ORD (NYS)</t>
+  </si>
+  <si>
+    <t>HEALTHEQUITY ORD (NMS)</t>
+  </si>
+  <si>
     <t>FAIR ISAAC ORD (NYS)</t>
   </si>
   <si>
-    <t>HEALTHEQUITY ORD (NMS)</t>
+    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
+  </si>
+  <si>
+    <t>EXPEDIA GROUP ORD (NMS)</t>
+  </si>
+  <si>
+    <t>LOGITECH N ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WILLIAMS SONOMA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
+  </si>
+  <si>
+    <t>SERVICENOW ORD (NYS)</t>
+  </si>
+  <si>
+    <t>VERISK ANALYTICS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SANRIO ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>GARMIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ARAMARK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ATLASSIAN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GARTNER ORD (NYS)</t>
+  </si>
+  <si>
+    <t>REA GROUP ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>SPOT US 01/21/28 C700 OTC (SPOT 1/21/28 C700 OTC)</t>
+  </si>
+  <si>
+    <t>BEST BUY ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ADOBE ORD (NMS)</t>
   </si>
   <si>
     <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
   </si>
   <si>
-    <t>APPLE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>AUTODESK ORD (NMS)</t>
-  </si>
-  <si>
-    <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
-  </si>
-  <si>
-    <t>SERVICENOW ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EQUIFAX ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
-  </si>
-  <si>
-    <t>GE VERNOVA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ARAMARK ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SALESFORCE ORD (NYS)</t>
-  </si>
-  <si>
-    <t>WILLIAMS SONOMA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EXPEDIA GROUP ORD (NMS)</t>
-  </si>
-  <si>
-    <t>VERISK ANALYTICS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GARMIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SANRIO ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>LOGITECH N ORD (NMS)</t>
-  </si>
-  <si>
-    <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ATLASSIAN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GARTNER ORD (NYS)</t>
-  </si>
-  <si>
-    <t>PINTEREST CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>REA GROUP ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
+    <t>ARISTA NETWORKS ORD (NYS)</t>
   </si>
   <si>
     <t>SAMSARA CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>ADOBE ORD (NMS)</t>
+    <t>DUOLINGO CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SEAGATE TECHNOLOGY HOLDINGS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>NEW YORK TIMES CL A ORD (NYS)</t>
   </si>
   <si>
     <t>COINBASE GLOBAL CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>ARISTA NETWORKS ORD (NYS)</t>
-  </si>
-  <si>
     <t>EBAY ORD (NMS)</t>
   </si>
   <si>
-    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
+    <t>RINGCENTRAL CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SYNCHRONY FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>COVISTA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
   </si>
   <si>
     <t>ROBERT HALF ORD (NYS)</t>
   </si>
   <si>
-    <t>DUOLINGO CL A ORD (NMS)</t>
+    <t>ASTERA LABS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SERVICETITAN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GENERAL MOTORS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>BREAD FINANCIAL HOLDINGS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TRANE TECHNOLOGIES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>POWELL INDUSTRIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>WESTERN DIGITAL ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CIENA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>QUALYS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>H&amp;R BLOCK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FORD MOTOR ORD (NYS)</t>
+  </si>
+  <si>
+    <t>COMFORT SYSTEMS USA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FACTSET RESEARCH SYSTEMS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ELBIT SYSTEMS ORD (NMS)</t>
   </si>
   <si>
     <t>CARGURUS CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>GRAND CANYON EDUCATION ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ASTERA LABS ORD (NMS)</t>
+    <t>SEZZLE INC (NMS)</t>
+  </si>
+  <si>
+    <t>SOMNIGROUP INTERNATIONAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SYMBOTIC CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CHIME FINANCIAL CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>COREWEAVE CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
+    <t>SLM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CONCENTRIX ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DAVE CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>HUT 8 ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
   </si>
   <si>
     <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
   </si>
   <si>
-    <t>SYMBOTIC CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>BEST BUY ORD (NYS)</t>
-  </si>
-  <si>
-    <t>CORNING ORD (NYS)</t>
-  </si>
-  <si>
-    <t>META US 01/15/27 C720 OTC (META 1/15/27 C720 OTC)</t>
-  </si>
-  <si>
-    <t>CIENA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>QUALYS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SERVICETITAN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CHIME FINANCIAL CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
-  </si>
-  <si>
-    <t>H&amp;R BLOCK ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SLM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SEZZLE INC (NMS)</t>
-  </si>
-  <si>
-    <t>COREWEAVE CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
-    <t>CONCENTRIX ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DAVE CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>OPENDOOR TECHNOLOGIES ORD (NMS)</t>
+    <t>NEBIUS CL A ORD (NMS)</t>
   </si>
   <si>
     <t>BLOCK CL A ORD (NYS)</t>
@@ -556,97 +645,106 @@
     <t>WAYFAIR CL A ORD (NYS)</t>
   </si>
   <si>
+    <t>EATON ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TESLA ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SPOTIFY TECHNOLOGY ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GLOBAL E ONLINE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ALPHABET CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>LYFT CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>AUTO1 GROUP ORD (GER)</t>
+  </si>
+  <si>
+    <t>SHOPIFY CL A SUB VTG ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
+  </si>
+  <si>
     <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
   </si>
   <si>
-    <t>EATON ORD (NYS)</t>
-  </si>
-  <si>
-    <t>LYFT CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>AUTO1 GROUP ORD (GER)</t>
-  </si>
-  <si>
-    <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>ALPHABET CL A ORD (NMS)</t>
+    <t>AMAZON COM ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SAP ORD (GER)</t>
+  </si>
+  <si>
+    <t>PROCORE TECHNOLOGIES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
+  </si>
+  <si>
+    <t>DOXIMITY CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ADVANTEST ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>MAPLEBEAR ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ZILLOW GROUP CL C ORD (NMS)</t>
   </si>
   <si>
     <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>GLOBAL E ONLINE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>PROCORE TECHNOLOGIES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>APPLOVIN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>AMAZON COM ORD (NMS)</t>
+    <t>FERRARI ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (MIL)</t>
+  </si>
+  <si>
+    <t>DOORDASH CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>UBER TECHNOLOGIES INC. (NYS)</t>
+  </si>
+  <si>
+    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>REGAL REXNORD ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SUMITOMO ELEC ORD (TYO) 5802 JP CFD JPY EQSW 20360101</t>
+  </si>
+  <si>
+    <t>APPLIED MATERIAL ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TERADYNE ORD (NMS)</t>
   </si>
   <si>
     <t>HEWLETT PACKARD ENTERPRISE ORD (NYS)</t>
   </si>
   <si>
-    <t>TESLA ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SAP ORD (GER)</t>
-  </si>
-  <si>
-    <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ZILLOW GROUP CL C ORD (NMS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (MIL)</t>
-  </si>
-  <si>
-    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>APPLIED MATERIAL ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ADVANTEST ORD (TYO) CFD</t>
-  </si>
-  <si>
     <t>AECOM ORD (NYS)</t>
   </si>
   <si>
-    <t>MAPLEBEAR ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TERADYNE ORD (NMS)</t>
-  </si>
-  <si>
-    <t>STMICROELECTRONICS ADR (NYS)</t>
-  </si>
-  <si>
-    <t>SK HYNIX ORD (KSC) CFD_USD</t>
-  </si>
-  <si>
-    <t>CHECK POINT SOFTWARE TECHNOLOGIS ORD (NMS)</t>
+    <t>DRAFTKINGS CL A ORD (NMS)</t>
   </si>
   <si>
     <t>ROBLOX CL A ORD (NYS)</t>
   </si>
   <si>
-    <t>META US 01/15/27 P620 OTC (META 1/15/27 P620 OTC)</t>
-  </si>
-  <si>
-    <t>REGAL REXNORD ORD (NYS)</t>
+    <t>SPOT US 01/21/28 P450 OTC (SPOT 1/21/28 P450 OTC)</t>
   </si>
   <si>
     <t>LIONSGATE STUDIOS ORD (NYS)</t>
@@ -656,19 +754,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -709,13 +801,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249970003962517"/>
+        <fgColor theme="0" tint="-0.24994659260841701"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499799996614456"/>
+        <fgColor theme="0" tint="-4.9958800012207406E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -739,6 +831,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -749,6 +842,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -761,6 +855,7 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -771,6 +866,7 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -779,6 +875,7 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -789,6 +886,7 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -797,6 +895,7 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -805,6 +904,7 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -813,40 +913,19 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment/>
-      <protection/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
@@ -855,96 +934,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -957,9 +964,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -997,7 +1004,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1103,7 +1110,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1245,49 +1252,48 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D6D00E-F3A7-4FD6-86F3-70A35F8FFA0A}">
-  <dimension ref="A1:Q199"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D6D00E-F3A7-4FD6-86F3-70A35F8FFA0A}">
+  <dimension ref="A1:Q212"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7142857142857" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7142857142857" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7142857142857" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="15.7142857142857" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7142857142857" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="15.7142857142857" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.75">
+    <row r="1" spans="1:17" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15"/>
-    <row r="6" spans="1:17" ht="15">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1304,12 +1310,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:17" ht="15.75" thickBot="1"/>
-    <row r="9" spans="1:17" ht="15.75" thickBot="1">
+    <row r="8" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>1</v>
       </c>
@@ -1347,7 +1353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1363,26 +1369,26 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="8"/>
     </row>
-    <row r="11" spans="1:17" ht="15">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C11" s="10">
-        <v>10.032656621227209</v>
+        <v>10.75290592062041</v>
       </c>
       <c r="D11" s="10">
-        <f>IF(B11="","",(C11/100))</f>
-        <v>0.10032656621227209</v>
+        <f t="shared" ref="D11:D47" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10752905920620411</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="10">
-        <v>-5.1704988081845586</v>
+        <v>-5.9934308634348037</v>
       </c>
       <c r="H11" s="12">
-        <f>IF(F11="","",G11/100)</f>
-        <v>-0.051704988081845586</v>
+        <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
+        <v>-5.9934308634348038E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -1401,26 +1407,26 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C12" s="10">
-        <v>6.5645846909600483</v>
+        <v>7.4692394833383151</v>
       </c>
       <c r="D12" s="10">
-        <f>IF(B12="","",(C12/100))</f>
-        <v>0.065645846909600486</v>
+        <f t="shared" si="0"/>
+        <v>7.4692394833383149E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="10">
-        <v>-4.5072716016839154</v>
+        <v>-5.1837847861408672</v>
       </c>
       <c r="H12" s="12">
-        <f>IF(F12="","",G12/100)</f>
-        <v>-0.045072716016839154</v>
+        <f t="shared" si="1"/>
+        <v>-5.1837847861408673E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -1429,1607 +1435,1782 @@
       <c r="P12" s="11"/>
       <c r="Q12" s="13"/>
     </row>
-    <row r="13" spans="1:17" ht="15">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C13" s="10">
-        <v>4.9922384134675024</v>
+        <v>5.5324314060717423</v>
       </c>
       <c r="D13" s="10">
-        <f>IF(B13="","",(C13/100))</f>
-        <v>0.049922384134675021</v>
+        <f t="shared" si="0"/>
+        <v>5.5324314060717424E-2</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="10">
-        <v>-3.8342330644920741</v>
+        <v>-4.4904464480105091</v>
       </c>
       <c r="H13" s="12">
-        <f>IF(F13="","",G13/100)</f>
-        <v>-0.038342330644920743</v>
+        <f t="shared" si="1"/>
+        <v>-4.4904464480105093E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="15">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C14" s="10">
-        <v>4.7916088472466889</v>
+        <v>5.4798915119943992</v>
       </c>
       <c r="D14" s="10">
-        <f>IF(B14="","",(C14/100))</f>
-        <v>0.047916088472466888</v>
+        <f t="shared" si="0"/>
+        <v>5.4798915119943989E-2</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="10">
-        <v>-3.432968433269576</v>
+        <v>-4.4006869587325159</v>
       </c>
       <c r="H14" s="12">
-        <f>IF(F14="","",G14/100)</f>
-        <v>-0.034329684332695759</v>
+        <f t="shared" si="1"/>
+        <v>-4.4006869587325158E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:17" ht="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C15" s="10">
-        <v>4.4429121029125751</v>
+        <v>4.4256917874129238</v>
       </c>
       <c r="D15" s="10">
-        <f>IF(B15="","",(C15/100))</f>
-        <v>0.044429121029125752</v>
+        <f t="shared" si="0"/>
+        <v>4.4256917874129241E-2</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="10">
-        <v>-3.4186706210816249</v>
+        <v>-4.2768448521035598</v>
       </c>
       <c r="H15" s="12">
-        <f>IF(F15="","",G15/100)</f>
-        <v>-0.034186706210816251</v>
+        <f t="shared" si="1"/>
+        <v>-4.2768448521035597E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="2:9" ht="15">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C16" s="10">
-        <v>4.288895898514375</v>
+        <v>4.0114585996489325</v>
       </c>
       <c r="D16" s="10">
-        <f>IF(B16="","",(C16/100))</f>
-        <v>0.042888958985143749</v>
+        <f t="shared" si="0"/>
+        <v>4.0114585996489323E-2</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.3953542191112787</v>
+        <v>-4.2758220209296685</v>
       </c>
       <c r="H16" s="12">
-        <f>IF(F16="","",G16/100)</f>
-        <v>-0.033953542191112789</v>
+        <f t="shared" si="1"/>
+        <v>-4.2758220209296684E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="2:8" ht="15">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C17" s="10">
-        <v>3.8064092987500033</v>
+        <v>3.9764142686120283</v>
       </c>
       <c r="D17" s="10">
-        <f>IF(B17="","",(C17/100))</f>
-        <v>0.038064092987500034</v>
+        <f t="shared" si="0"/>
+        <v>3.9764142686120281E-2</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.3205937108620782</v>
+        <v>-3.8146942577688012</v>
       </c>
       <c r="H17" s="12">
-        <f>IF(F17="","",G17/100)</f>
-        <v>-0.033205937108620784</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.8146942577688012E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C18" s="10">
-        <v>3.7435246533950188</v>
+        <v>3.9389470657314019</v>
       </c>
       <c r="D18" s="10">
-        <f>IF(B18="","",(C18/100))</f>
-        <v>0.037435246533950188</v>
+        <f t="shared" si="0"/>
+        <v>3.9389470657314019E-2</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.305152152253104</v>
+        <v>-3.7592318427414506</v>
       </c>
       <c r="H18" s="12">
-        <f>IF(F18="","",G18/100)</f>
-        <v>-0.03305152152253104</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.7592318427414506E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="C19" s="10">
-        <v>3.0688986018070477</v>
+        <v>3.7697534312823535</v>
       </c>
       <c r="D19" s="10">
-        <f>IF(B19="","",(C19/100))</f>
-        <v>0.030688986018070477</v>
+        <f t="shared" si="0"/>
+        <v>3.7697534312823536E-2</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.1295440683041695</v>
+        <v>-3.6320376874597859</v>
       </c>
       <c r="H19" s="12">
-        <f>IF(F19="","",G19/100)</f>
-        <v>-0.031295440683041693</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.6320376874597861E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C20" s="10">
-        <v>2.974535595805587</v>
+        <v>3.7290016734757856</v>
       </c>
       <c r="D20" s="10">
-        <f>IF(B20="","",(C20/100))</f>
-        <v>0.029745355958055872</v>
+        <f t="shared" si="0"/>
+        <v>3.7290016734757854E-2</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="10">
-        <v>-2.8489805574986744</v>
+        <v>-3.5311836688318596</v>
       </c>
       <c r="H20" s="12">
-        <f>IF(F20="","",G20/100)</f>
-        <v>-0.028489805574986746</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.5311836688318596E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C21" s="10">
-        <v>2.6597141564846702</v>
+        <v>2.9431557514540136</v>
       </c>
       <c r="D21" s="10">
-        <f>IF(B21="","",(C21/100))</f>
-        <v>0.026597141564846702</v>
+        <f t="shared" si="0"/>
+        <v>2.9431557514540137E-2</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.8465368730952396</v>
+        <v>-3.2721487094228197</v>
       </c>
       <c r="H21" s="12">
-        <f>IF(F21="","",G21/100)</f>
-        <v>-0.028465368730952397</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.2721487094228195E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C22" s="10">
-        <v>2.534463384052581</v>
+        <v>2.8545808131970469</v>
       </c>
       <c r="D22" s="10">
-        <f>IF(B22="","",(C22/100))</f>
-        <v>0.025344633840525811</v>
+        <f t="shared" si="0"/>
+        <v>2.8545808131970468E-2</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.7632198690417806</v>
+        <v>-2.7413886334777815</v>
       </c>
       <c r="H22" s="12">
-        <f>IF(F22="","",G22/100)</f>
-        <v>-0.027632198690417806</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.7413886334777815E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C23" s="10">
-        <v>2.5274959704581641</v>
+        <v>2.7819275358197402</v>
       </c>
       <c r="D23" s="10">
-        <f>IF(B23="","",(C23/100))</f>
-        <v>0.025274959704581643</v>
+        <f t="shared" si="0"/>
+        <v>2.7819275358197403E-2</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.5298056841944709</v>
+        <v>-2.7170502309773621</v>
       </c>
       <c r="H23" s="12">
-        <f>IF(F23="","",G23/100)</f>
-        <v>-0.025298056841944708</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.7170502309773623E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C24" s="10">
-        <v>2.4518662620613929</v>
+        <v>2.5907317747027272</v>
       </c>
       <c r="D24" s="10">
-        <f>IF(B24="","",(C24/100))</f>
-        <v>0.024518662620613928</v>
+        <f t="shared" si="0"/>
+        <v>2.5907317747027273E-2</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.454110615658279</v>
+        <v>-2.6765686262803565</v>
       </c>
       <c r="H24" s="12">
-        <f>IF(F24="","",G24/100)</f>
-        <v>-0.024541106156582792</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.6765686262803564E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C25" s="10">
-        <v>2.327973295734207</v>
+        <v>2.5707776652134351</v>
       </c>
       <c r="D25" s="10">
-        <f>IF(B25="","",(C25/100))</f>
-        <v>0.023279732957342071</v>
+        <f t="shared" si="0"/>
+        <v>2.5707776652134352E-2</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.2702908225579899</v>
+        <v>-2.4387673018160689</v>
       </c>
       <c r="H25" s="12">
-        <f>IF(F25="","",G25/100)</f>
-        <v>-0.022702908225579899</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.438767301816069E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C26" s="10">
-        <v>2.2621840484749103</v>
+        <v>2.5144788409927368</v>
       </c>
       <c r="D26" s="10">
-        <f>IF(B26="","",(C26/100))</f>
-        <v>0.022621840484749103</v>
+        <f t="shared" si="0"/>
+        <v>2.5144788409927368E-2</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.2192043988824128</v>
+        <v>-2.4110763049710839</v>
       </c>
       <c r="H26" s="12">
-        <f>IF(F26="","",G26/100)</f>
-        <v>-0.022192043988824128</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.411076304971084E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C27" s="10">
-        <v>2.218799976641737</v>
+        <v>2.3721711358365862</v>
       </c>
       <c r="D27" s="10">
-        <f>IF(B27="","",(C27/100))</f>
-        <v>0.02218799976641737</v>
+        <f t="shared" si="0"/>
+        <v>2.3721711358365861E-2</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.2125510049526969</v>
+        <v>-2.40224469153938</v>
       </c>
       <c r="H27" s="12">
-        <f>IF(F27="","",G27/100)</f>
-        <v>-0.022125510049526967</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.4022446915393802E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C28" s="10">
-        <v>2.0979262992440884</v>
+        <v>2.2786355668412965</v>
       </c>
       <c r="D28" s="10">
-        <f>IF(B28="","",(C28/100))</f>
-        <v>0.020979262992440885</v>
+        <f t="shared" si="0"/>
+        <v>2.2786355668412965E-2</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>34</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.1734866837248878</v>
+        <v>-2.3746831600873963</v>
       </c>
       <c r="H28" s="12">
-        <f>IF(F28="","",G28/100)</f>
-        <v>-0.02173486683724888</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.3746831600873965E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C29" s="10">
-        <v>1.9968619267310121</v>
+        <v>2.1812497213005262</v>
       </c>
       <c r="D29" s="10">
-        <f>IF(B29="","",(C29/100))</f>
-        <v>0.019968619267310122</v>
+        <f t="shared" si="0"/>
+        <v>2.1812497213005263E-2</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.1534764237528137</v>
+        <v>-2.3697468997632218</v>
       </c>
       <c r="H29" s="12">
-        <f>IF(F29="","",G29/100)</f>
-        <v>-0.021534764237528137</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.3697468997632219E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C30" s="10">
-        <v>1.986472098938951</v>
+        <v>2.1265592043345598</v>
       </c>
       <c r="D30" s="10">
-        <f>IF(B30="","",(C30/100))</f>
-        <v>0.01986472098938951</v>
+        <f t="shared" si="0"/>
+        <v>2.1265592043345598E-2</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.1391396618670315</v>
+        <v>-2.34329223603106</v>
       </c>
       <c r="H30" s="12">
-        <f>IF(F30="","",G30/100)</f>
-        <v>-0.021391396618670316</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.3432922360310599E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="C31" s="10">
-        <v>1.9679910923984449</v>
+        <v>2.1027171598591958</v>
       </c>
       <c r="D31" s="10">
-        <f>IF(B31="","",(C31/100))</f>
-        <v>0.01967991092398445</v>
+        <f t="shared" si="0"/>
+        <v>2.1027171598591958E-2</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0454718574419917</v>
+        <v>-2.2876371235668143</v>
       </c>
       <c r="H31" s="12">
-        <f>IF(F31="","",G31/100)</f>
-        <v>-0.020454718574419918</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.2876371235668144E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C32" s="10">
-        <v>1.9307280114811938</v>
+        <v>2.0498538751452804</v>
       </c>
       <c r="D32" s="10">
-        <f>IF(B32="","",(C32/100))</f>
-        <v>0.019307280114811937</v>
+        <f t="shared" si="0"/>
+        <v>2.0498538751452803E-2</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.033411263528131</v>
+        <v>-2.2863701634985345</v>
       </c>
       <c r="H32" s="12">
-        <f>IF(F32="","",G32/100)</f>
-        <v>-0.020334112635281308</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.2863701634985346E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C33" s="10">
-        <v>1.6640148823011673</v>
+        <v>2.0311422378021988</v>
       </c>
       <c r="D33" s="10">
-        <f>IF(B33="","",(C33/100))</f>
-        <v>0.016640148823011673</v>
+        <f t="shared" si="0"/>
+        <v>2.0311422378021988E-2</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9741664165062998</v>
+        <v>-2.0171062929217198</v>
       </c>
       <c r="H33" s="12">
-        <f>IF(F33="","",G33/100)</f>
-        <v>-0.019741664165062997</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.01710629292172E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C34" s="10">
-        <v>1.5499138700087787</v>
+        <v>2.0118308168971288</v>
       </c>
       <c r="D34" s="10">
-        <f>IF(B34="","",(C34/100))</f>
-        <v>0.015499138700087787</v>
+        <f t="shared" si="0"/>
+        <v>2.011830816897129E-2</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.929297673838144</v>
+        <v>-2.0085239924570435</v>
       </c>
       <c r="H34" s="12">
-        <f>IF(F34="","",G34/100)</f>
-        <v>-0.019292976738381439</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.0085239924570435E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C35" s="10">
-        <v>1.5162825406658633</v>
+        <v>1.9939764614609139</v>
       </c>
       <c r="D35" s="10">
-        <f>IF(B35="","",(C35/100))</f>
-        <v>0.015162825406658633</v>
+        <f t="shared" si="0"/>
+        <v>1.993976461460914E-2</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.6379702994790253</v>
+        <v>-1.8660124031809358</v>
       </c>
       <c r="H35" s="12">
-        <f>IF(F35="","",G35/100)</f>
-        <v>-0.016379702994790253</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.8660124031809357E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C36" s="10">
-        <v>1.4198630546469748</v>
+        <v>1.9810263751637747</v>
       </c>
       <c r="D36" s="10">
-        <f>IF(B36="","",(C36/100))</f>
-        <v>0.014198630546469748</v>
+        <f t="shared" si="0"/>
+        <v>1.9810263751637747E-2</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.5474968939695712</v>
+        <v>-1.8481858780294125</v>
       </c>
       <c r="H36" s="12">
-        <f>IF(F36="","",G36/100)</f>
-        <v>-0.015474968939695712</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.8481858780294125E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C37" s="10">
-        <v>1.3616945285188287</v>
+        <v>1.7804097216213104</v>
       </c>
       <c r="D37" s="10">
-        <f>IF(B37="","",(C37/100))</f>
-        <v>0.013616945285188286</v>
+        <f t="shared" si="0"/>
+        <v>1.7804097216213104E-2</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.5376735183298007</v>
+        <v>-1.740215150840926</v>
       </c>
       <c r="H37" s="12">
-        <f>IF(F37="","",G37/100)</f>
-        <v>-0.015376735183298008</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.740215150840926E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C38" s="10">
-        <v>1.3511011926338614</v>
+        <v>1.7584797301304107</v>
       </c>
       <c r="D38" s="10">
-        <f>IF(B38="","",(C38/100))</f>
-        <v>0.013511011926338613</v>
+        <f t="shared" si="0"/>
+        <v>1.7584797301304106E-2</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>44</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.5215067098010393</v>
+        <v>-1.662796755748001</v>
       </c>
       <c r="H38" s="12">
-        <f>IF(F38="","",G38/100)</f>
-        <v>-0.015215067098010394</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.6627967557480011E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C39" s="10">
-        <v>1.3056266021448164</v>
+        <v>1.7139454766481832</v>
       </c>
       <c r="D39" s="10">
-        <f>IF(B39="","",(C39/100))</f>
-        <v>0.013056266021448165</v>
+        <f t="shared" si="0"/>
+        <v>1.7139454766481831E-2</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.4898873451015626</v>
+        <v>-1.5345054187769702</v>
       </c>
       <c r="H39" s="12">
-        <f>IF(F39="","",G39/100)</f>
-        <v>-0.014898873451015626</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.5345054187769703E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C40" s="10">
-        <v>1.0144456000955313</v>
+        <v>1.7088300247605672</v>
       </c>
       <c r="D40" s="10">
-        <f>IF(B40="","",(C40/100))</f>
-        <v>0.010144456000955314</v>
+        <f t="shared" si="0"/>
+        <v>1.7088300247605673E-2</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.2536474121179391</v>
+        <v>-1.4991249415563426</v>
       </c>
       <c r="H40" s="12">
-        <f>IF(F40="","",G40/100)</f>
-        <v>-0.01253647412117939</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.4991249415563426E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C41" s="10">
-        <v>0.62192586338377553</v>
+        <v>1.5899809986203635</v>
       </c>
       <c r="D41" s="10">
-        <f>IF(B41="","",(C41/100))</f>
-        <v>0.0062192586338377549</v>
+        <f t="shared" si="0"/>
+        <v>1.5899809986203634E-2</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.1839464368861896</v>
+        <v>-1.4710904316875686</v>
       </c>
       <c r="H41" s="12">
-        <f>IF(F41="","",G41/100)</f>
-        <v>-0.011839464368861897</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.4710904316875686E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C42" s="10">
-        <v>0.46883194855321542</v>
+        <v>1.4257662892427765</v>
       </c>
       <c r="D42" s="10">
-        <f>IF(B42="","",(C42/100))</f>
-        <v>0.0046883194855321542</v>
+        <f t="shared" si="0"/>
+        <v>1.4257662892427764E-2</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.1038327999980688</v>
+        <v>-1.3891977726386431</v>
       </c>
       <c r="H42" s="12">
-        <f>IF(F42="","",G42/100)</f>
-        <v>-0.011038327999980689</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.389197772638643E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C43" s="10">
-        <v>0.43950969956230901</v>
+        <v>1.4204945648496996</v>
       </c>
       <c r="D43" s="10">
-        <f>IF(B43="","",(C43/100))</f>
-        <v>0.0043950969956230903</v>
+        <f t="shared" si="0"/>
+        <v>1.4204945648496996E-2</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.0732978734402292</v>
+        <v>-1.3581861044227097</v>
       </c>
       <c r="H43" s="12">
-        <f>IF(F43="","",G43/100)</f>
-        <v>-0.010732978734402291</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="15">
+        <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
+        <v>-1.3581861044227097E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C44" s="10">
-        <v>0.38619037808332551</v>
+        <v>1.4013027868842094</v>
       </c>
       <c r="D44" s="10">
-        <f>IF(B44="","",(C44/100))</f>
-        <v>0.0038619037808332551</v>
+        <f t="shared" si="0"/>
+        <v>1.4013027868842095E-2</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.0505283383197708</v>
+        <v>-1.2929764732396047</v>
       </c>
       <c r="H44" s="12">
-        <f>IF(F44="","",G44/100)</f>
-        <v>-0.010505283383197707</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.2929764732396048E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="C45" s="10">
-        <v>0.14305569396678564</v>
+        <v>1.0838954568849919</v>
       </c>
       <c r="D45" s="10">
-        <f>IF(B45="","",(C45/100))</f>
-        <v>0.0014305569396678563</v>
+        <f t="shared" si="0"/>
+        <v>1.0838954568849918E-2</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.0233135625590861</v>
+        <v>-1.2784004980554449</v>
       </c>
       <c r="H45" s="12">
-        <f>IF(F45="","",G45/100)</f>
-        <v>-0.010233135625590861</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="15">
-      <c r="B46" s="9"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
+        <f t="shared" si="2"/>
+        <v>-1.2784004980554448E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="10">
+        <v>0.54126152093270297</v>
+      </c>
+      <c r="D46" s="10">
+        <f t="shared" si="0"/>
+        <v>5.4126152093270296E-3</v>
+      </c>
       <c r="F46" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.0124649915953887</v>
+        <v>-1.2741244566663887</v>
       </c>
       <c r="H46" s="12">
-        <f>IF(F46="","",G46/100)</f>
-        <v>-0.010124649915953887</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.2741244566663888E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.51245997294786305</v>
+      </c>
+      <c r="D47" s="10">
+        <f t="shared" si="0"/>
+        <v>5.1245997294786308E-3</v>
+      </c>
       <c r="F47" s="11" t="s">
         <v>53</v>
       </c>
       <c r="G47" s="10">
-        <v>-0.98365098706492349</v>
+        <v>-1.238086147912516</v>
       </c>
       <c r="H47" s="12">
-        <f>IF(F47="","",G47/100)</f>
-        <v>-0.0098365098706492352</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.238086147912516E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="9"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
       <c r="F48" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G48" s="10">
-        <v>-0.94381664013024091</v>
+        <v>-1.232329098824392</v>
       </c>
       <c r="H48" s="12">
-        <f>IF(F48="","",G48/100)</f>
-        <v>-0.0094381664013024093</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.232329098824392E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F49" s="11" t="s">
         <v>55</v>
       </c>
       <c r="G49" s="10">
-        <v>-0.926678118467684</v>
+        <v>-1.163752003193627</v>
       </c>
       <c r="H49" s="12">
-        <f>IF(F49="","",G49/100)</f>
-        <v>-0.0092667811846768398</v>
-      </c>
-    </row>
-    <row r="50" spans="6:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.163752003193627E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F50" s="11" t="s">
         <v>56</v>
       </c>
       <c r="G50" s="10">
-        <v>-0.84580676266797039</v>
+        <v>-1.1222439521141796</v>
       </c>
       <c r="H50" s="12">
-        <f>IF(F50="","",G50/100)</f>
-        <v>-0.0084580676266797043</v>
-      </c>
-    </row>
-    <row r="51" spans="4:8" ht="15">
-      <c r="D51" s="1"/>
+        <f t="shared" si="2"/>
+        <v>-1.1222439521141795E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F51" s="11" t="s">
         <v>57</v>
       </c>
       <c r="G51" s="10">
-        <v>-0.78224890759350829</v>
+        <v>-1.1188912213466502</v>
       </c>
       <c r="H51" s="12">
-        <f>IF(F51="","",G51/100)</f>
-        <v>-0.0078224890759350831</v>
-      </c>
-    </row>
-    <row r="52" spans="4:8" ht="15">
-      <c r="D52" s="1"/>
+        <f t="shared" si="2"/>
+        <v>-1.1188912213466502E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="4:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
         <v>58</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.77747557302802051</v>
+        <v>-1.0025669067929244</v>
       </c>
       <c r="H52" s="12">
-        <f>IF(F52="","",G52/100)</f>
-        <v>-0.0077747557302802047</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.0025669067929243E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D53" s="1"/>
       <c r="F53" s="11" t="s">
         <v>59</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.75649150514848595</v>
+        <v>-0.98530667336568545</v>
       </c>
       <c r="H53" s="12">
-        <f>IF(F53="","",G53/100)</f>
-        <v>-0.00756491505148486</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-9.8530667336568546E-3</v>
+      </c>
+    </row>
+    <row r="54" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D54" s="1"/>
       <c r="F54" s="11" t="s">
         <v>60</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.71720860738108261</v>
+        <v>-0.94970027971638638</v>
       </c>
       <c r="H54" s="12">
-        <f>IF(F54="","",G54/100)</f>
-        <v>-0.0071720860738108258</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-9.4970027971638636E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
         <v>61</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.65754618032149303</v>
+        <v>-0.94896359570984901</v>
       </c>
       <c r="H55" s="12">
-        <f>IF(F55="","",G55/100)</f>
-        <v>-0.0065754618032149307</v>
-      </c>
-    </row>
-    <row r="56" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-9.4896359570984905E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
         <v>62</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.62313755902555368</v>
+        <v>-0.85141844786647047</v>
       </c>
       <c r="H56" s="12">
-        <f>IF(F56="","",G56/100)</f>
-        <v>-0.0062313755902555371</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-8.5141844786647044E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
         <v>63</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.59141221187096971</v>
+        <v>-0.81507946289955924</v>
       </c>
       <c r="H57" s="12">
-        <f>IF(F57="","",G57/100)</f>
-        <v>-0.0059141221187096974</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-8.1507946289955929E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
         <v>64</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.55113135083728282</v>
+        <v>-0.79425954506813967</v>
       </c>
       <c r="H58" s="12">
-        <f>IF(F58="","",G58/100)</f>
-        <v>-0.0055113135083728285</v>
-      </c>
-    </row>
-    <row r="59" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-7.9425954506813969E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
         <v>65</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.53187612584804311</v>
+        <v>-0.77839123514436381</v>
       </c>
       <c r="H59" s="12">
-        <f>IF(F59="","",G59/100)</f>
-        <v>-0.0053187612584804315</v>
-      </c>
-    </row>
-    <row r="60" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-7.7839123514436385E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.50047808707859631</v>
+        <v>-0.74874311445534492</v>
       </c>
       <c r="H60" s="12">
-        <f>IF(F60="","",G60/100)</f>
-        <v>-0.0050047808707859628</v>
-      </c>
-    </row>
-    <row r="61" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-7.4874311445534492E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
         <v>67</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.49314703386829195</v>
+        <v>-0.72710233964849313</v>
       </c>
       <c r="H61" s="12">
-        <f>IF(F61="","",G61/100)</f>
-        <v>-0.0049314703386829197</v>
-      </c>
-    </row>
-    <row r="62" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-7.2710233964849314E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
         <v>68</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.46170906347585844</v>
+        <v>-0.69924954516799831</v>
       </c>
       <c r="H62" s="12">
-        <f>IF(F62="","",G62/100)</f>
-        <v>-0.0046170906347585841</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.992495451679983E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
         <v>69</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.45695785495720603</v>
+        <v>-0.69769432337641968</v>
       </c>
       <c r="H63" s="12">
-        <f>IF(F63="","",G63/100)</f>
-        <v>-0.0045695785495720601</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.9769432337641966E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.45286715475976053</v>
+        <v>-0.69166169990066484</v>
       </c>
       <c r="H64" s="12">
-        <f>IF(F64="","",G64/100)</f>
-        <v>-0.004528671547597605</v>
-      </c>
-    </row>
-    <row r="65" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.9166169990066487E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
         <v>71</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.40637620627318749</v>
+        <v>-0.6899591413077788</v>
       </c>
       <c r="H65" s="12">
-        <f>IF(F65="","",G65/100)</f>
-        <v>-0.0040637620627318747</v>
-      </c>
-    </row>
-    <row r="66" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.8995914130777882E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.36077501290077152</v>
+        <v>-0.60217103207357514</v>
       </c>
       <c r="H66" s="12">
-        <f>IF(F66="","",G66/100)</f>
-        <v>-0.0036077501290077154</v>
-      </c>
-    </row>
-    <row r="67" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.0217103207357518E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
         <v>73</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.34724375695081222</v>
+        <v>-0.58918145132830757</v>
       </c>
       <c r="H67" s="12">
-        <f>IF(F67="","",G67/100)</f>
-        <v>-0.0034724375695081222</v>
-      </c>
-    </row>
-    <row r="68" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-5.8918145132830753E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
         <v>74</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.30292024459061806</v>
+        <v>-0.58261336771817163</v>
       </c>
       <c r="H68" s="12">
-        <f>IF(F68="","",G68/100)</f>
-        <v>-0.0030292024459061804</v>
-      </c>
-    </row>
-    <row r="69" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-5.8261336771817159E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
         <v>75</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.28449775759484458</v>
+        <v>-0.57868438634997299</v>
       </c>
       <c r="H69" s="12">
-        <f>IF(F69="","",G69/100)</f>
-        <v>-0.0028449775759484459</v>
-      </c>
-    </row>
-    <row r="70" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-5.7868438634997299E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
         <v>76</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.22294826677158472</v>
+        <v>-0.55286020134673897</v>
       </c>
       <c r="H70" s="12">
-        <f>IF(F70="","",G70/100)</f>
-        <v>-0.0022294826677158471</v>
-      </c>
-    </row>
-    <row r="71" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-5.52860201346739E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G71" s="10">
+        <v>-0.54892235248586918</v>
+      </c>
+      <c r="H71" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.4892235248586918E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D72" s="1"/>
+      <c r="F72" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-0.54509807574267388</v>
+      </c>
+      <c r="H72" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.4509807574267388E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D73" s="1"/>
+      <c r="F73" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="G73" s="10">
+        <v>-0.53861150485363163</v>
+      </c>
+      <c r="H73" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.3861150485363159E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D74" s="1"/>
+      <c r="F74" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-0.50531338775814905</v>
+      </c>
+      <c r="H74" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.0531338775814906E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D75" s="1"/>
+      <c r="F75" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-0.48493588959954442</v>
+      </c>
+      <c r="H75" s="12">
+        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
+        <v>-4.8493588959954443E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D76" s="1"/>
+      <c r="F76" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G76" s="10">
+        <v>-0.44717142107998376</v>
+      </c>
+      <c r="H76" s="12">
+        <f t="shared" si="3"/>
+        <v>-4.4717142107998376E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D77" s="1"/>
+      <c r="F77" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-0.43447780995549073</v>
+      </c>
+      <c r="H77" s="12">
+        <f t="shared" si="3"/>
+        <v>-4.3447780995549074E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D78" s="1"/>
+      <c r="F78" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-0.38811276029405428</v>
+      </c>
+      <c r="H78" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.8811276029405428E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D79" s="1"/>
+      <c r="F79" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="G79" s="10">
+        <v>-0.3726406908697204</v>
+      </c>
+      <c r="H79" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.7264069086972041E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D80" s="1"/>
+      <c r="F80" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G80" s="10">
+        <v>-0.34666303003179116</v>
+      </c>
+      <c r="H80" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.4666303003179117E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D81" s="1"/>
+      <c r="F81" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="G81" s="10">
+        <v>-0.34602859503690198</v>
+      </c>
+      <c r="H81" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.4602859503690196E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D82" s="1"/>
+      <c r="F82" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G82" s="10">
+        <v>-0.26711125262511992</v>
+      </c>
+      <c r="H82" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.6711125262511991E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D83" s="1"/>
+      <c r="F83" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G83" s="10">
+        <v>-0.24576392361420543</v>
+      </c>
+      <c r="H83" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.4576392361420544E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D84" s="1"/>
+      <c r="F84" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G71" s="10">
-        <v>-0.21228573789399938</v>
-      </c>
-      <c r="H71" s="12">
-        <f>IF(F71="","",G71/100)</f>
-        <v>-0.0021228573789399937</v>
-      </c>
-    </row>
-    <row r="72" spans="4:8" ht="15">
-      <c r="D72" s="1"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="13"/>
-    </row>
-    <row r="73" spans="4:8" ht="15">
-      <c r="D73" s="1"/>
-    </row>
-    <row r="74" spans="4:8" ht="15">
-      <c r="D74" s="1"/>
-    </row>
-    <row r="75" spans="4:8" ht="15">
-      <c r="D75" s="1"/>
-      <c r="G75" t="s">
+      <c r="G84" s="10">
+        <v>-0.20520428498169269</v>
+      </c>
+      <c r="H84" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.0520428498169269E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D85" s="1"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="13"/>
+    </row>
+    <row r="86" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D86" s="1"/>
+    </row>
+    <row r="87" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D87" s="1"/>
+    </row>
+    <row r="88" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D88" s="1"/>
+      <c r="G88" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="4:4" ht="15">
-      <c r="D76" s="1"/>
-    </row>
-    <row r="77" spans="4:8" ht="15">
-      <c r="D77" s="1"/>
-      <c r="H77" s="1"/>
-    </row>
-    <row r="78" spans="4:8" ht="15">
-      <c r="D78" s="1"/>
-      <c r="H78" s="1"/>
-    </row>
-    <row r="79" spans="4:8" ht="15">
-      <c r="D79" s="1"/>
-      <c r="H79" s="1"/>
-    </row>
-    <row r="80" spans="4:8" ht="15">
-      <c r="D80" s="1"/>
-      <c r="H80" s="1"/>
-    </row>
-    <row r="81" spans="4:8" ht="15">
-      <c r="D81" s="1"/>
-      <c r="H81" s="1"/>
-    </row>
-    <row r="82" spans="4:8" ht="15">
-      <c r="D82" s="1"/>
-      <c r="H82" s="1"/>
-    </row>
-    <row r="83" spans="4:8" ht="15">
-      <c r="D83" s="1"/>
-      <c r="H83" s="1"/>
-    </row>
-    <row r="84" spans="4:8" ht="15">
-      <c r="D84" s="1"/>
-      <c r="H84" s="1"/>
-    </row>
-    <row r="85" spans="4:8" ht="15">
-      <c r="D85" s="1"/>
-      <c r="H85" s="1"/>
-    </row>
-    <row r="86" spans="4:8" ht="15">
-      <c r="D86" s="1"/>
-      <c r="H86" s="1"/>
-    </row>
-    <row r="87" spans="4:8" ht="15">
-      <c r="D87" s="1"/>
-      <c r="H87" s="1"/>
-    </row>
-    <row r="88" spans="4:8" ht="15">
-      <c r="D88" s="1"/>
-      <c r="H88" s="1"/>
-    </row>
-    <row r="89" spans="4:8" ht="15">
+    <row r="89" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D89" s="1"/>
-      <c r="H89" s="1"/>
-    </row>
-    <row r="90" spans="4:8" ht="15">
+    </row>
+    <row r="90" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D90" s="1"/>
       <c r="H90" s="1"/>
     </row>
-    <row r="91" spans="4:8" ht="15">
+    <row r="91" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D91" s="1"/>
       <c r="H91" s="1"/>
     </row>
-    <row r="92" spans="4:8" ht="15">
+    <row r="92" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D92" s="1"/>
       <c r="H92" s="1"/>
     </row>
-    <row r="93" spans="4:8" ht="15">
+    <row r="93" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D93" s="1"/>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="4:8" ht="15">
+    <row r="94" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D94" s="1"/>
       <c r="H94" s="1"/>
     </row>
-    <row r="95" spans="4:8" ht="15">
+    <row r="95" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D95" s="1"/>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="4:8" ht="15">
+    <row r="96" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D96" s="1"/>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="4:8" ht="15">
+    <row r="97" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D97" s="1"/>
       <c r="H97" s="1"/>
     </row>
-    <row r="98" spans="4:8" ht="15">
+    <row r="98" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D98" s="1"/>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="4:8" ht="15">
+    <row r="99" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D99" s="1"/>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="4:8" ht="15">
+    <row r="100" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D100" s="1"/>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="4:8" ht="15">
+    <row r="101" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D101" s="1"/>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="4:8" ht="15">
+    <row r="102" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D102" s="1"/>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="4:8" ht="15">
+    <row r="103" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D103" s="1"/>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="4:8" ht="15">
+    <row r="104" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D104" s="1"/>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="4:8" ht="15">
+    <row r="105" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D105" s="1"/>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="4:8" ht="15">
+    <row r="106" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D106" s="1"/>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="4:8" ht="15">
+    <row r="107" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D107" s="1"/>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="4:8" ht="15">
+    <row r="108" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D108" s="1"/>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="4:8" ht="15">
+    <row r="109" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D109" s="1"/>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="4:8" ht="15">
+    <row r="110" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D110" s="1"/>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="4:8" ht="15">
+    <row r="111" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D111" s="1"/>
       <c r="H111" s="1"/>
     </row>
-    <row r="112" spans="4:8" ht="15">
+    <row r="112" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D112" s="1"/>
       <c r="H112" s="1"/>
     </row>
-    <row r="113" spans="4:8" ht="15">
+    <row r="113" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D113" s="1"/>
       <c r="H113" s="1"/>
     </row>
-    <row r="114" spans="4:8" ht="15">
+    <row r="114" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D114" s="1"/>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="4:8" ht="15">
+    <row r="115" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D115" s="1"/>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="4:8" ht="15">
+    <row r="116" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D116" s="1"/>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="4:8" ht="15">
+    <row r="117" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D117" s="1"/>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="4:8" ht="15">
+    <row r="118" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D118" s="1"/>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="4:8" ht="15">
+    <row r="119" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D119" s="1"/>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="4:8" ht="15">
+    <row r="120" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D120" s="1"/>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="4:8" ht="15">
+    <row r="121" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D121" s="1"/>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="4:8" ht="15">
+    <row r="122" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D122" s="1"/>
       <c r="H122" s="1"/>
     </row>
-    <row r="123" spans="4:8" ht="15">
+    <row r="123" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D123" s="1"/>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="4:8" ht="15">
+    <row r="124" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D124" s="1"/>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="4:8" ht="15">
+    <row r="125" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D125" s="1"/>
       <c r="H125" s="1"/>
     </row>
-    <row r="126" spans="4:8" ht="15">
+    <row r="126" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D126" s="1"/>
       <c r="H126" s="1"/>
     </row>
-    <row r="127" spans="4:8" ht="15">
+    <row r="127" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D127" s="1"/>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="4:8" ht="15">
+    <row r="128" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D128" s="1"/>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="4:8" ht="15">
+    <row r="129" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D129" s="1"/>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="4:8" ht="15">
+    <row r="130" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D130" s="1"/>
       <c r="H130" s="1"/>
     </row>
-    <row r="131" spans="4:8" ht="15">
+    <row r="131" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D131" s="1"/>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="4:8" ht="15">
+    <row r="132" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D132" s="1"/>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="4:8" ht="15">
+    <row r="133" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D133" s="1"/>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="4:8" ht="15">
+    <row r="134" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D134" s="1"/>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="4:8" ht="15">
+    <row r="135" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D135" s="1"/>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="4:8" ht="15">
+    <row r="136" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D136" s="1"/>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="4:8" ht="15">
+    <row r="137" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D137" s="1"/>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="4:8" ht="15">
+    <row r="138" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D138" s="1"/>
       <c r="H138" s="1"/>
     </row>
-    <row r="139" spans="4:8" ht="15">
+    <row r="139" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D139" s="1"/>
       <c r="H139" s="1"/>
     </row>
-    <row r="140" spans="4:8" ht="15">
+    <row r="140" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D140" s="1"/>
       <c r="H140" s="1"/>
     </row>
-    <row r="141" spans="4:8" ht="15">
+    <row r="141" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D141" s="1"/>
       <c r="H141" s="1"/>
     </row>
-    <row r="142" spans="4:8" ht="15">
+    <row r="142" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D142" s="1"/>
       <c r="H142" s="1"/>
     </row>
-    <row r="143" spans="4:8" ht="15">
+    <row r="143" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D143" s="1"/>
       <c r="H143" s="1"/>
     </row>
-    <row r="144" spans="4:8" ht="15">
+    <row r="144" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D144" s="1"/>
       <c r="H144" s="1"/>
     </row>
-    <row r="145" spans="4:8" ht="15">
+    <row r="145" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D145" s="1"/>
       <c r="H145" s="1"/>
     </row>
-    <row r="146" spans="4:8" ht="15">
+    <row r="146" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D146" s="1"/>
       <c r="H146" s="1"/>
     </row>
-    <row r="147" spans="4:8" ht="15">
+    <row r="147" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D147" s="1"/>
       <c r="H147" s="1"/>
     </row>
-    <row r="148" spans="4:8" ht="15">
+    <row r="148" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D148" s="1"/>
       <c r="H148" s="1"/>
     </row>
-    <row r="149" spans="4:8" ht="15">
+    <row r="149" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D149" s="1"/>
       <c r="H149" s="1"/>
     </row>
-    <row r="150" spans="4:8" ht="15">
+    <row r="150" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D150" s="1"/>
       <c r="H150" s="1"/>
     </row>
-    <row r="151" spans="4:8" ht="15">
+    <row r="151" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D151" s="1"/>
       <c r="H151" s="1"/>
     </row>
-    <row r="152" spans="4:8" ht="15">
+    <row r="152" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D152" s="1"/>
       <c r="H152" s="1"/>
     </row>
-    <row r="153" spans="4:8" ht="15">
+    <row r="153" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D153" s="1"/>
       <c r="H153" s="1"/>
     </row>
-    <row r="154" spans="4:8" ht="15">
+    <row r="154" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D154" s="1"/>
       <c r="H154" s="1"/>
     </row>
-    <row r="155" spans="4:8" ht="15">
+    <row r="155" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D155" s="1"/>
       <c r="H155" s="1"/>
     </row>
-    <row r="156" spans="4:8" ht="15">
+    <row r="156" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D156" s="1"/>
       <c r="H156" s="1"/>
     </row>
-    <row r="157" spans="4:8" ht="15">
+    <row r="157" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D157" s="1"/>
       <c r="H157" s="1"/>
     </row>
-    <row r="158" spans="4:8" ht="15">
+    <row r="158" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D158" s="1"/>
       <c r="H158" s="1"/>
     </row>
-    <row r="159" spans="4:8" ht="15">
+    <row r="159" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D159" s="1"/>
       <c r="H159" s="1"/>
     </row>
-    <row r="160" spans="4:8" ht="15">
+    <row r="160" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D160" s="1"/>
       <c r="H160" s="1"/>
     </row>
-    <row r="161" spans="4:8" ht="15">
+    <row r="161" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D161" s="1"/>
       <c r="H161" s="1"/>
     </row>
-    <row r="162" spans="4:8" ht="15">
+    <row r="162" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D162" s="1"/>
       <c r="H162" s="1"/>
     </row>
-    <row r="163" spans="4:8" ht="15">
+    <row r="163" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D163" s="1"/>
       <c r="H163" s="1"/>
     </row>
-    <row r="164" spans="4:8" ht="15">
+    <row r="164" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D164" s="1"/>
       <c r="H164" s="1"/>
     </row>
-    <row r="165" spans="4:8" ht="15">
+    <row r="165" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D165" s="1"/>
       <c r="H165" s="1"/>
     </row>
-    <row r="166" spans="4:8" ht="15">
+    <row r="166" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D166" s="1"/>
       <c r="H166" s="1"/>
     </row>
-    <row r="167" spans="4:8" ht="15">
+    <row r="167" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D167" s="1"/>
       <c r="H167" s="1"/>
     </row>
-    <row r="168" spans="4:8" ht="15">
+    <row r="168" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D168" s="1"/>
       <c r="H168" s="1"/>
     </row>
-    <row r="169" spans="4:8" ht="15">
+    <row r="169" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D169" s="1"/>
       <c r="H169" s="1"/>
     </row>
-    <row r="170" spans="4:8" ht="15">
+    <row r="170" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D170" s="1"/>
       <c r="H170" s="1"/>
     </row>
-    <row r="171" spans="4:8" ht="15">
+    <row r="171" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D171" s="1"/>
       <c r="H171" s="1"/>
     </row>
-    <row r="172" spans="4:8" ht="15">
+    <row r="172" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D172" s="1"/>
       <c r="H172" s="1"/>
     </row>
-    <row r="173" spans="4:8" ht="15">
+    <row r="173" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D173" s="1"/>
       <c r="H173" s="1"/>
     </row>
-    <row r="174" spans="4:8" ht="15">
+    <row r="174" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D174" s="1"/>
       <c r="H174" s="1"/>
     </row>
-    <row r="175" spans="8:8" ht="15">
+    <row r="175" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
-    <row r="176" spans="8:8" ht="15">
+    <row r="176" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="8:8" ht="15">
+    <row r="177" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="8:8" ht="15">
+    <row r="178" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="8:8" ht="15">
+    <row r="179" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="8:8" ht="15">
+    <row r="180" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="8:8" ht="15">
+    <row r="181" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="8:8" ht="15">
+    <row r="182" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="8:8" ht="15">
+    <row r="183" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="8:8" ht="15">
+    <row r="184" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="8:8" ht="15">
+    <row r="185" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="8:8" ht="15">
+    <row r="186" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="8:8" ht="15">
+    <row r="187" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="8:8" ht="15">
+    <row r="188" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="8:8" ht="15">
+    <row r="189" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="8:8" ht="15">
+    <row r="190" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="8:8" ht="15">
+    <row r="191" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="8:8" ht="15">
+    <row r="192" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
-    <row r="193" spans="8:8" ht="15">
+    <row r="193" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H193" s="1"/>
     </row>
-    <row r="194" spans="8:8" ht="15">
+    <row r="194" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H194" s="1"/>
     </row>
-    <row r="195" spans="8:8" ht="15">
+    <row r="195" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H195" s="1"/>
     </row>
-    <row r="196" spans="8:8" ht="15">
+    <row r="196" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H196" s="1"/>
     </row>
-    <row r="197" spans="8:8" ht="15">
+    <row r="197" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H197" s="1"/>
     </row>
-    <row r="198" spans="8:8" ht="15">
+    <row r="198" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H198" s="1"/>
     </row>
-    <row r="199" spans="8:8" ht="15">
+    <row r="199" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H199" s="1"/>
+    </row>
+    <row r="200" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H200" s="1"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H201" s="1"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H202" s="1"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H203" s="1"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H204" s="1"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H205" s="1"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H206" s="1"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H207" s="1"/>
+    </row>
+    <row r="208" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H208" s="1"/>
+    </row>
+    <row r="209" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H209" s="1"/>
+    </row>
+    <row r="210" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H210" s="1"/>
+    </row>
+    <row r="211" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H211" s="1"/>
+    </row>
+    <row r="212" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H212" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="1" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
-  <dimension ref="A1:Q199"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
+  <dimension ref="A1:Q213"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="28.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="28.5" customWidth="1"/>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7142857142857" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.5714285714286" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5" customWidth="1"/>
     <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7142857142857" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="28.5714285714286" customWidth="1"/>
-    <col min="12" max="12" width="15.7142857142857" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="15.7142857142857" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.5714285714286" customWidth="1"/>
-    <col min="16" max="16" width="15.7142857142857" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="15.7142857142857" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.5" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.5" customWidth="1"/>
+    <col min="16" max="16" width="15.6640625" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="18.75">
+    <row r="1" spans="1:17" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15"/>
-    <row r="6" spans="1:17" ht="15">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
@@ -3046,12 +3227,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="K7" s="2"/>
       <c r="O7" s="2"/>
     </row>
-    <row r="8" spans="1:17" ht="15.75" thickBot="1"/>
-    <row r="9" spans="1:17" ht="15.75" thickBot="1">
+    <row r="8" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
@@ -3089,7 +3270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B10" s="6"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -3105,26 +3286,26 @@
       <c r="P10" s="7"/>
       <c r="Q10" s="8"/>
     </row>
-    <row r="11" spans="1:17" ht="15">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="C11" s="10">
-        <v>10.032656621227209</v>
+        <v>10.75290592062041</v>
       </c>
       <c r="D11" s="10">
-        <f>IF(B11="","",(C11/100))</f>
-        <v>0.10032656621227209</v>
+        <f t="shared" ref="D11:D50" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10752905920620411</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <v>-5.1704988081845586</v>
+        <v>-5.9934308634348037</v>
       </c>
       <c r="H11" s="12">
-        <f>IF(F11="","",G11/100)</f>
-        <v>-0.051704988081845586</v>
+        <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
+        <v>-5.9934308634348038E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -3143,26 +3324,26 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="C12" s="10">
-        <v>6.5645846909600483</v>
+        <v>7.4692394833383151</v>
       </c>
       <c r="D12" s="10">
-        <f>IF(B12="","",(C12/100))</f>
-        <v>0.065645846909600486</v>
+        <f t="shared" si="0"/>
+        <v>7.4692394833383149E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="10">
-        <v>-4.5072716016839154</v>
+        <v>-5.1837847861408672</v>
       </c>
       <c r="H12" s="12">
-        <f>IF(F12="","",G12/100)</f>
-        <v>-0.045072716016839154</v>
+        <f t="shared" si="1"/>
+        <v>-5.1837847861408673E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -3171,1583 +3352,1781 @@
       <c r="P12" s="11"/>
       <c r="Q12" s="13"/>
     </row>
-    <row r="13" spans="1:17" ht="15">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C13" s="10">
-        <v>4.9922384134675024</v>
+        <v>5.5324314060717423</v>
       </c>
       <c r="D13" s="10">
-        <f>IF(B13="","",(C13/100))</f>
-        <v>0.049922384134675021</v>
+        <f t="shared" si="0"/>
+        <v>5.5324314060717424E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="G13" s="10">
-        <v>-3.8342330644920741</v>
+        <v>-4.4904464480105091</v>
       </c>
       <c r="H13" s="12">
-        <f>IF(F13="","",G13/100)</f>
-        <v>-0.038342330644920743</v>
+        <f t="shared" si="1"/>
+        <v>-4.4904464480105093E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:17" ht="15">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="C14" s="10">
-        <v>4.7916088472466889</v>
+        <v>5.4798915119943992</v>
       </c>
       <c r="D14" s="10">
-        <f>IF(B14="","",(C14/100))</f>
-        <v>0.047916088472466888</v>
+        <f t="shared" si="0"/>
+        <v>5.4798915119943989E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="G14" s="10">
-        <v>-3.432968433269576</v>
+        <v>-4.4006869587325159</v>
       </c>
       <c r="H14" s="12">
-        <f>IF(F14="","",G14/100)</f>
-        <v>-0.034329684332695759</v>
+        <f t="shared" si="1"/>
+        <v>-4.4006869587325158E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:17" ht="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="C15" s="10">
-        <v>4.4429121029125751</v>
+        <v>4.4256917874129238</v>
       </c>
       <c r="D15" s="10">
-        <f>IF(B15="","",(C15/100))</f>
-        <v>0.044429121029125752</v>
+        <f t="shared" si="0"/>
+        <v>4.4256917874129241E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="G15" s="10">
-        <v>-3.4186706210816249</v>
+        <v>-4.2768448521035598</v>
       </c>
       <c r="H15" s="12">
-        <f>IF(F15="","",G15/100)</f>
-        <v>-0.034186706210816251</v>
+        <f t="shared" si="1"/>
+        <v>-4.2768448521035597E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="2:9" ht="15">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="C16" s="10">
-        <v>4.288895898514375</v>
+        <v>4.0114585996489325</v>
       </c>
       <c r="D16" s="10">
-        <f>IF(B16="","",(C16/100))</f>
-        <v>0.042888958985143749</v>
+        <f t="shared" si="0"/>
+        <v>4.0114585996489323E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="G16" s="10">
-        <v>-3.3953542191112787</v>
+        <v>-4.2758220209296685</v>
       </c>
       <c r="H16" s="12">
-        <f>IF(F16="","",G16/100)</f>
-        <v>-0.033953542191112789</v>
+        <f t="shared" si="1"/>
+        <v>-4.2758220209296684E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="2:8" ht="15">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="C17" s="10">
-        <v>3.8064092987500033</v>
+        <v>4.0026823739406829</v>
       </c>
       <c r="D17" s="10">
-        <f>IF(B17="","",(C17/100))</f>
-        <v>0.038064092987500034</v>
+        <f t="shared" si="0"/>
+        <v>4.002682373940683E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.3205937108620782</v>
+        <v>-3.8146942577688012</v>
       </c>
       <c r="H17" s="12">
-        <f>IF(F17="","",G17/100)</f>
-        <v>-0.033205937108620784</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.8146942577688012E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="C18" s="10">
-        <v>3.0688986018070477</v>
+        <v>3.9764142686120283</v>
       </c>
       <c r="D18" s="10">
-        <f>IF(B18="","",(C18/100))</f>
-        <v>0.030688986018070477</v>
+        <f t="shared" si="0"/>
+        <v>3.9764142686120281E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.305152152253104</v>
+        <v>-3.7592318427414506</v>
       </c>
       <c r="H18" s="12">
-        <f>IF(F18="","",G18/100)</f>
-        <v>-0.03305152152253104</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.7592318427414506E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>177</v>
+        <v>206</v>
       </c>
       <c r="C19" s="10">
-        <v>2.974535595805587</v>
+        <v>3.9389470657314019</v>
       </c>
       <c r="D19" s="10">
-        <f>IF(B19="","",(C19/100))</f>
-        <v>0.029745355958055872</v>
+        <f t="shared" si="0"/>
+        <v>3.9389470657314019E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.1295440683041695</v>
+        <v>-3.6320376874597859</v>
       </c>
       <c r="H19" s="12">
-        <f>IF(F19="","",G19/100)</f>
-        <v>-0.031295440683041693</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.6320376874597861E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="C20" s="10">
-        <v>2.6597141564846702</v>
+        <v>3.7290016734757856</v>
       </c>
       <c r="D20" s="10">
-        <f>IF(B20="","",(C20/100))</f>
-        <v>0.026597141564846702</v>
+        <f t="shared" si="0"/>
+        <v>3.7290016734757854E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="G20" s="10">
-        <v>-2.8489805574986744</v>
+        <v>-3.5311836688318596</v>
       </c>
       <c r="H20" s="12">
-        <f>IF(F20="","",G20/100)</f>
-        <v>-0.028489805574986746</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.5311836688318596E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="C21" s="10">
-        <v>2.534463384052581</v>
+        <v>2.9431557514540136</v>
       </c>
       <c r="D21" s="10">
-        <f>IF(B21="","",(C21/100))</f>
-        <v>0.025344633840525811</v>
+        <f t="shared" si="0"/>
+        <v>2.9431557514540137E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G21" s="10">
-        <v>-2.8465368730952396</v>
+        <v>-3.2721487094228197</v>
       </c>
       <c r="H21" s="12">
-        <f>IF(F21="","",G21/100)</f>
-        <v>-0.028465368730952397</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-3.2721487094228195E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>180</v>
+        <v>209</v>
       </c>
       <c r="C22" s="10">
-        <v>2.5274959704581641</v>
+        <v>2.7819275358197402</v>
       </c>
       <c r="D22" s="10">
-        <f>IF(B22="","",(C22/100))</f>
-        <v>0.025274959704581643</v>
+        <f t="shared" si="0"/>
+        <v>2.7819275358197403E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.7632198690417806</v>
+        <v>-2.7413886334777815</v>
       </c>
       <c r="H22" s="12">
-        <f>IF(F22="","",G22/100)</f>
-        <v>-0.027632198690417806</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.7413886334777815E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="C23" s="10">
-        <v>2.4518662620613929</v>
+        <v>2.5907317747027272</v>
       </c>
       <c r="D23" s="10">
-        <f>IF(B23="","",(C23/100))</f>
-        <v>0.024518662620613928</v>
+        <f t="shared" si="0"/>
+        <v>2.5907317747027273E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.5298056841944709</v>
+        <v>-2.7170502309773621</v>
       </c>
       <c r="H23" s="12">
-        <f>IF(F23="","",G23/100)</f>
-        <v>-0.025298056841944708</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.7170502309773623E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="C24" s="10">
-        <v>2.327973295734207</v>
+        <v>2.5707776652134351</v>
       </c>
       <c r="D24" s="10">
-        <f>IF(B24="","",(C24/100))</f>
-        <v>0.023279732957342071</v>
+        <f t="shared" si="0"/>
+        <v>2.5707776652134352E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.454110615658279</v>
+        <v>-2.6765686262803565</v>
       </c>
       <c r="H24" s="12">
-        <f>IF(F24="","",G24/100)</f>
-        <v>-0.024541106156582792</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.6765686262803564E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="C25" s="10">
-        <v>2.2621840484749103</v>
+        <v>2.5144788409927368</v>
       </c>
       <c r="D25" s="10">
-        <f>IF(B25="","",(C25/100))</f>
-        <v>0.022621840484749103</v>
+        <f t="shared" si="0"/>
+        <v>2.5144788409927368E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.2702908225579899</v>
+        <v>-2.4387673018160689</v>
       </c>
       <c r="H25" s="12">
-        <f>IF(F25="","",G25/100)</f>
-        <v>-0.022702908225579899</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.438767301816069E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="C26" s="10">
-        <v>2.218799976641737</v>
+        <v>2.3721711358365862</v>
       </c>
       <c r="D26" s="10">
-        <f>IF(B26="","",(C26/100))</f>
-        <v>0.02218799976641737</v>
+        <f t="shared" si="0"/>
+        <v>2.3721711358365861E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.2192043988824128</v>
+        <v>-2.4110763049710839</v>
       </c>
       <c r="H26" s="12">
-        <f>IF(F26="","",G26/100)</f>
-        <v>-0.022192043988824128</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.411076304971084E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="C27" s="10">
-        <v>2.0979262992440884</v>
+        <v>2.2786355668412965</v>
       </c>
       <c r="D27" s="10">
-        <f>IF(B27="","",(C27/100))</f>
-        <v>0.020979262992440885</v>
+        <f t="shared" si="0"/>
+        <v>2.2786355668412965E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.2125510049526969</v>
+        <v>-2.40224469153938</v>
       </c>
       <c r="H27" s="12">
-        <f>IF(F27="","",G27/100)</f>
-        <v>-0.022125510049526967</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.4022446915393802E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="C28" s="10">
-        <v>1.9968619267310121</v>
+        <v>2.1812497213005262</v>
       </c>
       <c r="D28" s="10">
-        <f>IF(B28="","",(C28/100))</f>
-        <v>0.019968619267310122</v>
+        <f t="shared" si="0"/>
+        <v>2.1812497213005263E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.1734866837248878</v>
+        <v>-2.3746831600873963</v>
       </c>
       <c r="H28" s="12">
-        <f>IF(F28="","",G28/100)</f>
-        <v>-0.02173486683724888</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.3746831600873965E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="C29" s="10">
-        <v>1.986472098938951</v>
+        <v>2.1265592043345598</v>
       </c>
       <c r="D29" s="10">
-        <f>IF(B29="","",(C29/100))</f>
-        <v>0.01986472098938951</v>
+        <f t="shared" si="0"/>
+        <v>2.1265592043345598E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.1534764237528137</v>
+        <v>-2.3697468997632218</v>
       </c>
       <c r="H29" s="12">
-        <f>IF(F29="","",G29/100)</f>
-        <v>-0.021534764237528137</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.3697468997632219E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="C30" s="10">
-        <v>1.9679910923984449</v>
+        <v>2.1027171598591958</v>
       </c>
       <c r="D30" s="10">
-        <f>IF(B30="","",(C30/100))</f>
-        <v>0.01967991092398445</v>
+        <f t="shared" si="0"/>
+        <v>2.1027171598591958E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.1391396618670315</v>
+        <v>-2.34329223603106</v>
       </c>
       <c r="H30" s="12">
-        <f>IF(F30="","",G30/100)</f>
-        <v>-0.021391396618670316</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.3432922360310599E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="C31" s="10">
-        <v>1.9488561827770516</v>
+        <v>2.0498538751452804</v>
       </c>
       <c r="D31" s="10">
-        <f>IF(B31="","",(C31/100))</f>
-        <v>0.019488561827770517</v>
+        <f t="shared" si="0"/>
+        <v>2.0498538751452803E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.0454718574419917</v>
+        <v>-2.2876371235668143</v>
       </c>
       <c r="H31" s="12">
-        <f>IF(F31="","",G31/100)</f>
-        <v>-0.020454718574419918</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.2876371235668144E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="C32" s="10">
-        <v>1.9307280114811938</v>
+        <v>2.0311422378021988</v>
       </c>
       <c r="D32" s="10">
-        <f>IF(B32="","",(C32/100))</f>
-        <v>0.019307280114811937</v>
+        <f t="shared" si="0"/>
+        <v>2.0311422378021988E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.033411263528131</v>
+        <v>-2.2863701634985345</v>
       </c>
       <c r="H32" s="12">
-        <f>IF(F32="","",G32/100)</f>
-        <v>-0.020334112635281308</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.2863701634985346E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>191</v>
+        <v>220</v>
       </c>
       <c r="C33" s="10">
-        <v>1.7946684706179672</v>
+        <v>2.0118308168971288</v>
       </c>
       <c r="D33" s="10">
-        <f>IF(B33="","",(C33/100))</f>
-        <v>0.017946684706179671</v>
+        <f t="shared" si="0"/>
+        <v>2.011830816897129E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="G33" s="10">
-        <v>-1.9741664165062998</v>
+        <v>-2.0171062929217198</v>
       </c>
       <c r="H33" s="12">
-        <f>IF(F33="","",G33/100)</f>
-        <v>-0.019741664165062997</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.01710629292172E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="C34" s="10">
-        <v>1.6640148823011673</v>
+        <v>1.9939764614609139</v>
       </c>
       <c r="D34" s="10">
-        <f>IF(B34="","",(C34/100))</f>
-        <v>0.016640148823011673</v>
+        <f t="shared" si="0"/>
+        <v>1.993976461460914E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="G34" s="10">
-        <v>-1.929297673838144</v>
+        <v>-2.0085239924570435</v>
       </c>
       <c r="H34" s="12">
-        <f>IF(F34="","",G34/100)</f>
-        <v>-0.019292976738381439</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-2.0085239924570435E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="C35" s="10">
-        <v>1.5499138700087787</v>
+        <v>1.9563549642078071</v>
       </c>
       <c r="D35" s="10">
-        <f>IF(B35="","",(C35/100))</f>
-        <v>0.015499138700087787</v>
+        <f t="shared" si="0"/>
+        <v>1.9563549642078071E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.6379702994790253</v>
+        <v>-1.8660124031809358</v>
       </c>
       <c r="H35" s="12">
-        <f>IF(F35="","",G35/100)</f>
-        <v>-0.016379702994790253</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.8660124031809357E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="C36" s="10">
-        <v>1.5162825406658633</v>
+        <v>1.8133984670745464</v>
       </c>
       <c r="D36" s="10">
-        <f>IF(B36="","",(C36/100))</f>
-        <v>0.015162825406658633</v>
+        <f t="shared" si="0"/>
+        <v>1.8133984670745465E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.5474968939695712</v>
+        <v>-1.8481858780294125</v>
       </c>
       <c r="H36" s="12">
-        <f>IF(F36="","",G36/100)</f>
-        <v>-0.015474968939695712</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.8481858780294125E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="C37" s="10">
-        <v>1.4198630546469748</v>
+        <v>1.7991699255396374</v>
       </c>
       <c r="D37" s="10">
-        <f>IF(B37="","",(C37/100))</f>
-        <v>0.014198630546469748</v>
+        <f t="shared" si="0"/>
+        <v>1.7991699255396374E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.5376735183298007</v>
+        <v>-1.740215150840926</v>
       </c>
       <c r="H37" s="12">
-        <f>IF(F37="","",G37/100)</f>
-        <v>-0.015376735183298008</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.740215150840926E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>196</v>
+        <v>225</v>
       </c>
       <c r="C38" s="10">
-        <v>1.3616945285188287</v>
+        <v>1.7804097216213104</v>
       </c>
       <c r="D38" s="10">
-        <f>IF(B38="","",(C38/100))</f>
-        <v>0.013616945285188286</v>
+        <f t="shared" si="0"/>
+        <v>1.7804097216213104E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.5215067098010393</v>
+        <v>-1.6715201857691149</v>
       </c>
       <c r="H38" s="12">
-        <f>IF(F38="","",G38/100)</f>
-        <v>-0.015215067098010394</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.671520185769115E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>197</v>
+        <v>226</v>
       </c>
       <c r="C39" s="10">
-        <v>1.3511011926338614</v>
+        <v>1.7584797301304107</v>
       </c>
       <c r="D39" s="10">
-        <f>IF(B39="","",(C39/100))</f>
-        <v>0.013511011926338613</v>
+        <f t="shared" si="0"/>
+        <v>1.7584797301304106E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.4898873451015626</v>
+        <v>-1.662796755748001</v>
       </c>
       <c r="H39" s="12">
-        <f>IF(F39="","",G39/100)</f>
-        <v>-0.014898873451015626</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.6627967557480011E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="C40" s="10">
-        <v>1.3056266021448164</v>
+        <v>1.7139454766481832</v>
       </c>
       <c r="D40" s="10">
-        <f>IF(B40="","",(C40/100))</f>
-        <v>0.013056266021448165</v>
+        <f t="shared" si="0"/>
+        <v>1.7139454766481831E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.2536474121179391</v>
+        <v>-1.5345054187769702</v>
       </c>
       <c r="H40" s="12">
-        <f>IF(F40="","",G40/100)</f>
-        <v>-0.01253647412117939</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.5345054187769703E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C41" s="10">
-        <v>1.0144456000955313</v>
+        <v>1.7088300247605672</v>
       </c>
       <c r="D41" s="10">
-        <f>IF(B41="","",(C41/100))</f>
-        <v>0.010144456000955314</v>
+        <f t="shared" si="0"/>
+        <v>1.7088300247605673E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.1839464368861896</v>
+        <v>-1.4991249415563426</v>
       </c>
       <c r="H41" s="12">
-        <f>IF(F41="","",G41/100)</f>
-        <v>-0.011839464368861897</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.4991249415563426E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="C42" s="10">
-        <v>0.62192586338377553</v>
+        <v>1.5899809986203635</v>
       </c>
       <c r="D42" s="10">
-        <f>IF(B42="","",(C42/100))</f>
-        <v>0.0062192586338377549</v>
+        <f t="shared" si="0"/>
+        <v>1.5899809986203634E-2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.1038327999980688</v>
+        <v>-1.4710904316875686</v>
       </c>
       <c r="H42" s="12">
-        <f>IF(F42="","",G42/100)</f>
-        <v>-0.011038327999980689</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1.4710904316875686E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="C43" s="10">
-        <v>0.46883194855321542</v>
+        <v>1.4257662892427765</v>
       </c>
       <c r="D43" s="10">
-        <f>IF(B43="","",(C43/100))</f>
-        <v>0.0046883194855321542</v>
+        <f t="shared" si="0"/>
+        <v>1.4257662892427764E-2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.0732978734402292</v>
+        <v>-1.3891977726386431</v>
       </c>
       <c r="H43" s="12">
-        <f>IF(F43="","",G43/100)</f>
-        <v>-0.010732978734402291</v>
-      </c>
-    </row>
-    <row r="44" spans="2:8" ht="15">
+        <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
+        <v>-1.389197772638643E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="C44" s="10">
-        <v>0.44721761564726037</v>
+        <v>1.4204945648496996</v>
       </c>
       <c r="D44" s="10">
-        <f>IF(B44="","",(C44/100))</f>
-        <v>0.0044721761564726036</v>
+        <f t="shared" si="0"/>
+        <v>1.4204945648496996E-2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.0505283383197708</v>
+        <v>-1.3581861044227097</v>
       </c>
       <c r="H44" s="12">
-        <f>IF(F44="","",G44/100)</f>
-        <v>-0.010505283383197707</v>
-      </c>
-    </row>
-    <row r="45" spans="2:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.3581861044227097E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="C45" s="10">
-        <v>0.43950969956230901</v>
+        <v>1.4013027868842094</v>
       </c>
       <c r="D45" s="10">
-        <f>IF(B45="","",(C45/100))</f>
-        <v>0.0043950969956230903</v>
+        <f t="shared" si="0"/>
+        <v>1.4013027868842095E-2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.0233135625590861</v>
+        <v>-1.2929764732396047</v>
       </c>
       <c r="H45" s="12">
-        <f>IF(F45="","",G45/100)</f>
-        <v>-0.010233135625590861</v>
-      </c>
-    </row>
-    <row r="46" spans="2:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.2929764732396048E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="C46" s="10">
-        <v>0.38619037808332551</v>
+        <v>1.0838954568849919</v>
       </c>
       <c r="D46" s="10">
-        <f>IF(B46="","",(C46/100))</f>
-        <v>0.0038619037808332551</v>
+        <f t="shared" si="0"/>
+        <v>1.0838954568849918E-2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.0124649915953887</v>
+        <v>-1.2784004980554449</v>
       </c>
       <c r="H46" s="12">
-        <f>IF(F46="","",G46/100)</f>
-        <v>-0.010124649915953887</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.2784004980554448E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.54126152093270297</v>
+      </c>
+      <c r="D47" s="10">
+        <f t="shared" si="0"/>
+        <v>5.4126152093270296E-3</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G47" s="10">
+        <v>-1.2741244566663887</v>
+      </c>
+      <c r="H47" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.2741244566663888E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" s="10">
+        <v>0.52341862502547887</v>
+      </c>
+      <c r="D48" s="10">
+        <f t="shared" si="0"/>
+        <v>5.2341862502547883E-3</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G48" s="10">
+        <v>-1.238086147912516</v>
+      </c>
+      <c r="H48" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.238086147912516E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B49" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C49" s="10">
+        <v>0.51245997294786305</v>
+      </c>
+      <c r="D49" s="10">
+        <f t="shared" si="0"/>
+        <v>5.1245997294786308E-3</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="G49" s="10">
+        <v>-1.232329098824392</v>
+      </c>
+      <c r="H49" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.232329098824392E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B50" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C47" s="10">
-        <v>0.14305569396678564</v>
-      </c>
-      <c r="D47" s="10">
-        <f>IF(B47="","",(C47/100))</f>
-        <v>0.0014305569396678563</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G47" s="10">
-        <v>-0.98365098706492349</v>
-      </c>
-      <c r="H47" s="12">
-        <f>IF(F47="","",G47/100)</f>
-        <v>-0.0098365098706492352</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" ht="15">
-      <c r="B48" s="9"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="F48" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="G48" s="10">
-        <v>-0.94381664013024091</v>
-      </c>
-      <c r="H48" s="12">
-        <f>IF(F48="","",G48/100)</f>
-        <v>-0.0094381664013024093</v>
-      </c>
-    </row>
-    <row r="49" spans="2:8" ht="15">
-      <c r="F49" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="G49" s="10">
-        <v>-0.926678118467684</v>
-      </c>
-      <c r="H49" s="12">
-        <f>IF(F49="","",G49/100)</f>
-        <v>-0.0092667811846768398</v>
-      </c>
-    </row>
-    <row r="50" spans="2:8" ht="15">
+      <c r="C50" s="10">
+        <v>0.18185644962413716</v>
+      </c>
+      <c r="D50" s="10">
+        <f t="shared" si="0"/>
+        <v>1.8185644962413717E-3</v>
+      </c>
       <c r="F50" s="11" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="G50" s="10">
-        <v>-0.84580676266797039</v>
+        <v>-1.163752003193627</v>
       </c>
       <c r="H50" s="12">
-        <f>IF(F50="","",G50/100)</f>
-        <v>-0.0084580676266797043</v>
-      </c>
-    </row>
-    <row r="51" spans="2:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.163752003193627E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B51" s="9"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
       <c r="F51" s="11" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="G51" s="10">
-        <v>-0.78224890759350829</v>
+        <v>-1.1222439521141796</v>
       </c>
       <c r="H51" s="12">
-        <f>IF(F51="","",G51/100)</f>
-        <v>-0.0078224890759350831</v>
-      </c>
-    </row>
-    <row r="52" spans="6:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-1.1222439521141795E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="G52" s="10">
-        <v>-0.77747557302802051</v>
+        <v>-1.1188912213466502</v>
       </c>
       <c r="H52" s="12">
-        <f>IF(F52="","",G52/100)</f>
-        <v>-0.0077747557302802047</v>
-      </c>
-    </row>
-    <row r="53" spans="4:8" ht="15">
-      <c r="D53" s="1"/>
+        <f t="shared" si="2"/>
+        <v>-1.1188912213466502E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.75649150514848595</v>
+        <v>-1.0025669067929244</v>
       </c>
       <c r="H53" s="12">
-        <f>IF(F53="","",G53/100)</f>
-        <v>-0.00756491505148486</v>
-      </c>
-    </row>
-    <row r="54" spans="4:8" ht="15">
-      <c r="D54" s="1"/>
+        <f t="shared" si="2"/>
+        <v>-1.0025669067929243E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F54" s="11" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.71720860738108261</v>
+        <v>-0.98530667336568545</v>
       </c>
       <c r="H54" s="12">
-        <f>IF(F54="","",G54/100)</f>
-        <v>-0.0071720860738108258</v>
-      </c>
-    </row>
-    <row r="55" spans="4:8" ht="15">
-      <c r="D55" s="1"/>
+        <f t="shared" si="2"/>
+        <v>-9.8530667336568546E-3</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F55" s="11" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.67016588241884512</v>
+        <v>-0.94970027971638638</v>
       </c>
       <c r="H55" s="12">
-        <f>IF(F55="","",G55/100)</f>
-        <v>-0.0067016588241884511</v>
-      </c>
-    </row>
-    <row r="56" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-9.4970027971638636E-3</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.65754618032149303</v>
+        <v>-0.94896359570984901</v>
       </c>
       <c r="H56" s="12">
-        <f>IF(F56="","",G56/100)</f>
-        <v>-0.0065754618032149307</v>
-      </c>
-    </row>
-    <row r="57" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-9.4896359570984905E-3</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.62313755902555368</v>
+        <v>-0.85141844786647047</v>
       </c>
       <c r="H57" s="12">
-        <f>IF(F57="","",G57/100)</f>
-        <v>-0.0062313755902555371</v>
-      </c>
-    </row>
-    <row r="58" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-8.5141844786647044E-3</v>
+      </c>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.59141221187096971</v>
+        <v>-0.81507946289955924</v>
       </c>
       <c r="H58" s="12">
-        <f>IF(F58="","",G58/100)</f>
-        <v>-0.0059141221187096974</v>
-      </c>
-    </row>
-    <row r="59" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-8.1507946289955929E-3</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.55113135083728282</v>
+        <v>-0.79425954506813967</v>
       </c>
       <c r="H59" s="12">
-        <f>IF(F59="","",G59/100)</f>
-        <v>-0.0055113135083728285</v>
-      </c>
-    </row>
-    <row r="60" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-7.9425954506813969E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.53187612584804311</v>
+        <v>-0.77839123514436381</v>
       </c>
       <c r="H60" s="12">
-        <f>IF(F60="","",G60/100)</f>
-        <v>-0.0053187612584804315</v>
-      </c>
-    </row>
-    <row r="61" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-7.7839123514436385E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.50047808707859631</v>
+        <v>-0.74874311445534492</v>
       </c>
       <c r="H61" s="12">
-        <f>IF(F61="","",G61/100)</f>
-        <v>-0.0050047808707859628</v>
-      </c>
-    </row>
-    <row r="62" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-7.4874311445534492E-3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.49314703386829195</v>
+        <v>-0.72710233964849313</v>
       </c>
       <c r="H62" s="12">
-        <f>IF(F62="","",G62/100)</f>
-        <v>-0.0049314703386829197</v>
-      </c>
-    </row>
-    <row r="63" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-7.2710233964849314E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.46170906347585844</v>
+        <v>-0.69924954516799831</v>
       </c>
       <c r="H63" s="12">
-        <f>IF(F63="","",G63/100)</f>
-        <v>-0.0046170906347585841</v>
-      </c>
-    </row>
-    <row r="64" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.992495451679983E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.45695785495720603</v>
+        <v>-0.69769432337641968</v>
       </c>
       <c r="H64" s="12">
-        <f>IF(F64="","",G64/100)</f>
-        <v>-0.0045695785495720601</v>
-      </c>
-    </row>
-    <row r="65" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.9769432337641966E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.45286715475976053</v>
+        <v>-0.69166169990066484</v>
       </c>
       <c r="H65" s="12">
-        <f>IF(F65="","",G65/100)</f>
-        <v>-0.004528671547597605</v>
-      </c>
-    </row>
-    <row r="66" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.9166169990066487E-3</v>
+      </c>
+    </row>
+    <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.40637620627318749</v>
+        <v>-0.6899591413077788</v>
       </c>
       <c r="H66" s="12">
-        <f>IF(F66="","",G66/100)</f>
-        <v>-0.0040637620627318747</v>
-      </c>
-    </row>
-    <row r="67" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.8995914130777882E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.36077501290077152</v>
+        <v>-0.60217103207357514</v>
       </c>
       <c r="H67" s="12">
-        <f>IF(F67="","",G67/100)</f>
-        <v>-0.0036077501290077154</v>
-      </c>
-    </row>
-    <row r="68" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-6.0217103207357518E-3</v>
+      </c>
+    </row>
+    <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.34724375695081222</v>
+        <v>-0.58918145132830757</v>
       </c>
       <c r="H68" s="12">
-        <f>IF(F68="","",G68/100)</f>
-        <v>-0.0034724375695081222</v>
-      </c>
-    </row>
-    <row r="69" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-5.8918145132830753E-3</v>
+      </c>
+    </row>
+    <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.30292024459061806</v>
+        <v>-0.58261336771817163</v>
       </c>
       <c r="H69" s="12">
-        <f>IF(F69="","",G69/100)</f>
-        <v>-0.0030292024459061804</v>
-      </c>
-    </row>
-    <row r="70" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-5.8261336771817159E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.28449775759484458</v>
+        <v>-0.57868438634997299</v>
       </c>
       <c r="H70" s="12">
-        <f>IF(F70="","",G70/100)</f>
-        <v>-0.0028449775759484459</v>
-      </c>
-    </row>
-    <row r="71" spans="4:8" ht="15">
+        <f t="shared" si="2"/>
+        <v>-5.7868438634997299E-3</v>
+      </c>
+    </row>
+    <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G71" s="10">
+        <v>-0.55286020134673897</v>
+      </c>
+      <c r="H71" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.52860201346739E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D72" s="1"/>
+      <c r="F72" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="G72" s="10">
+        <v>-0.54892235248586918</v>
+      </c>
+      <c r="H72" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.4892235248586918E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D73" s="1"/>
+      <c r="F73" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G73" s="10">
+        <v>-0.54509807574267388</v>
+      </c>
+      <c r="H73" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.4509807574267388E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D74" s="1"/>
+      <c r="F74" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="G74" s="10">
+        <v>-0.53861150485363163</v>
+      </c>
+      <c r="H74" s="12">
+        <f t="shared" si="2"/>
+        <v>-5.3861150485363159E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D75" s="1"/>
+      <c r="F75" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G75" s="10">
+        <v>-0.50531338775814905</v>
+      </c>
+      <c r="H75" s="12">
+        <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
+        <v>-5.0531338775814906E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D76" s="1"/>
+      <c r="F76" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G76" s="10">
+        <v>-0.48493588959954442</v>
+      </c>
+      <c r="H76" s="12">
+        <f t="shared" si="3"/>
+        <v>-4.8493588959954443E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D77" s="1"/>
+      <c r="F77" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G77" s="10">
+        <v>-0.44717142107998376</v>
+      </c>
+      <c r="H77" s="12">
+        <f t="shared" si="3"/>
+        <v>-4.4717142107998376E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D78" s="1"/>
+      <c r="F78" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="G78" s="10">
+        <v>-0.43447780995549073</v>
+      </c>
+      <c r="H78" s="12">
+        <f t="shared" si="3"/>
+        <v>-4.3447780995549074E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D79" s="1"/>
+      <c r="F79" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="G79" s="10">
+        <v>-0.38811276029405428</v>
+      </c>
+      <c r="H79" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.8811276029405428E-3</v>
+      </c>
+    </row>
+    <row r="80" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D80" s="1"/>
+      <c r="F80" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="G80" s="10">
+        <v>-0.3726406908697204</v>
+      </c>
+      <c r="H80" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.7264069086972041E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D81" s="1"/>
+      <c r="F81" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="G81" s="10">
+        <v>-0.34666303003179116</v>
+      </c>
+      <c r="H81" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.4666303003179117E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D82" s="1"/>
+      <c r="F82" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="G82" s="10">
+        <v>-0.34602859503690198</v>
+      </c>
+      <c r="H82" s="12">
+        <f t="shared" si="3"/>
+        <v>-3.4602859503690196E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D83" s="1"/>
+      <c r="F83" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G83" s="10">
+        <v>-0.26711125262511992</v>
+      </c>
+      <c r="H83" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.6711125262511991E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D84" s="1"/>
+      <c r="F84" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="G84" s="10">
+        <v>-0.24576392361420543</v>
+      </c>
+      <c r="H84" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.4576392361420544E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D85" s="1"/>
+      <c r="F85" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G71" s="10">
-        <v>-0.21228573789399938</v>
-      </c>
-      <c r="H71" s="12">
-        <f>IF(F71="","",G71/100)</f>
-        <v>-0.0021228573789399937</v>
-      </c>
-    </row>
-    <row r="72" spans="4:8" ht="15">
-      <c r="D72" s="1"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="13"/>
-    </row>
-    <row r="73" spans="4:8" ht="15">
-      <c r="D73" s="1"/>
-    </row>
-    <row r="74" spans="4:8" ht="15">
-      <c r="D74" s="1"/>
-    </row>
-    <row r="75" spans="4:8" ht="15">
-      <c r="D75" s="1"/>
-      <c r="G75" t="s">
+      <c r="G85" s="10">
+        <v>-0.20520428498169269</v>
+      </c>
+      <c r="H85" s="12">
+        <f t="shared" si="3"/>
+        <v>-2.0520428498169269E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D86" s="1"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="13"/>
+    </row>
+    <row r="87" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D87" s="1"/>
+    </row>
+    <row r="88" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D88" s="1"/>
+    </row>
+    <row r="89" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D89" s="1"/>
+      <c r="G89" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="4:4" ht="15">
-      <c r="D76" s="1"/>
-    </row>
-    <row r="77" spans="4:8" ht="15">
-      <c r="D77" s="1"/>
-      <c r="H77" s="1"/>
-    </row>
-    <row r="78" spans="4:8" ht="15">
-      <c r="D78" s="1"/>
-      <c r="H78" s="1"/>
-    </row>
-    <row r="79" spans="4:8" ht="15">
-      <c r="D79" s="1"/>
-      <c r="H79" s="1"/>
-    </row>
-    <row r="80" spans="4:8" ht="15">
-      <c r="D80" s="1"/>
-      <c r="H80" s="1"/>
-    </row>
-    <row r="81" spans="4:8" ht="15">
-      <c r="D81" s="1"/>
-      <c r="H81" s="1"/>
-    </row>
-    <row r="82" spans="4:8" ht="15">
-      <c r="D82" s="1"/>
-      <c r="H82" s="1"/>
-    </row>
-    <row r="83" spans="4:8" ht="15">
-      <c r="D83" s="1"/>
-      <c r="H83" s="1"/>
-    </row>
-    <row r="84" spans="4:8" ht="15">
-      <c r="D84" s="1"/>
-      <c r="H84" s="1"/>
-    </row>
-    <row r="85" spans="4:8" ht="15">
-      <c r="D85" s="1"/>
-      <c r="H85" s="1"/>
-    </row>
-    <row r="86" spans="4:8" ht="15">
-      <c r="D86" s="1"/>
-      <c r="H86" s="1"/>
-    </row>
-    <row r="87" spans="4:8" ht="15">
-      <c r="D87" s="1"/>
-      <c r="H87" s="1"/>
-    </row>
-    <row r="88" spans="4:8" ht="15">
-      <c r="D88" s="1"/>
-      <c r="H88" s="1"/>
-    </row>
-    <row r="89" spans="4:8" ht="15">
-      <c r="D89" s="1"/>
-      <c r="H89" s="1"/>
-    </row>
-    <row r="90" spans="4:8" ht="15">
+    <row r="90" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D90" s="1"/>
-      <c r="H90" s="1"/>
-    </row>
-    <row r="91" spans="4:8" ht="15">
+    </row>
+    <row r="91" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D91" s="1"/>
       <c r="H91" s="1"/>
     </row>
-    <row r="92" spans="4:8" ht="15">
+    <row r="92" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D92" s="1"/>
       <c r="H92" s="1"/>
     </row>
-    <row r="93" spans="4:8" ht="15">
+    <row r="93" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D93" s="1"/>
       <c r="H93" s="1"/>
     </row>
-    <row r="94" spans="4:8" ht="15">
+    <row r="94" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D94" s="1"/>
       <c r="H94" s="1"/>
     </row>
-    <row r="95" spans="4:8" ht="15">
+    <row r="95" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D95" s="1"/>
       <c r="H95" s="1"/>
     </row>
-    <row r="96" spans="4:8" ht="15">
+    <row r="96" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D96" s="1"/>
       <c r="H96" s="1"/>
     </row>
-    <row r="97" spans="4:8" ht="15">
+    <row r="97" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D97" s="1"/>
       <c r="H97" s="1"/>
     </row>
-    <row r="98" spans="4:8" ht="15">
+    <row r="98" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D98" s="1"/>
       <c r="H98" s="1"/>
     </row>
-    <row r="99" spans="4:8" ht="15">
+    <row r="99" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D99" s="1"/>
       <c r="H99" s="1"/>
     </row>
-    <row r="100" spans="4:8" ht="15">
+    <row r="100" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D100" s="1"/>
       <c r="H100" s="1"/>
     </row>
-    <row r="101" spans="4:8" ht="15">
+    <row r="101" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D101" s="1"/>
       <c r="H101" s="1"/>
     </row>
-    <row r="102" spans="4:8" ht="15">
+    <row r="102" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D102" s="1"/>
       <c r="H102" s="1"/>
     </row>
-    <row r="103" spans="4:8" ht="15">
+    <row r="103" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D103" s="1"/>
       <c r="H103" s="1"/>
     </row>
-    <row r="104" spans="4:8" ht="15">
+    <row r="104" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D104" s="1"/>
       <c r="H104" s="1"/>
     </row>
-    <row r="105" spans="4:8" ht="15">
+    <row r="105" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D105" s="1"/>
       <c r="H105" s="1"/>
     </row>
-    <row r="106" spans="4:8" ht="15">
+    <row r="106" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D106" s="1"/>
       <c r="H106" s="1"/>
     </row>
-    <row r="107" spans="4:8" ht="15">
+    <row r="107" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D107" s="1"/>
       <c r="H107" s="1"/>
     </row>
-    <row r="108" spans="4:8" ht="15">
+    <row r="108" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D108" s="1"/>
       <c r="H108" s="1"/>
     </row>
-    <row r="109" spans="4:8" ht="15">
+    <row r="109" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D109" s="1"/>
       <c r="H109" s="1"/>
     </row>
-    <row r="110" spans="4:8" ht="15">
+    <row r="110" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D110" s="1"/>
       <c r="H110" s="1"/>
     </row>
-    <row r="111" spans="4:8" ht="15">
+    <row r="111" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D111" s="1"/>
       <c r="H111" s="1"/>
     </row>
-    <row r="112" spans="4:8" ht="15">
+    <row r="112" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D112" s="1"/>
       <c r="H112" s="1"/>
     </row>
-    <row r="113" spans="4:8" ht="15">
+    <row r="113" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D113" s="1"/>
       <c r="H113" s="1"/>
     </row>
-    <row r="114" spans="4:8" ht="15">
+    <row r="114" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D114" s="1"/>
       <c r="H114" s="1"/>
     </row>
-    <row r="115" spans="4:8" ht="15">
+    <row r="115" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D115" s="1"/>
       <c r="H115" s="1"/>
     </row>
-    <row r="116" spans="4:8" ht="15">
+    <row r="116" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D116" s="1"/>
       <c r="H116" s="1"/>
     </row>
-    <row r="117" spans="4:8" ht="15">
+    <row r="117" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D117" s="1"/>
       <c r="H117" s="1"/>
     </row>
-    <row r="118" spans="4:8" ht="15">
+    <row r="118" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D118" s="1"/>
       <c r="H118" s="1"/>
     </row>
-    <row r="119" spans="4:8" ht="15">
+    <row r="119" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D119" s="1"/>
       <c r="H119" s="1"/>
     </row>
-    <row r="120" spans="4:8" ht="15">
+    <row r="120" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D120" s="1"/>
       <c r="H120" s="1"/>
     </row>
-    <row r="121" spans="4:8" ht="15">
+    <row r="121" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D121" s="1"/>
       <c r="H121" s="1"/>
     </row>
-    <row r="122" spans="4:8" ht="15">
+    <row r="122" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D122" s="1"/>
       <c r="H122" s="1"/>
     </row>
-    <row r="123" spans="4:8" ht="15">
+    <row r="123" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D123" s="1"/>
       <c r="H123" s="1"/>
     </row>
-    <row r="124" spans="4:8" ht="15">
+    <row r="124" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D124" s="1"/>
       <c r="H124" s="1"/>
     </row>
-    <row r="125" spans="4:8" ht="15">
+    <row r="125" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D125" s="1"/>
       <c r="H125" s="1"/>
     </row>
-    <row r="126" spans="4:8" ht="15">
+    <row r="126" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D126" s="1"/>
       <c r="H126" s="1"/>
     </row>
-    <row r="127" spans="4:8" ht="15">
+    <row r="127" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D127" s="1"/>
       <c r="H127" s="1"/>
     </row>
-    <row r="128" spans="4:8" ht="15">
+    <row r="128" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D128" s="1"/>
       <c r="H128" s="1"/>
     </row>
-    <row r="129" spans="4:8" ht="15">
+    <row r="129" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D129" s="1"/>
       <c r="H129" s="1"/>
     </row>
-    <row r="130" spans="4:8" ht="15">
+    <row r="130" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D130" s="1"/>
       <c r="H130" s="1"/>
     </row>
-    <row r="131" spans="4:8" ht="15">
+    <row r="131" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D131" s="1"/>
       <c r="H131" s="1"/>
     </row>
-    <row r="132" spans="4:8" ht="15">
+    <row r="132" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D132" s="1"/>
       <c r="H132" s="1"/>
     </row>
-    <row r="133" spans="4:8" ht="15">
+    <row r="133" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D133" s="1"/>
       <c r="H133" s="1"/>
     </row>
-    <row r="134" spans="4:8" ht="15">
+    <row r="134" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D134" s="1"/>
       <c r="H134" s="1"/>
     </row>
-    <row r="135" spans="4:8" ht="15">
+    <row r="135" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D135" s="1"/>
       <c r="H135" s="1"/>
     </row>
-    <row r="136" spans="4:8" ht="15">
+    <row r="136" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D136" s="1"/>
       <c r="H136" s="1"/>
     </row>
-    <row r="137" spans="4:8" ht="15">
+    <row r="137" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D137" s="1"/>
       <c r="H137" s="1"/>
     </row>
-    <row r="138" spans="4:8" ht="15">
+    <row r="138" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D138" s="1"/>
       <c r="H138" s="1"/>
     </row>
-    <row r="139" spans="4:8" ht="15">
+    <row r="139" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D139" s="1"/>
       <c r="H139" s="1"/>
     </row>
-    <row r="140" spans="4:8" ht="15">
+    <row r="140" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D140" s="1"/>
       <c r="H140" s="1"/>
     </row>
-    <row r="141" spans="4:8" ht="15">
+    <row r="141" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D141" s="1"/>
       <c r="H141" s="1"/>
     </row>
-    <row r="142" spans="4:8" ht="15">
+    <row r="142" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D142" s="1"/>
       <c r="H142" s="1"/>
     </row>
-    <row r="143" spans="4:8" ht="15">
+    <row r="143" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D143" s="1"/>
       <c r="H143" s="1"/>
     </row>
-    <row r="144" spans="4:8" ht="15">
+    <row r="144" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D144" s="1"/>
       <c r="H144" s="1"/>
     </row>
-    <row r="145" spans="4:8" ht="15">
+    <row r="145" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D145" s="1"/>
       <c r="H145" s="1"/>
     </row>
-    <row r="146" spans="4:8" ht="15">
+    <row r="146" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D146" s="1"/>
       <c r="H146" s="1"/>
     </row>
-    <row r="147" spans="4:8" ht="15">
+    <row r="147" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D147" s="1"/>
       <c r="H147" s="1"/>
     </row>
-    <row r="148" spans="4:8" ht="15">
+    <row r="148" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D148" s="1"/>
       <c r="H148" s="1"/>
     </row>
-    <row r="149" spans="4:8" ht="15">
+    <row r="149" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D149" s="1"/>
       <c r="H149" s="1"/>
     </row>
-    <row r="150" spans="4:8" ht="15">
+    <row r="150" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D150" s="1"/>
       <c r="H150" s="1"/>
     </row>
-    <row r="151" spans="4:8" ht="15">
+    <row r="151" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D151" s="1"/>
       <c r="H151" s="1"/>
     </row>
-    <row r="152" spans="4:8" ht="15">
+    <row r="152" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D152" s="1"/>
       <c r="H152" s="1"/>
     </row>
-    <row r="153" spans="4:8" ht="15">
+    <row r="153" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D153" s="1"/>
       <c r="H153" s="1"/>
     </row>
-    <row r="154" spans="4:8" ht="15">
+    <row r="154" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D154" s="1"/>
       <c r="H154" s="1"/>
     </row>
-    <row r="155" spans="4:8" ht="15">
+    <row r="155" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D155" s="1"/>
       <c r="H155" s="1"/>
     </row>
-    <row r="156" spans="4:8" ht="15">
+    <row r="156" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D156" s="1"/>
       <c r="H156" s="1"/>
     </row>
-    <row r="157" spans="4:8" ht="15">
+    <row r="157" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D157" s="1"/>
       <c r="H157" s="1"/>
     </row>
-    <row r="158" spans="4:8" ht="15">
+    <row r="158" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D158" s="1"/>
       <c r="H158" s="1"/>
     </row>
-    <row r="159" spans="4:8" ht="15">
+    <row r="159" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D159" s="1"/>
       <c r="H159" s="1"/>
     </row>
-    <row r="160" spans="4:8" ht="15">
+    <row r="160" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D160" s="1"/>
       <c r="H160" s="1"/>
     </row>
-    <row r="161" spans="4:8" ht="15">
+    <row r="161" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D161" s="1"/>
       <c r="H161" s="1"/>
     </row>
-    <row r="162" spans="4:8" ht="15">
+    <row r="162" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D162" s="1"/>
       <c r="H162" s="1"/>
     </row>
-    <row r="163" spans="4:8" ht="15">
+    <row r="163" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D163" s="1"/>
       <c r="H163" s="1"/>
     </row>
-    <row r="164" spans="4:8" ht="15">
+    <row r="164" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D164" s="1"/>
       <c r="H164" s="1"/>
     </row>
-    <row r="165" spans="4:8" ht="15">
+    <row r="165" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D165" s="1"/>
       <c r="H165" s="1"/>
     </row>
-    <row r="166" spans="4:8" ht="15">
+    <row r="166" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D166" s="1"/>
       <c r="H166" s="1"/>
     </row>
-    <row r="167" spans="4:8" ht="15">
+    <row r="167" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D167" s="1"/>
       <c r="H167" s="1"/>
     </row>
-    <row r="168" spans="4:8" ht="15">
+    <row r="168" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D168" s="1"/>
       <c r="H168" s="1"/>
     </row>
-    <row r="169" spans="4:8" ht="15">
+    <row r="169" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D169" s="1"/>
       <c r="H169" s="1"/>
     </row>
-    <row r="170" spans="4:8" ht="15">
+    <row r="170" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D170" s="1"/>
       <c r="H170" s="1"/>
     </row>
-    <row r="171" spans="4:8" ht="15">
+    <row r="171" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D171" s="1"/>
       <c r="H171" s="1"/>
     </row>
-    <row r="172" spans="4:8" ht="15">
+    <row r="172" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D172" s="1"/>
       <c r="H172" s="1"/>
     </row>
-    <row r="173" spans="4:8" ht="15">
+    <row r="173" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D173" s="1"/>
       <c r="H173" s="1"/>
     </row>
-    <row r="174" spans="4:8" ht="15">
+    <row r="174" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D174" s="1"/>
       <c r="H174" s="1"/>
     </row>
-    <row r="175" spans="4:8" ht="15">
+    <row r="175" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D175" s="1"/>
       <c r="H175" s="1"/>
     </row>
-    <row r="176" spans="4:8" ht="15">
+    <row r="176" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
-    <row r="177" spans="8:8" ht="15">
+    <row r="177" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D177" s="1"/>
       <c r="H177" s="1"/>
     </row>
-    <row r="178" spans="8:8" ht="15">
+    <row r="178" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D178" s="1"/>
       <c r="H178" s="1"/>
     </row>
-    <row r="179" spans="8:8" ht="15">
+    <row r="179" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D179" s="1"/>
       <c r="H179" s="1"/>
     </row>
-    <row r="180" spans="8:8" ht="15">
+    <row r="180" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H180" s="1"/>
     </row>
-    <row r="181" spans="8:8" ht="15">
+    <row r="181" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H181" s="1"/>
     </row>
-    <row r="182" spans="8:8" ht="15">
+    <row r="182" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H182" s="1"/>
     </row>
-    <row r="183" spans="8:8" ht="15">
+    <row r="183" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H183" s="1"/>
     </row>
-    <row r="184" spans="8:8" ht="15">
+    <row r="184" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H184" s="1"/>
     </row>
-    <row r="185" spans="8:8" ht="15">
+    <row r="185" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H185" s="1"/>
     </row>
-    <row r="186" spans="8:8" ht="15">
+    <row r="186" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H186" s="1"/>
     </row>
-    <row r="187" spans="8:8" ht="15">
+    <row r="187" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H187" s="1"/>
     </row>
-    <row r="188" spans="8:8" ht="15">
+    <row r="188" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H188" s="1"/>
     </row>
-    <row r="189" spans="8:8" ht="15">
+    <row r="189" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H189" s="1"/>
     </row>
-    <row r="190" spans="8:8" ht="15">
+    <row r="190" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H190" s="1"/>
     </row>
-    <row r="191" spans="8:8" ht="15">
+    <row r="191" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H191" s="1"/>
     </row>
-    <row r="192" spans="8:8" ht="15">
+    <row r="192" spans="4:8" x14ac:dyDescent="0.2">
       <c r="H192" s="1"/>
     </row>
-    <row r="193" spans="8:8" ht="15">
+    <row r="193" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H193" s="1"/>
     </row>
-    <row r="194" spans="8:8" ht="15">
+    <row r="194" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H194" s="1"/>
     </row>
-    <row r="195" spans="8:8" ht="15">
+    <row r="195" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H195" s="1"/>
     </row>
-    <row r="196" spans="8:8" ht="15">
+    <row r="196" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H196" s="1"/>
     </row>
-    <row r="197" spans="8:8" ht="15">
+    <row r="197" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H197" s="1"/>
     </row>
-    <row r="198" spans="8:8" ht="15">
+    <row r="198" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H198" s="1"/>
     </row>
-    <row r="199" spans="8:8" ht="15">
+    <row r="199" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H199" s="1"/>
+    </row>
+    <row r="200" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H200" s="1"/>
+    </row>
+    <row r="201" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H201" s="1"/>
+    </row>
+    <row r="202" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H202" s="1"/>
+    </row>
+    <row r="203" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H203" s="1"/>
+    </row>
+    <row r="204" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H204" s="1"/>
+    </row>
+    <row r="205" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H205" s="1"/>
+    </row>
+    <row r="206" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H206" s="1"/>
+    </row>
+    <row r="207" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H207" s="1"/>
+    </row>
+    <row r="208" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H208" s="1"/>
+    </row>
+    <row r="209" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H209" s="1"/>
+    </row>
+    <row r="210" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H210" s="1"/>
+    </row>
+    <row r="211" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H211" s="1"/>
+    </row>
+    <row r="212" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H212" s="1"/>
+    </row>
+    <row r="213" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H213" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="77" r:id="rId1"/>
+  <pageSetup scale="77" orientation="portrait" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="11" man="1"/>
   </colBreaks>

--- a/Contour_Portfolio_Delta_Adjusted.xlsx
+++ b/Contour_Portfolio_Delta_Adjusted.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harikumar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BEBF5D6-FB02-B540-BFE8-33A7CE52766F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55A8F7AB-654A-7D45-964B-2AD86AB12C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="227">
   <si>
     <t>Contour Portfolio (Delta Adjusted)</t>
   </si>
@@ -66,7 +66,7 @@
     <t>LION</t>
   </si>
   <si>
-    <t>SITM</t>
+    <t>NBIS</t>
   </si>
   <si>
     <t>PUBP</t>
@@ -81,7 +81,7 @@
     <t>DASH US 01/15/27 P150 OTC (DASH 1/15/27 P150 OTC)</t>
   </si>
   <si>
-    <t>SITIME ORD (NMS)</t>
+    <t>NEBIUS CL A ORD (NMS)</t>
   </si>
   <si>
     <t>Instrument</t>
@@ -102,27 +102,27 @@
     <t>ADSK</t>
   </si>
   <si>
+    <t>GEV</t>
+  </si>
+  <si>
     <t>7751</t>
   </si>
   <si>
-    <t>GEV</t>
+    <t>EFX</t>
+  </si>
+  <si>
+    <t>HQY</t>
   </si>
   <si>
     <t>AAPL</t>
   </si>
   <si>
-    <t>EFX</t>
-  </si>
-  <si>
-    <t>HQY</t>
+    <t>CSU</t>
   </si>
   <si>
     <t>FICO</t>
   </si>
   <si>
-    <t>CSU</t>
-  </si>
-  <si>
     <t>EXPE</t>
   </si>
   <si>
@@ -135,261 +135,249 @@
     <t>EXLS</t>
   </si>
   <si>
+    <t>NOW</t>
+  </si>
+  <si>
+    <t>VRSK</t>
+  </si>
+  <si>
+    <t>GRMN</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>8136</t>
+  </si>
+  <si>
+    <t>ARMK</t>
+  </si>
+  <si>
+    <t>TEAM</t>
+  </si>
+  <si>
+    <t>FNF</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
     <t>LAMR</t>
   </si>
   <si>
-    <t>NOW</t>
-  </si>
-  <si>
-    <t>VRSK</t>
-  </si>
-  <si>
-    <t>8136</t>
-  </si>
-  <si>
-    <t>GRMN</t>
-  </si>
-  <si>
-    <t>ARMK</t>
-  </si>
-  <si>
-    <t>6098</t>
-  </si>
-  <si>
-    <t>FNF</t>
-  </si>
-  <si>
-    <t>TEAM</t>
+    <t>REA</t>
+  </si>
+  <si>
+    <t>LRCX</t>
+  </si>
+  <si>
+    <t>BBY</t>
   </si>
   <si>
     <t>MANH</t>
   </si>
   <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>REA</t>
-  </si>
-  <si>
-    <t>BBY</t>
+    <t>NYT</t>
   </si>
   <si>
     <t>ADBE</t>
   </si>
   <si>
-    <t>IBM</t>
+    <t>FIX</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>IOT</t>
   </si>
   <si>
     <t>ANET</t>
   </si>
   <si>
-    <t>IOT</t>
+    <t>RHI</t>
   </si>
   <si>
     <t>DUOL</t>
   </si>
   <si>
+    <t>RNG</t>
+  </si>
+  <si>
+    <t>FAF</t>
+  </si>
+  <si>
     <t>STX</t>
   </si>
   <si>
-    <t>FAF</t>
-  </si>
-  <si>
-    <t>NYT</t>
+    <t>EBAY</t>
+  </si>
+  <si>
+    <t>CVSA</t>
+  </si>
+  <si>
+    <t>SYF</t>
   </si>
   <si>
     <t>COIN</t>
   </si>
   <si>
-    <t>EBAY</t>
-  </si>
-  <si>
-    <t>RNG</t>
-  </si>
-  <si>
-    <t>SYF</t>
-  </si>
-  <si>
-    <t>CVSA</t>
-  </si>
-  <si>
     <t>LOPE</t>
   </si>
   <si>
-    <t>RHI</t>
+    <t>TTAN</t>
+  </si>
+  <si>
+    <t>POWL</t>
+  </si>
+  <si>
+    <t>GM</t>
   </si>
   <si>
     <t>ALAB</t>
   </si>
   <si>
-    <t>TTAN</t>
-  </si>
-  <si>
-    <t>GM</t>
+    <t>SGI</t>
   </si>
   <si>
     <t>BFH</t>
   </si>
   <si>
-    <t>TT</t>
-  </si>
-  <si>
-    <t>POWL</t>
+    <t>HRB</t>
   </si>
   <si>
     <t>WDC</t>
   </si>
   <si>
+    <t>SOFI</t>
+  </si>
+  <si>
     <t>CIEN</t>
   </si>
   <si>
-    <t>SOFI</t>
+    <t>F</t>
+  </si>
+  <si>
+    <t>ESLT</t>
+  </si>
+  <si>
+    <t>FDS</t>
+  </si>
+  <si>
+    <t>CARG</t>
+  </si>
+  <si>
+    <t>SEZL</t>
+  </si>
+  <si>
+    <t>CHYM</t>
+  </si>
+  <si>
+    <t>DOCN</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>3034</t>
+  </si>
+  <si>
+    <t>CRWV</t>
+  </si>
+  <si>
+    <t>CNXC</t>
+  </si>
+  <si>
+    <t>TEPRF</t>
+  </si>
+  <si>
+    <t>DAVE</t>
   </si>
   <si>
     <t>QLYS</t>
   </si>
   <si>
-    <t>HRB</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>FIX</t>
-  </si>
-  <si>
-    <t>FDS</t>
-  </si>
-  <si>
-    <t>ESLT</t>
-  </si>
-  <si>
-    <t>CARG</t>
-  </si>
-  <si>
-    <t>SEZL</t>
-  </si>
-  <si>
-    <t>SGI</t>
-  </si>
-  <si>
-    <t>SYM</t>
-  </si>
-  <si>
-    <t>CHYM</t>
-  </si>
-  <si>
-    <t>DOCN</t>
-  </si>
-  <si>
-    <t>CRWV</t>
-  </si>
-  <si>
-    <t>3034</t>
-  </si>
-  <si>
-    <t>SLM</t>
-  </si>
-  <si>
-    <t>CNXC</t>
-  </si>
-  <si>
-    <t>DAVE</t>
-  </si>
-  <si>
-    <t>HUT</t>
-  </si>
-  <si>
-    <t>TEPRF</t>
-  </si>
-  <si>
-    <t>CHH</t>
-  </si>
-  <si>
-    <t>NBIS</t>
-  </si>
-  <si>
     <t>XYZ</t>
   </si>
   <si>
     <t>TRMB</t>
   </si>
   <si>
+    <t>W</t>
+  </si>
+  <si>
     <t>IRM</t>
   </si>
   <si>
-    <t>W</t>
-  </si>
-  <si>
     <t>ETN</t>
   </si>
   <si>
     <t>TSLA</t>
   </si>
   <si>
+    <t>SPOT</t>
+  </si>
+  <si>
     <t>GLBE</t>
   </si>
   <si>
+    <t>RACE</t>
+  </si>
+  <si>
     <t>GOOG</t>
   </si>
   <si>
-    <t>RACE</t>
-  </si>
-  <si>
     <t>LYFT</t>
   </si>
   <si>
+    <t>META</t>
+  </si>
+  <si>
     <t>AG1G</t>
   </si>
   <si>
-    <t>SPOT</t>
-  </si>
-  <si>
     <t>SHOP</t>
   </si>
   <si>
+    <t>TSM</t>
+  </si>
+  <si>
     <t>005930</t>
   </si>
   <si>
-    <t>TSM</t>
-  </si>
-  <si>
     <t>AMZN</t>
   </si>
   <si>
     <t>ZBRA</t>
   </si>
   <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>DOCS</t>
+  </si>
+  <si>
+    <t>NOD</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>ZETA</t>
+  </si>
+  <si>
+    <t>PCOR</t>
+  </si>
+  <si>
     <t>SAPG</t>
   </si>
   <si>
-    <t>PCOR</t>
-  </si>
-  <si>
-    <t>NOD</t>
-  </si>
-  <si>
-    <t>DOCS</t>
+    <t>DASH</t>
   </si>
   <si>
     <t>6857</t>
   </si>
   <si>
-    <t>CART</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>ZETA</t>
-  </si>
-  <si>
-    <t>DASH</t>
-  </si>
-  <si>
-    <t>UBER</t>
-  </si>
-  <si>
     <t>SPHR</t>
   </si>
   <si>
@@ -402,9 +390,6 @@
     <t>AMAT</t>
   </si>
   <si>
-    <t>TER</t>
-  </si>
-  <si>
     <t>HPE</t>
   </si>
   <si>
@@ -423,27 +408,27 @@
     <t>AUTODESK ORD (NMS)</t>
   </si>
   <si>
+    <t>GE VERNOVA ORD (NYS)</t>
+  </si>
+  <si>
     <t>CANON ORD (TYO) CFD</t>
   </si>
   <si>
-    <t>GE VERNOVA ORD (NYS)</t>
+    <t>EQUIFAX ORD (NYS)</t>
+  </si>
+  <si>
+    <t>HEALTHEQUITY ORD (NMS)</t>
   </si>
   <si>
     <t>APPLE ORD (NMS)</t>
   </si>
   <si>
-    <t>EQUIFAX ORD (NYS)</t>
-  </si>
-  <si>
-    <t>HEALTHEQUITY ORD (NMS)</t>
+    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
   </si>
   <si>
     <t>FAIR ISAAC ORD (NYS)</t>
   </si>
   <si>
-    <t>CONSTELLATION SOFTWARE ORD (TOR)</t>
-  </si>
-  <si>
     <t>EXPEDIA GROUP ORD (NMS)</t>
   </si>
   <si>
@@ -453,207 +438,195 @@
     <t>WILLIAMS SONOMA ORD (NYS)</t>
   </si>
   <si>
+    <t>SPOT US 01/21/28 C700 OTC (SPOT 1/21/28 C700 OTC)</t>
+  </si>
+  <si>
     <t>EXLSERVICE HOLDINGS ORD (NMS)</t>
   </si>
   <si>
+    <t>SERVICENOW ORD (NYS)</t>
+  </si>
+  <si>
+    <t>VERISK ANALYTICS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GARMIN ORD (NYS)</t>
+  </si>
+  <si>
+    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>SANRIO ORD (TYO) CFD</t>
+  </si>
+  <si>
+    <t>ARAMARK ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ATLASSIAN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
+    <t>GARTNER ORD (NYS)</t>
+  </si>
+  <si>
     <t>LAMAR ADVERTISING CL A REIT (NMS)</t>
   </si>
   <si>
-    <t>SERVICENOW ORD (NYS)</t>
-  </si>
-  <si>
-    <t>VERISK ANALYTICS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SANRIO ORD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>GARMIN ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ARAMARK ORD (NYS)</t>
-  </si>
-  <si>
-    <t>RECRUIT HOLDINGS CO LTD (TYO) CFD</t>
-  </si>
-  <si>
-    <t>FIDELITY NATIONAL FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ATLASSIAN CL A ORD (NMS)</t>
+    <t>REA GROUP ORD (ASX) CFD</t>
+  </si>
+  <si>
+    <t>LAM RESEARCH ORD (NMS)</t>
+  </si>
+  <si>
+    <t>BEST BUY ORD (NYS)</t>
   </si>
   <si>
     <t>MANHATTAN ASSOCIATES ORD (NMS)</t>
   </si>
   <si>
-    <t>GARTNER ORD (NYS)</t>
-  </si>
-  <si>
-    <t>REA GROUP ORD (ASX) CFD</t>
-  </si>
-  <si>
-    <t>SPOT US 01/21/28 C700 OTC (SPOT 1/21/28 C700 OTC)</t>
-  </si>
-  <si>
-    <t>BEST BUY ORD (NYS)</t>
+    <t>NEW YORK TIMES CL A ORD (NYS)</t>
   </si>
   <si>
     <t>ADOBE ORD (NMS)</t>
   </si>
   <si>
-    <t>INTERNATIONAL BUSINESS MACHINES ORD (NYS)</t>
+    <t>COMFORT SYSTEMS USA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>TRANE TECHNOLOGIES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SAMSARA CL A ORD (NYS)</t>
   </si>
   <si>
     <t>ARISTA NETWORKS ORD (NYS)</t>
   </si>
   <si>
-    <t>SAMSARA CL A ORD (NYS)</t>
+    <t>ROBERT HALF ORD (NYS)</t>
   </si>
   <si>
     <t>DUOLINGO CL A ORD (NMS)</t>
   </si>
   <si>
+    <t>RINGCENTRAL CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
+  </si>
+  <si>
     <t>SEAGATE TECHNOLOGY HOLDINGS ORD (NMS)</t>
   </si>
   <si>
-    <t>FIRST AMERICAN FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NEW YORK TIMES CL A ORD (NYS)</t>
+    <t>EBAY ORD (NMS)</t>
+  </si>
+  <si>
+    <t>COVISTA ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SYNCHRONY FINANCIAL ORD (NYS)</t>
   </si>
   <si>
     <t>COINBASE GLOBAL CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>EBAY ORD (NMS)</t>
-  </si>
-  <si>
-    <t>RINGCENTRAL CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SYNCHRONY FINANCIAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>COVISTA ORD (NYS)</t>
-  </si>
-  <si>
     <t>GRAND CANYON EDUCATION ORD (NMS)</t>
   </si>
   <si>
-    <t>ROBERT HALF ORD (NYS)</t>
+    <t>SERVICETITAN CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>POWELL INDUSTRIES ORD (NMS)</t>
+  </si>
+  <si>
+    <t>GENERAL MOTORS ORD (NYS)</t>
   </si>
   <si>
     <t>ASTERA LABS ORD (NMS)</t>
   </si>
   <si>
-    <t>SERVICETITAN CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>GENERAL MOTORS ORD (NYS)</t>
+    <t>SOMNIGROUP INTERNATIONAL ORD (NYS)</t>
   </si>
   <si>
     <t>BREAD FINANCIAL HOLDINGS ORD (NYS)</t>
   </si>
   <si>
-    <t>TRANE TECHNOLOGIES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>POWELL INDUSTRIES ORD (NMS)</t>
+    <t>H&amp;R BLOCK ORD (NYS)</t>
   </si>
   <si>
     <t>WESTERN DIGITAL ORD (NMS)</t>
   </si>
   <si>
+    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
+  </si>
+  <si>
     <t>CIENA ORD (NYS)</t>
   </si>
   <si>
-    <t>SOFI TECHNOLOGIES ORD (NMS)</t>
+    <t>FORD MOTOR ORD (NYS)</t>
+  </si>
+  <si>
+    <t>ELBIT SYSTEMS ORD (NMS)</t>
+  </si>
+  <si>
+    <t>FACTSET RESEARCH SYSTEMS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>CARGURUS CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>SEZZLE INC (NMS)</t>
+  </si>
+  <si>
+    <t>CHIME FINANCIAL CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
+  </si>
+  <si>
+    <t>SYMBOTIC CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
+    <t>COREWEAVE CL A ORD (NMS)</t>
+  </si>
+  <si>
+    <t>CONCENTRIX ORD (NMS)</t>
+  </si>
+  <si>
+    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
+  </si>
+  <si>
+    <t>DAVE CL A ORD (NMS)</t>
   </si>
   <si>
     <t>QUALYS ORD (NMS)</t>
   </si>
   <si>
-    <t>H&amp;R BLOCK ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FORD MOTOR ORD (NYS)</t>
-  </si>
-  <si>
-    <t>COMFORT SYSTEMS USA ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FACTSET RESEARCH SYSTEMS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>ELBIT SYSTEMS ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CARGURUS CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>SEZZLE INC (NMS)</t>
-  </si>
-  <si>
-    <t>SOMNIGROUP INTERNATIONAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>SYMBOTIC CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CHIME FINANCIAL CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DIGITALOCEAN HOLDINGS ORD (NYS)</t>
-  </si>
-  <si>
-    <t>COREWEAVE CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>NOVATEK MICROELE ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
-    <t>SLM ORD (NMS)</t>
-  </si>
-  <si>
-    <t>CONCENTRIX ORD (NMS)</t>
-  </si>
-  <si>
-    <t>DAVE CL A ORD (NMS)</t>
-  </si>
-  <si>
-    <t>HUT 8 ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TELEPERFORMANCE ORD (PAR) CFD</t>
-  </si>
-  <si>
-    <t>CHOICE HOTELS INTERNATIONAL ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NEBIUS CL A ORD (NMS)</t>
-  </si>
-  <si>
     <t>BLOCK CL A ORD (NYS)</t>
   </si>
   <si>
     <t>TRIMBLE ORD (NMS)</t>
   </si>
   <si>
+    <t>SPOTIFY TECHNOLOGY ORD (NYS)</t>
+  </si>
+  <si>
+    <t>WAYFAIR CL A ORD (NYS)</t>
+  </si>
+  <si>
     <t>IRON MOUNTAIN ORD (NYS)</t>
   </si>
   <si>
-    <t>WAYFAIR CL A ORD (NYS)</t>
-  </si>
-  <si>
     <t>EATON ORD (NYS)</t>
   </si>
   <si>
     <t>TESLA ORD (NMS)</t>
   </si>
   <si>
-    <t>SPOTIFY TECHNOLOGY ORD (NYS)</t>
-  </si>
-  <si>
     <t>GLOBAL E ONLINE ORD (NMS)</t>
   </si>
   <si>
@@ -663,73 +636,70 @@
     <t>LYFT CL A ORD (NMS)</t>
   </si>
   <si>
+    <t>META PLATFORMS CL A ORD (NMS)</t>
+  </si>
+  <si>
     <t>AUTO1 GROUP ORD (GER)</t>
   </si>
   <si>
     <t>SHOPIFY CL A SUB VTG ORD (NMS)</t>
   </si>
   <si>
+    <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
+  </si>
+  <si>
     <t>SAMSUNG ELECTR ORD (KSC) CFD_USD</t>
   </si>
   <si>
-    <t>TWN SEMICONT MAN ORD (TAI) CFD_USD</t>
-  </si>
-  <si>
     <t>AMAZON COM ORD (NMS)</t>
   </si>
   <si>
     <t>ZEBRA TECHNOLOGIES CL A ORD (NMS)</t>
   </si>
   <si>
+    <t>ZILLOW GROUP CL C ORD (NMS)</t>
+  </si>
+  <si>
+    <t>DOXIMITY CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
+  </si>
+  <si>
+    <t>TERADYNE ORD (NMS)</t>
+  </si>
+  <si>
+    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>PROCORE TECHNOLOGIES ORD (NYS)</t>
+  </si>
+  <si>
+    <t>FERRARI ORD (NYS)</t>
+  </si>
+  <si>
     <t>SAP ORD (GER)</t>
   </si>
   <si>
-    <t>PROCORE TECHNOLOGIES ORD (NYS)</t>
-  </si>
-  <si>
-    <t>NORDIC SEMICONDUCTOR ORD (OSL)</t>
-  </si>
-  <si>
-    <t>DOXIMITY CL A ORD (NYS)</t>
-  </si>
-  <si>
     <t>ADVANTEST ORD (TYO) CFD</t>
   </si>
   <si>
-    <t>MAPLEBEAR ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ZILLOW GROUP CL C ORD (NMS)</t>
-  </si>
-  <si>
-    <t>ZETA GLOBAL HOLDINGS CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>FERRARI ORD (NYS)</t>
-  </si>
-  <si>
     <t>FERRARI ORD (MIL)</t>
   </si>
   <si>
+    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
+  </si>
+  <si>
+    <t>REGAL REXNORD ORD (NYS)</t>
+  </si>
+  <si>
     <t>DOORDASH CL A ORD (NMS)</t>
   </si>
   <si>
-    <t>UBER TECHNOLOGIES INC. (NYS)</t>
-  </si>
-  <si>
-    <t>SPHERE ENTERTAINMENT CL A ORD (NYS)</t>
-  </si>
-  <si>
-    <t>REGAL REXNORD ORD (NYS)</t>
-  </si>
-  <si>
     <t>SUMITOMO ELEC ORD (TYO) 5802 JP CFD JPY EQSW 20360101</t>
   </si>
   <si>
     <t>APPLIED MATERIAL ORD (NMS)</t>
-  </si>
-  <si>
-    <t>TERADYNE ORD (NMS)</t>
   </si>
   <si>
     <t>HEWLETT PACKARD ENTERPRISE ORD (NYS)</t>
@@ -1260,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D6D00E-F3A7-4FD6-86F3-70A35F8FFA0A}">
-  <dimension ref="A1:Q212"/>
+  <dimension ref="A1:Q208"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
@@ -1371,24 +1341,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C11" s="10">
-        <v>10.75290592062041</v>
+        <v>10.427609093334581</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D47" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10752905920620411</v>
+        <f t="shared" ref="D11:D46" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10427609093334582</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>10</v>
       </c>
       <c r="G11" s="10">
-        <v>-5.9934308634348037</v>
+        <v>-5.973303024824042</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-5.9934308634348038E-2</v>
+        <v>-5.9733030248240421E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -1409,24 +1379,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C12" s="10">
-        <v>7.4692394833383151</v>
+        <v>7.6935835776592301</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>7.4692394833383149E-2</v>
+        <v>7.6935835776592298E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="10">
-        <v>-5.1837847861408672</v>
+        <v>-5.4122233600522378</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1837847861408673E-2</v>
+        <v>-5.4122233600522381E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -1437,791 +1407,781 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C13" s="10">
-        <v>5.5324314060717423</v>
+        <v>5.5622156661108972</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>5.5324314060717424E-2</v>
+        <v>5.5622156661108972E-2</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="10">
-        <v>-4.4904464480105091</v>
+        <v>-4.7009188450550372</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-4.4904464480105093E-2</v>
+        <v>-4.7009188450550375E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C14" s="10">
-        <v>5.4798915119943992</v>
+        <v>5.5479972315174511</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>5.4798915119943989E-2</v>
+        <v>5.5479972315174514E-2</v>
       </c>
       <c r="F14" s="11" t="s">
         <v>20</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.4006869587325159</v>
+        <v>-4.5613684035814783</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.4006869587325158E-2</v>
+        <v>-4.5613684035814783E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C15" s="10">
-        <v>4.4256917874129238</v>
+        <v>5.2774866730442138</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.4256917874129241E-2</v>
+        <v>5.2774866730442141E-2</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="10">
-        <v>-4.2768448521035598</v>
+        <v>-4.5040153508061271</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2768448521035597E-2</v>
+        <v>-4.5040153508061273E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C16" s="10">
-        <v>4.0114585996489325</v>
+        <v>4.9969701922286207</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.0114585996489323E-2</v>
+        <v>4.9969701922286204E-2</v>
       </c>
       <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="10">
-        <v>-4.2758220209296685</v>
+        <v>-4.4896258564182894</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2758220209296684E-2</v>
+        <v>-4.4896258564182896E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C17" s="10">
-        <v>3.9764142686120283</v>
+        <v>4.6139346967229438</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>3.9764142686120281E-2</v>
+        <v>4.613934696722944E-2</v>
       </c>
       <c r="F17" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.8146942577688012</v>
+        <v>-4.1448738898746678</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8146942577688012E-2</v>
+        <v>-4.144873889874668E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C18" s="10">
-        <v>3.9389470657314019</v>
+        <v>4.114267718792167</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>3.9389470657314019E-2</v>
+        <v>4.1142677187921667E-2</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.7592318427414506</v>
+        <v>-3.9166794302020596</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.7592318427414506E-2</v>
+        <v>-3.9166794302020594E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C19" s="10">
-        <v>3.7697534312823535</v>
+        <v>3.8033105616935128</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>3.7697534312823536E-2</v>
+        <v>3.8033105616935126E-2</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.6320376874597859</v>
+        <v>-3.8800047654481853</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.6320376874597861E-2</v>
+        <v>-3.8800047654481855E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C20" s="10">
-        <v>3.7290016734757856</v>
+        <v>3.7923227764295206</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.7290016734757854E-2</v>
+        <v>3.7923227764295207E-2</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.5311836688318596</v>
+        <v>-3.4643571575274645</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5311836688318596E-2</v>
+        <v>-3.4643571575274645E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C21" s="10">
-        <v>2.9431557514540136</v>
+        <v>3.1723219992012024</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>2.9431557514540137E-2</v>
+        <v>3.1723219992012025E-2</v>
       </c>
       <c r="F21" s="11" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="10">
-        <v>-3.2721487094228197</v>
+        <v>-3.1988082315684001</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2721487094228195E-2</v>
+        <v>-3.1988082315684001E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C22" s="10">
-        <v>2.8545808131970469</v>
+        <v>2.9580406341239374</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>2.8545808131970468E-2</v>
+        <v>2.9580406341239374E-2</v>
       </c>
       <c r="F22" s="11" t="s">
         <v>28</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.7413886334777815</v>
+        <v>-2.77266615364428</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7413886334777815E-2</v>
+        <v>-2.77266615364428E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C23" s="10">
-        <v>2.7819275358197402</v>
+        <v>2.9067463416621426</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>2.7819275358197403E-2</v>
+        <v>2.9067463416621427E-2</v>
       </c>
       <c r="F23" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.7170502309773621</v>
+        <v>-2.7529377893896254</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7170502309773623E-2</v>
+        <v>-2.7529377893896253E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C24" s="10">
-        <v>2.5907317747027272</v>
+        <v>2.7309970286623573</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>2.5907317747027273E-2</v>
+        <v>2.7309970286623571E-2</v>
       </c>
       <c r="F24" s="11" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.6765686262803565</v>
+        <v>-2.6869089863363786</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.6765686262803564E-2</v>
+        <v>-2.6869089863363785E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C25" s="10">
-        <v>2.5707776652134351</v>
+        <v>2.5648691691948944</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>2.5707776652134352E-2</v>
+        <v>2.5648691691948944E-2</v>
       </c>
       <c r="F25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.4387673018160689</v>
+        <v>-2.526461699951791</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.438767301816069E-2</v>
+        <v>-2.526461699951791E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C26" s="10">
-        <v>2.5144788409927368</v>
+        <v>2.514208405827949</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>2.5144788409927368E-2</v>
+        <v>2.5142084058279491E-2</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.4110763049710839</v>
+        <v>-2.5247037743081715</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.411076304971084E-2</v>
+        <v>-2.5247037743081714E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C27" s="10">
-        <v>2.3721711358365862</v>
+        <v>2.4286427699734028</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.3721711358365861E-2</v>
+        <v>2.4286427699734027E-2</v>
       </c>
       <c r="F27" s="11" t="s">
         <v>33</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.40224469153938</v>
+        <v>-2.4642596398202143</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4022446915393802E-2</v>
+        <v>-2.4642596398202144E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C28" s="10">
-        <v>2.2786355668412965</v>
+        <v>2.3710659168585337</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.2786355668412965E-2</v>
+        <v>2.3710659168585339E-2</v>
       </c>
       <c r="F28" s="11" t="s">
         <v>34</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.3746831600873963</v>
+        <v>-2.3986233374554371</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3746831600873965E-2</v>
+        <v>-2.3986233374554369E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C29" s="10">
-        <v>2.1812497213005262</v>
+        <v>2.132386289837457</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.1812497213005263E-2</v>
+        <v>2.1323862898374572E-2</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>35</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.3697468997632218</v>
+        <v>-2.3616472882443462</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3697468997632219E-2</v>
+        <v>-2.3616472882443462E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C30" s="10">
-        <v>2.1265592043345598</v>
+        <v>2.1073622890838983</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.1265592043345598E-2</v>
+        <v>2.1073622890838983E-2</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>36</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.34329223603106</v>
+        <v>-2.3210498372603086</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3432922360310599E-2</v>
+        <v>-2.3210498372603087E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C31" s="10">
-        <v>2.1027171598591958</v>
+        <v>2.0931168178411013</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.1027171598591958E-2</v>
+        <v>2.0931168178411012E-2</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>37</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.2876371235668143</v>
+        <v>-2.0469200976686563</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2876371235668144E-2</v>
+        <v>-2.0469200976686565E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C32" s="10">
-        <v>2.0498538751452804</v>
+        <v>2.0049387625386745</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.0498538751452803E-2</v>
+        <v>2.0049387625386744E-2</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>38</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.2863701634985345</v>
+        <v>-2.0244483923219616</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2863701634985346E-2</v>
+        <v>-2.0244483923219616E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C33" s="10">
-        <v>2.0311422378021988</v>
+        <v>2.0042031707250647</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.0311422378021988E-2</v>
+        <v>2.0042031707250649E-2</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G33" s="10">
-        <v>-2.0171062929217198</v>
+        <v>-2.0177644303680498</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-2.01710629292172E-2</v>
+        <v>-2.0177644303680499E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C34" s="10">
-        <v>2.0118308168971288</v>
+        <v>1.9732465525992879</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>2.011830816897129E-2</v>
+        <v>1.9732465525992879E-2</v>
       </c>
       <c r="F34" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G34" s="10">
-        <v>-2.0085239924570435</v>
+        <v>-1.9784020796763355</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0085239924570435E-2</v>
+        <v>-1.9784020796763356E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C35" s="10">
-        <v>1.9939764614609139</v>
+        <v>1.9679593000080795</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.993976461460914E-2</v>
+        <v>1.9679593000080795E-2</v>
       </c>
       <c r="F35" s="11" t="s">
         <v>41</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.8660124031809358</v>
+        <v>-1.8882387174049113</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.8660124031809357E-2</v>
+        <v>-1.8882387174049112E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C36" s="10">
-        <v>1.9810263751637747</v>
+        <v>1.9442153113479081</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.9810263751637747E-2</v>
+        <v>1.9442153113479081E-2</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>42</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.8481858780294125</v>
+        <v>-1.7990615339319025</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.8481858780294125E-2</v>
+        <v>-1.7990615339319026E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C37" s="10">
-        <v>1.7804097216213104</v>
+        <v>1.8891075484904203</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.7804097216213104E-2</v>
+        <v>1.8891075484904204E-2</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>43</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.740215150840926</v>
+        <v>-1.7964748183797983</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.740215150840926E-2</v>
+        <v>-1.7964748183797983E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C38" s="10">
-        <v>1.7584797301304107</v>
+        <v>1.7320716732346295</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.7584797301304106E-2</v>
+        <v>1.7320716732346295E-2</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>44</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.662796755748001</v>
+        <v>-1.7604967451943221</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6627967557480011E-2</v>
+        <v>-1.7604967451943222E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C39" s="10">
-        <v>1.7139454766481832</v>
+        <v>1.7131131127524628</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.7139454766481831E-2</v>
+        <v>1.7131131127524627E-2</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>45</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.5345054187769702</v>
+        <v>-1.7553441327263473</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5345054187769703E-2</v>
+        <v>-1.7553441327263473E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C40" s="10">
-        <v>1.7088300247605672</v>
+        <v>1.5563744582266428</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>1.7088300247605673E-2</v>
+        <v>1.5563744582266427E-2</v>
       </c>
       <c r="F40" s="11" t="s">
         <v>46</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.4991249415563426</v>
+        <v>-1.5900082141812351</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4991249415563426E-2</v>
+        <v>-1.5900082141812349E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C41" s="10">
-        <v>1.5899809986203635</v>
+        <v>1.5331280914256717</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>1.5899809986203634E-2</v>
+        <v>1.5331280914256718E-2</v>
       </c>
       <c r="F41" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.4710904316875686</v>
+        <v>-1.5829300166525011</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4710904316875686E-2</v>
+        <v>-1.582930016652501E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C42" s="10">
-        <v>1.4257662892427765</v>
+        <v>1.4588145814784628</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>1.4257662892427764E-2</v>
+        <v>1.4588145814784627E-2</v>
       </c>
       <c r="F42" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.3891977726386431</v>
+        <v>-1.5714085669877464</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.389197772638643E-2</v>
+        <v>-1.5714085669877465E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C43" s="10">
-        <v>1.4204945648496996</v>
+        <v>1.4551015777060856</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>1.4204945648496996E-2</v>
+        <v>1.4551015777060855E-2</v>
       </c>
       <c r="F43" s="11" t="s">
         <v>49</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.3581861044227097</v>
+        <v>-1.515696647306741</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.3581861044227097E-2</v>
+        <v>-1.5156966473067411E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C44" s="10">
-        <v>1.4013027868842094</v>
+        <v>1.1397703690977865</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>1.4013027868842095E-2</v>
+        <v>1.1397703690977866E-2</v>
       </c>
       <c r="F44" s="11" t="s">
         <v>50</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.2929764732396047</v>
+        <v>-1.4593968093384804</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2929764732396048E-2</v>
+        <v>-1.4593968093384804E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C45" s="10">
-        <v>1.0838954568849919</v>
+        <v>0.56972765686805427</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>1.0838954568849918E-2</v>
+        <v>5.697276568680543E-3</v>
       </c>
       <c r="F45" s="11" t="s">
         <v>51</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.2784004980554449</v>
+        <v>-1.4390590836012493</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2784004980554448E-2</v>
+        <v>-1.4390590836012494E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
       <c r="C46" s="10">
-        <v>0.54126152093270297</v>
+        <v>0.49915213305670336</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="0"/>
-        <v>5.4126152093270296E-3</v>
+        <v>4.9915213305670334E-3</v>
       </c>
       <c r="F46" s="11" t="s">
         <v>52</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.2741244566663887</v>
+        <v>-1.3952691641461448</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2741244566663888E-2</v>
+        <v>-1.3952691641461448E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B47" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="10">
-        <v>0.51245997294786305</v>
-      </c>
-      <c r="D47" s="10">
-        <f t="shared" si="0"/>
-        <v>5.1245997294786308E-3</v>
-      </c>
+      <c r="B47" s="9"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
       <c r="F47" s="11" t="s">
         <v>53</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.238086147912516</v>
+        <v>-1.3946404413318709</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="2"/>
-        <v>-1.238086147912516E-2</v>
+        <v>-1.394640441331871E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B48" s="9"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
       <c r="F48" s="11" t="s">
         <v>54</v>
       </c>
       <c r="G48" s="10">
-        <v>-1.232329098824392</v>
+        <v>-1.3296738050992951</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="2"/>
-        <v>-1.232329098824392E-2</v>
+        <v>-1.3296738050992952E-2</v>
       </c>
     </row>
     <row r="49" spans="4:8" x14ac:dyDescent="0.2">
@@ -2229,11 +2189,11 @@
         <v>55</v>
       </c>
       <c r="G49" s="10">
-        <v>-1.163752003193627</v>
+        <v>-1.2528405462132017</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-1.163752003193627E-2</v>
+        <v>-1.2528405462132018E-2</v>
       </c>
     </row>
     <row r="50" spans="4:8" x14ac:dyDescent="0.2">
@@ -2241,11 +2201,11 @@
         <v>56</v>
       </c>
       <c r="G50" s="10">
-        <v>-1.1222439521141796</v>
+        <v>-1.2159826774604667</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-1.1222439521141795E-2</v>
+        <v>-1.2159826774604667E-2</v>
       </c>
     </row>
     <row r="51" spans="4:8" x14ac:dyDescent="0.2">
@@ -2253,23 +2213,24 @@
         <v>57</v>
       </c>
       <c r="G51" s="10">
-        <v>-1.1188912213466502</v>
+        <v>-1.2100582487518343</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-1.1188912213466502E-2</v>
+        <v>-1.2100582487518344E-2</v>
       </c>
     </row>
     <row r="52" spans="4:8" x14ac:dyDescent="0.2">
+      <c r="D52" s="1"/>
       <c r="F52" s="11" t="s">
         <v>58</v>
       </c>
       <c r="G52" s="10">
-        <v>-1.0025669067929244</v>
+        <v>-1.179837500021484</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0025669067929243E-2</v>
+        <v>-1.179837500021484E-2</v>
       </c>
     </row>
     <row r="53" spans="4:8" x14ac:dyDescent="0.2">
@@ -2278,11 +2239,11 @@
         <v>59</v>
       </c>
       <c r="G53" s="10">
-        <v>-0.98530667336568545</v>
+        <v>-1.1528153265621626</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-9.8530667336568546E-3</v>
+        <v>-1.1528153265621626E-2</v>
       </c>
     </row>
     <row r="54" spans="4:8" x14ac:dyDescent="0.2">
@@ -2291,11 +2252,11 @@
         <v>60</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.94970027971638638</v>
+        <v>-1.1352402338532157</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4970027971638636E-3</v>
+        <v>-1.1352402338532156E-2</v>
       </c>
     </row>
     <row r="55" spans="4:8" x14ac:dyDescent="0.2">
@@ -2304,11 +2265,11 @@
         <v>61</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.94896359570984901</v>
+        <v>-1.0260339956228759</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4896359570984905E-3</v>
+        <v>-1.026033995622876E-2</v>
       </c>
     </row>
     <row r="56" spans="4:8" x14ac:dyDescent="0.2">
@@ -2317,11 +2278,11 @@
         <v>62</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.85141844786647047</v>
+        <v>-0.97481737466847596</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-8.5141844786647044E-3</v>
+        <v>-9.7481737466847598E-3</v>
       </c>
     </row>
     <row r="57" spans="4:8" x14ac:dyDescent="0.2">
@@ -2330,11 +2291,11 @@
         <v>63</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.81507946289955924</v>
+        <v>-0.88649243676744327</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-8.1507946289955929E-3</v>
+        <v>-8.8649243676744323E-3</v>
       </c>
     </row>
     <row r="58" spans="4:8" x14ac:dyDescent="0.2">
@@ -2343,11 +2304,11 @@
         <v>64</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.79425954506813967</v>
+        <v>-0.86847300496580326</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-7.9425954506813969E-3</v>
+        <v>-8.6847300496580328E-3</v>
       </c>
     </row>
     <row r="59" spans="4:8" x14ac:dyDescent="0.2">
@@ -2356,11 +2317,11 @@
         <v>65</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.77839123514436381</v>
+        <v>-0.86442308626370223</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-7.7839123514436385E-3</v>
+        <v>-8.6442308626370219E-3</v>
       </c>
     </row>
     <row r="60" spans="4:8" x14ac:dyDescent="0.2">
@@ -2369,11 +2330,11 @@
         <v>66</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.74874311445534492</v>
+        <v>-0.82620305414216078</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-7.4874311445534492E-3</v>
+        <v>-8.2620305414216073E-3</v>
       </c>
     </row>
     <row r="61" spans="4:8" x14ac:dyDescent="0.2">
@@ -2382,11 +2343,11 @@
         <v>67</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.72710233964849313</v>
+        <v>-0.77647961517393482</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-7.2710233964849314E-3</v>
+        <v>-7.7647961517393485E-3</v>
       </c>
     </row>
     <row r="62" spans="4:8" x14ac:dyDescent="0.2">
@@ -2395,11 +2356,11 @@
         <v>68</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.69924954516799831</v>
+        <v>-0.73647452378621547</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-6.992495451679983E-3</v>
+        <v>-7.3647452378621551E-3</v>
       </c>
     </row>
     <row r="63" spans="4:8" x14ac:dyDescent="0.2">
@@ -2408,11 +2369,11 @@
         <v>69</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.69769432337641968</v>
+        <v>-0.71670028913639117</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9769432337641966E-3</v>
+        <v>-7.1670028913639119E-3</v>
       </c>
     </row>
     <row r="64" spans="4:8" x14ac:dyDescent="0.2">
@@ -2421,11 +2382,11 @@
         <v>70</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.69166169990066484</v>
+        <v>-0.69037928734543907</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9166169990066487E-3</v>
+        <v>-6.903792873454391E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
@@ -2434,11 +2395,11 @@
         <v>71</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.6899591413077788</v>
+        <v>-0.68770443956660965</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-6.8995914130777882E-3</v>
+        <v>-6.8770443956660968E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
@@ -2447,11 +2408,11 @@
         <v>72</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.60217103207357514</v>
+        <v>-0.68305945484547959</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-6.0217103207357518E-3</v>
+        <v>-6.8305945484547961E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
@@ -2460,11 +2421,11 @@
         <v>73</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.58918145132830757</v>
+        <v>-0.62084920605031768</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-5.8918145132830753E-3</v>
+        <v>-6.2084920605031766E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
@@ -2473,11 +2434,11 @@
         <v>74</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.58261336771817163</v>
+        <v>-0.60592848946123645</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-5.8261336771817159E-3</v>
+        <v>-6.0592848946123649E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
@@ -2486,11 +2447,11 @@
         <v>75</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.57868438634997299</v>
+        <v>-0.58835131488866599</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-5.7868438634997299E-3</v>
+        <v>-5.8835131488866599E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
@@ -2499,11 +2460,11 @@
         <v>76</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.55286020134673897</v>
+        <v>-0.52620352200220677</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-5.52860201346739E-3</v>
+        <v>-5.2620352200220674E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
@@ -2512,11 +2473,11 @@
         <v>77</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.54892235248586918</v>
+        <v>-0.51512245588926087</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-5.4892235248586918E-3</v>
+        <v>-5.1512245588926087E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
@@ -2525,11 +2486,11 @@
         <v>78</v>
       </c>
       <c r="G72" s="10">
-        <v>-0.54509807574267388</v>
+        <v>-0.50420585700256559</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="2"/>
-        <v>-5.4509807574267388E-3</v>
+        <v>-5.0420585700256563E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
@@ -2538,11 +2499,11 @@
         <v>79</v>
       </c>
       <c r="G73" s="10">
-        <v>-0.53861150485363163</v>
+        <v>-0.5036617966423107</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
-        <v>-5.3861150485363159E-3</v>
+        <v>-5.0366179664231066E-3</v>
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
@@ -2551,11 +2512,11 @@
         <v>80</v>
       </c>
       <c r="G74" s="10">
-        <v>-0.50531338775814905</v>
+        <v>-0.44731997442431104</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="2"/>
-        <v>-5.0531338775814906E-3</v>
+        <v>-4.4731997442431105E-3</v>
       </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
@@ -2564,11 +2525,11 @@
         <v>81</v>
       </c>
       <c r="G75" s="10">
-        <v>-0.48493588959954442</v>
+        <v>-0.44044253794432919</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
-        <v>-4.8493588959954443E-3</v>
+        <v>-4.4044253794432919E-3</v>
       </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
@@ -2577,11 +2538,11 @@
         <v>82</v>
       </c>
       <c r="G76" s="10">
-        <v>-0.44717142107998376</v>
+        <v>-0.41983486389059421</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="3"/>
-        <v>-4.4717142107998376E-3</v>
+        <v>-4.1983486389059422E-3</v>
       </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
@@ -2590,11 +2551,11 @@
         <v>83</v>
       </c>
       <c r="G77" s="10">
-        <v>-0.43447780995549073</v>
+        <v>-0.36020543203393712</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="3"/>
-        <v>-4.3447780995549074E-3</v>
+        <v>-3.6020543203393713E-3</v>
       </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
@@ -2603,11 +2564,11 @@
         <v>84</v>
       </c>
       <c r="G78" s="10">
-        <v>-0.38811276029405428</v>
+        <v>-0.32502367168442103</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="3"/>
-        <v>-3.8811276029405428E-3</v>
+        <v>-3.2502367168442104E-3</v>
       </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
@@ -2616,98 +2577,62 @@
         <v>85</v>
       </c>
       <c r="G79" s="10">
-        <v>-0.3726406908697204</v>
+        <v>-0.28055145612446619</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="3"/>
-        <v>-3.7264069086972041E-3</v>
+        <v>-2.8055145612446621E-3</v>
       </c>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
       <c r="F80" s="11" t="s">
-        <v>86</v>
+        <v>9</v>
       </c>
       <c r="G80" s="10">
-        <v>-0.34666303003179116</v>
+        <v>-0.22336106629355884</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="3"/>
-        <v>-3.4666303003179117E-3</v>
+        <v>-2.2336106629355884E-3</v>
       </c>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
-      <c r="F81" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="G81" s="10">
-        <v>-0.34602859503690198</v>
-      </c>
-      <c r="H81" s="12">
-        <f t="shared" si="3"/>
-        <v>-3.4602859503690196E-3</v>
-      </c>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="13"/>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
-      <c r="F82" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G82" s="10">
-        <v>-0.26711125262511992</v>
-      </c>
-      <c r="H82" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.6711125262511991E-3</v>
-      </c>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
-      <c r="F83" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="G83" s="10">
-        <v>-0.24576392361420543</v>
-      </c>
-      <c r="H83" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.4576392361420544E-3</v>
-      </c>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
-      <c r="F84" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="G84" s="10">
-        <v>-0.20520428498169269</v>
-      </c>
-      <c r="H84" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.0520428498169269E-3</v>
+      <c r="G84" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="13"/>
     </row>
     <row r="86" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D86" s="1"/>
+      <c r="H86" s="1"/>
     </row>
     <row r="87" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D87" s="1"/>
+      <c r="H87" s="1"/>
     </row>
     <row r="88" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D88" s="1"/>
-      <c r="G88" t="s">
-        <v>5</v>
-      </c>
+      <c r="H88" s="1"/>
     </row>
     <row r="89" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D89" s="1"/>
+      <c r="H89" s="1"/>
     </row>
     <row r="90" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D90" s="1"/>
@@ -3054,7 +2979,6 @@
       <c r="H175" s="1"/>
     </row>
     <row r="176" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D176" s="1"/>
       <c r="H176" s="1"/>
     </row>
     <row r="177" spans="8:8" x14ac:dyDescent="0.2">
@@ -3152,18 +3076,6 @@
     </row>
     <row r="208" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H208" s="1"/>
-    </row>
-    <row r="209" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H209" s="1"/>
-    </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H210" s="1"/>
-    </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H211" s="1"/>
-    </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H212" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3173,7 +3085,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2F19BB-E553-43BB-81C1-D22E0CC77CE4}">
-  <dimension ref="A1:Q213"/>
+  <dimension ref="A1:Q209"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="28.5" customWidth="1"/>
@@ -3288,24 +3200,24 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C11" s="10">
-        <v>10.75290592062041</v>
+        <v>10.427609093334581</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" ref="D11:D50" si="0">IF(B11="","",(C11/100))</f>
-        <v>0.10752905920620411</v>
+        <f t="shared" ref="D11:D49" si="0">IF(B11="","",(C11/100))</f>
+        <v>0.10427609093334582</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>16</v>
       </c>
       <c r="G11" s="10">
-        <v>-5.9934308634348037</v>
+        <v>-5.973303024824042</v>
       </c>
       <c r="H11" s="12">
         <f t="shared" ref="H11:H42" si="1">IF(F11="","",G11/100)</f>
-        <v>-5.9934308634348038E-2</v>
+        <v>-5.9733030248240421E-2</v>
       </c>
       <c r="K11" s="20" t="s">
         <v>11</v>
@@ -3326,24 +3238,24 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B12" s="9" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C12" s="10">
-        <v>7.4692394833383151</v>
+        <v>7.6935835776592301</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="0"/>
-        <v>7.4692394833383149E-2</v>
+        <v>7.6935835776592298E-2</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>17</v>
       </c>
       <c r="G12" s="10">
-        <v>-5.1837847861408672</v>
+        <v>-5.4122233600522378</v>
       </c>
       <c r="H12" s="12">
         <f t="shared" si="1"/>
-        <v>-5.1837847861408673E-2</v>
+        <v>-5.4122233600522381E-2</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="11"/>
@@ -3354,1317 +3266,1272 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B13" s="9" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C13" s="10">
-        <v>5.5324314060717423</v>
+        <v>6.6926821866756008</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="0"/>
-        <v>5.5324314060717424E-2</v>
+        <v>6.6926821866756012E-2</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G13" s="10">
-        <v>-4.4904464480105091</v>
+        <v>-4.7009188450550372</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="1"/>
-        <v>-4.4904464480105093E-2</v>
+        <v>-4.7009188450550375E-2</v>
       </c>
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B14" s="9" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C14" s="10">
-        <v>5.4798915119943992</v>
+        <v>5.5622156661108972</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="0"/>
-        <v>5.4798915119943989E-2</v>
+        <v>5.5622156661108972E-2</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G14" s="10">
-        <v>-4.4006869587325159</v>
+        <v>-4.5613684035814783</v>
       </c>
       <c r="H14" s="12">
         <f t="shared" si="1"/>
-        <v>-4.4006869587325158E-2</v>
+        <v>-4.5613684035814783E-2</v>
       </c>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B15" s="9" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C15" s="10">
-        <v>4.4256917874129238</v>
+        <v>5.5479972315174511</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="0"/>
-        <v>4.4256917874129241E-2</v>
+        <v>5.5479972315174514E-2</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G15" s="10">
-        <v>-4.2768448521035598</v>
+        <v>-4.5040153508061271</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2768448521035597E-2</v>
+        <v>-4.5040153508061273E-2</v>
       </c>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B16" s="9" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C16" s="10">
-        <v>4.0114585996489325</v>
+        <v>5.2774866730442138</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="0"/>
-        <v>4.0114585996489323E-2</v>
+        <v>5.2774866730442141E-2</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G16" s="10">
-        <v>-4.2758220209296685</v>
+        <v>-4.4896258564182894</v>
       </c>
       <c r="H16" s="12">
         <f t="shared" si="1"/>
-        <v>-4.2758220209296684E-2</v>
+        <v>-4.4896258564182896E-2</v>
       </c>
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" s="9" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C17" s="10">
-        <v>4.0026823739406829</v>
+        <v>4.9969701922286207</v>
       </c>
       <c r="D17" s="10">
         <f t="shared" si="0"/>
-        <v>4.002682373940683E-2</v>
+        <v>4.9969701922286204E-2</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G17" s="10">
-        <v>-3.8146942577688012</v>
+        <v>-4.1448738898746678</v>
       </c>
       <c r="H17" s="12">
         <f t="shared" si="1"/>
-        <v>-3.8146942577688012E-2</v>
+        <v>-4.144873889874668E-2</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="9" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C18" s="10">
-        <v>3.9764142686120283</v>
+        <v>4.114267718792167</v>
       </c>
       <c r="D18" s="10">
         <f t="shared" si="0"/>
-        <v>3.9764142686120281E-2</v>
+        <v>4.1142677187921667E-2</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G18" s="10">
-        <v>-3.7592318427414506</v>
+        <v>-3.9166794302020596</v>
       </c>
       <c r="H18" s="12">
         <f t="shared" si="1"/>
-        <v>-3.7592318427414506E-2</v>
+        <v>-3.9166794302020594E-2</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="9" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C19" s="10">
-        <v>3.9389470657314019</v>
+        <v>3.7923227764295206</v>
       </c>
       <c r="D19" s="10">
         <f t="shared" si="0"/>
-        <v>3.9389470657314019E-2</v>
+        <v>3.7923227764295207E-2</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G19" s="10">
-        <v>-3.6320376874597859</v>
+        <v>-3.8800047654481853</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="1"/>
-        <v>-3.6320376874597861E-2</v>
+        <v>-3.8800047654481855E-2</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="9" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C20" s="10">
-        <v>3.7290016734757856</v>
+        <v>3.1723219992012024</v>
       </c>
       <c r="D20" s="10">
         <f t="shared" si="0"/>
-        <v>3.7290016734757854E-2</v>
+        <v>3.1723219992012025E-2</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G20" s="10">
-        <v>-3.5311836688318596</v>
+        <v>-3.4643571575274645</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="1"/>
-        <v>-3.5311836688318596E-2</v>
+        <v>-3.4643571575274645E-2</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="9" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C21" s="10">
-        <v>2.9431557514540136</v>
+        <v>2.9580406341239374</v>
       </c>
       <c r="D21" s="10">
         <f t="shared" si="0"/>
-        <v>2.9431557514540137E-2</v>
+        <v>2.9580406341239374E-2</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G21" s="10">
-        <v>-3.2721487094228197</v>
+        <v>-3.1988082315684001</v>
       </c>
       <c r="H21" s="12">
         <f t="shared" si="1"/>
-        <v>-3.2721487094228195E-2</v>
+        <v>-3.1988082315684001E-2</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" s="9" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C22" s="10">
-        <v>2.7819275358197402</v>
+        <v>2.9067463416621426</v>
       </c>
       <c r="D22" s="10">
         <f t="shared" si="0"/>
-        <v>2.7819275358197403E-2</v>
+        <v>2.9067463416621427E-2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G22" s="10">
-        <v>-2.7413886334777815</v>
+        <v>-2.77266615364428</v>
       </c>
       <c r="H22" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7413886334777815E-2</v>
+        <v>-2.77266615364428E-2</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="9" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C23" s="10">
-        <v>2.5907317747027272</v>
+        <v>2.7309970286623573</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="0"/>
-        <v>2.5907317747027273E-2</v>
+        <v>2.7309970286623571E-2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G23" s="10">
-        <v>-2.7170502309773621</v>
+        <v>-2.7529377893896254</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="1"/>
-        <v>-2.7170502309773623E-2</v>
+        <v>-2.7529377893896253E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" s="9" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C24" s="10">
-        <v>2.5707776652134351</v>
+        <v>2.5648691691948944</v>
       </c>
       <c r="D24" s="10">
         <f t="shared" si="0"/>
-        <v>2.5707776652134352E-2</v>
+        <v>2.5648691691948944E-2</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G24" s="10">
-        <v>-2.6765686262803565</v>
+        <v>-2.6869089863363786</v>
       </c>
       <c r="H24" s="12">
         <f t="shared" si="1"/>
-        <v>-2.6765686262803564E-2</v>
+        <v>-2.6869089863363785E-2</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" s="9" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C25" s="10">
-        <v>2.5144788409927368</v>
+        <v>2.514208405827949</v>
       </c>
       <c r="D25" s="10">
         <f t="shared" si="0"/>
-        <v>2.5144788409927368E-2</v>
+        <v>2.5142084058279491E-2</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G25" s="10">
-        <v>-2.4387673018160689</v>
+        <v>-2.6329349370127533</v>
       </c>
       <c r="H25" s="12">
         <f t="shared" si="1"/>
-        <v>-2.438767301816069E-2</v>
+        <v>-2.6329349370127531E-2</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" s="9" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C26" s="10">
-        <v>2.3721711358365862</v>
+        <v>2.4286427699734028</v>
       </c>
       <c r="D26" s="10">
         <f t="shared" si="0"/>
-        <v>2.3721711358365861E-2</v>
+        <v>2.4286427699734027E-2</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G26" s="10">
-        <v>-2.4110763049710839</v>
+        <v>-2.526461699951791</v>
       </c>
       <c r="H26" s="12">
         <f t="shared" si="1"/>
-        <v>-2.411076304971084E-2</v>
+        <v>-2.526461699951791E-2</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" s="9" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C27" s="10">
-        <v>2.2786355668412965</v>
+        <v>2.3710659168585337</v>
       </c>
       <c r="D27" s="10">
         <f t="shared" si="0"/>
-        <v>2.2786355668412965E-2</v>
+        <v>2.3710659168585339E-2</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G27" s="10">
-        <v>-2.40224469153938</v>
+        <v>-2.5247037743081715</v>
       </c>
       <c r="H27" s="12">
         <f t="shared" si="1"/>
-        <v>-2.4022446915393802E-2</v>
+        <v>-2.5247037743081714E-2</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" s="9" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C28" s="10">
-        <v>2.1812497213005262</v>
+        <v>2.132386289837457</v>
       </c>
       <c r="D28" s="10">
         <f t="shared" si="0"/>
-        <v>2.1812497213005263E-2</v>
+        <v>2.1323862898374572E-2</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G28" s="10">
-        <v>-2.3746831600873963</v>
+        <v>-2.4642596398202143</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3746831600873965E-2</v>
+        <v>-2.4642596398202144E-2</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" s="9" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C29" s="10">
-        <v>2.1265592043345598</v>
+        <v>2.1073622890838983</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="0"/>
-        <v>2.1265592043345598E-2</v>
+        <v>2.1073622890838983E-2</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G29" s="10">
-        <v>-2.3697468997632218</v>
+        <v>-2.3986233374554371</v>
       </c>
       <c r="H29" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3697468997632219E-2</v>
+        <v>-2.3986233374554369E-2</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" s="9" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C30" s="10">
-        <v>2.1027171598591958</v>
+        <v>2.0931168178411013</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="0"/>
-        <v>2.1027171598591958E-2</v>
+        <v>2.0931168178411012E-2</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G30" s="10">
-        <v>-2.34329223603106</v>
+        <v>-2.3616472882443462</v>
       </c>
       <c r="H30" s="12">
         <f t="shared" si="1"/>
-        <v>-2.3432922360310599E-2</v>
+        <v>-2.3616472882443462E-2</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" s="9" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C31" s="10">
-        <v>2.0498538751452804</v>
+        <v>2.0049387625386745</v>
       </c>
       <c r="D31" s="10">
         <f t="shared" si="0"/>
-        <v>2.0498538751452803E-2</v>
+        <v>2.0049387625386744E-2</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G31" s="10">
-        <v>-2.2876371235668143</v>
+        <v>-2.3210498372603086</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2876371235668144E-2</v>
+        <v>-2.3210498372603087E-2</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" s="9" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C32" s="10">
-        <v>2.0311422378021988</v>
+        <v>2.0042031707250647</v>
       </c>
       <c r="D32" s="10">
         <f t="shared" si="0"/>
-        <v>2.0311422378021988E-2</v>
+        <v>2.0042031707250649E-2</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G32" s="10">
-        <v>-2.2863701634985345</v>
+        <v>-2.0469200976686563</v>
       </c>
       <c r="H32" s="12">
         <f t="shared" si="1"/>
-        <v>-2.2863701634985346E-2</v>
+        <v>-2.0469200976686565E-2</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="9" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="C33" s="10">
-        <v>2.0118308168971288</v>
+        <v>1.9732465525992879</v>
       </c>
       <c r="D33" s="10">
         <f t="shared" si="0"/>
-        <v>2.011830816897129E-2</v>
+        <v>1.9732465525992879E-2</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G33" s="10">
-        <v>-2.0171062929217198</v>
+        <v>-2.0244483923219616</v>
       </c>
       <c r="H33" s="12">
         <f t="shared" si="1"/>
-        <v>-2.01710629292172E-2</v>
+        <v>-2.0244483923219616E-2</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C34" s="10">
-        <v>1.9939764614609139</v>
+        <v>1.9687676311998532</v>
       </c>
       <c r="D34" s="10">
         <f t="shared" si="0"/>
-        <v>1.993976461460914E-2</v>
+        <v>1.9687676311998532E-2</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G34" s="10">
-        <v>-2.0085239924570435</v>
+        <v>-2.0177644303680498</v>
       </c>
       <c r="H34" s="12">
         <f t="shared" si="1"/>
-        <v>-2.0085239924570435E-2</v>
+        <v>-2.0177644303680499E-2</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="9" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C35" s="10">
-        <v>1.9563549642078071</v>
+        <v>1.9679593000080795</v>
       </c>
       <c r="D35" s="10">
         <f t="shared" si="0"/>
-        <v>1.9563549642078071E-2</v>
+        <v>1.9679593000080795E-2</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G35" s="10">
-        <v>-1.8660124031809358</v>
+        <v>-1.9784020796763355</v>
       </c>
       <c r="H35" s="12">
         <f t="shared" si="1"/>
-        <v>-1.8660124031809357E-2</v>
+        <v>-1.9784020796763356E-2</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="9" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="C36" s="10">
-        <v>1.8133984670745464</v>
+        <v>1.8891075484904203</v>
       </c>
       <c r="D36" s="10">
         <f t="shared" si="0"/>
-        <v>1.8133984670745465E-2</v>
+        <v>1.8891075484904204E-2</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G36" s="10">
-        <v>-1.8481858780294125</v>
+        <v>-1.8882387174049113</v>
       </c>
       <c r="H36" s="12">
         <f t="shared" si="1"/>
-        <v>-1.8481858780294125E-2</v>
+        <v>-1.8882387174049112E-2</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="9" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C37" s="10">
-        <v>1.7991699255396374</v>
+        <v>1.8345429304936589</v>
       </c>
       <c r="D37" s="10">
         <f t="shared" si="0"/>
-        <v>1.7991699255396374E-2</v>
+        <v>1.834542930493659E-2</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G37" s="10">
-        <v>-1.740215150840926</v>
+        <v>-1.7990615339319025</v>
       </c>
       <c r="H37" s="12">
         <f t="shared" si="1"/>
-        <v>-1.740215150840926E-2</v>
+        <v>-1.7990615339319026E-2</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="9" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C38" s="10">
-        <v>1.7804097216213104</v>
+        <v>1.7320716732346295</v>
       </c>
       <c r="D38" s="10">
         <f t="shared" si="0"/>
-        <v>1.7804097216213104E-2</v>
+        <v>1.7320716732346295E-2</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G38" s="10">
-        <v>-1.6715201857691149</v>
+        <v>-1.7964748183797983</v>
       </c>
       <c r="H38" s="12">
         <f t="shared" si="1"/>
-        <v>-1.671520185769115E-2</v>
+        <v>-1.7964748183797983E-2</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="C39" s="10">
-        <v>1.7584797301304107</v>
+        <v>1.7131131127524628</v>
       </c>
       <c r="D39" s="10">
         <f t="shared" si="0"/>
-        <v>1.7584797301304106E-2</v>
+        <v>1.7131131127524627E-2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G39" s="10">
-        <v>-1.662796755748001</v>
+        <v>-1.7604967451943221</v>
       </c>
       <c r="H39" s="12">
         <f t="shared" si="1"/>
-        <v>-1.6627967557480011E-2</v>
+        <v>-1.7604967451943222E-2</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="9" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="C40" s="10">
-        <v>1.7139454766481832</v>
+        <v>1.6715227516109599</v>
       </c>
       <c r="D40" s="10">
         <f t="shared" si="0"/>
-        <v>1.7139454766481831E-2</v>
+        <v>1.6715227516109599E-2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G40" s="10">
-        <v>-1.5345054187769702</v>
+        <v>-1.7553441327263473</v>
       </c>
       <c r="H40" s="12">
         <f t="shared" si="1"/>
-        <v>-1.5345054187769703E-2</v>
+        <v>-1.7553441327263473E-2</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="9" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C41" s="10">
-        <v>1.7088300247605672</v>
+        <v>1.5563744582266428</v>
       </c>
       <c r="D41" s="10">
         <f t="shared" si="0"/>
-        <v>1.7088300247605673E-2</v>
+        <v>1.5563744582266427E-2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G41" s="10">
-        <v>-1.4991249415563426</v>
+        <v>-1.5900082141812351</v>
       </c>
       <c r="H41" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4991249415563426E-2</v>
+        <v>-1.5900082141812349E-2</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="9" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C42" s="10">
-        <v>1.5899809986203635</v>
+        <v>1.5331280914256717</v>
       </c>
       <c r="D42" s="10">
         <f t="shared" si="0"/>
-        <v>1.5899809986203634E-2</v>
+        <v>1.5331280914256718E-2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G42" s="10">
-        <v>-1.4710904316875686</v>
+        <v>-1.5829300166525011</v>
       </c>
       <c r="H42" s="12">
         <f t="shared" si="1"/>
-        <v>-1.4710904316875686E-2</v>
+        <v>-1.582930016652501E-2</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="9" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C43" s="10">
-        <v>1.4257662892427765</v>
+        <v>1.4588145814784628</v>
       </c>
       <c r="D43" s="10">
         <f t="shared" si="0"/>
-        <v>1.4257662892427764E-2</v>
+        <v>1.4588145814784627E-2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G43" s="10">
-        <v>-1.3891977726386431</v>
+        <v>-1.5714085669877464</v>
       </c>
       <c r="H43" s="12">
         <f t="shared" ref="H43:H74" si="2">IF(F43="","",G43/100)</f>
-        <v>-1.389197772638643E-2</v>
+        <v>-1.5714085669877465E-2</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="9" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C44" s="10">
-        <v>1.4204945648496996</v>
+        <v>1.4551015777060856</v>
       </c>
       <c r="D44" s="10">
         <f t="shared" si="0"/>
-        <v>1.4204945648496996E-2</v>
+        <v>1.4551015777060855E-2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G44" s="10">
-        <v>-1.3581861044227097</v>
+        <v>-1.515696647306741</v>
       </c>
       <c r="H44" s="12">
         <f t="shared" si="2"/>
-        <v>-1.3581861044227097E-2</v>
+        <v>-1.5156966473067411E-2</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="9" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="C45" s="10">
-        <v>1.4013027868842094</v>
+        <v>1.1397703690977865</v>
       </c>
       <c r="D45" s="10">
         <f t="shared" si="0"/>
-        <v>1.4013027868842095E-2</v>
+        <v>1.1397703690977866E-2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G45" s="10">
-        <v>-1.2929764732396047</v>
+        <v>-1.4593968093384804</v>
       </c>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2929764732396048E-2</v>
+        <v>-1.4593968093384804E-2</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="9" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C46" s="10">
-        <v>1.0838954568849919</v>
+        <v>0.56972765686805427</v>
       </c>
       <c r="D46" s="10">
         <f t="shared" si="0"/>
-        <v>1.0838954568849918E-2</v>
+        <v>5.697276568680543E-3</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G46" s="10">
-        <v>-1.2784004980554449</v>
+        <v>-1.4390590836012493</v>
       </c>
       <c r="H46" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2784004980554448E-2</v>
+        <v>-1.4390590836012494E-2</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="9" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C47" s="10">
-        <v>0.54126152093270297</v>
+        <v>0.55418744706009604</v>
       </c>
       <c r="D47" s="10">
         <f t="shared" si="0"/>
-        <v>5.4126152093270296E-3</v>
+        <v>5.5418744706009606E-3</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G47" s="10">
-        <v>-1.2741244566663887</v>
+        <v>-1.3952691641461448</v>
       </c>
       <c r="H47" s="12">
         <f t="shared" si="2"/>
-        <v>-1.2741244566663888E-2</v>
+        <v>-1.3952691641461448E-2</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="9" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C48" s="10">
-        <v>0.52341862502547887</v>
+        <v>0.49915213305670336</v>
       </c>
       <c r="D48" s="10">
         <f t="shared" si="0"/>
-        <v>5.2341862502547883E-3</v>
+        <v>4.9915213305670334E-3</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G48" s="10">
-        <v>-1.238086147912516</v>
+        <v>-1.3946404413318709</v>
       </c>
       <c r="H48" s="12">
         <f t="shared" si="2"/>
-        <v>-1.238086147912516E-2</v>
+        <v>-1.394640441331871E-2</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" s="9" t="s">
-        <v>236</v>
+        <v>13</v>
       </c>
       <c r="C49" s="10">
-        <v>0.51245997294786305</v>
+        <v>0.27269255973694811</v>
       </c>
       <c r="D49" s="10">
         <f t="shared" si="0"/>
-        <v>5.1245997294786308E-3</v>
+        <v>2.726925597369481E-3</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G49" s="10">
-        <v>-1.232329098824392</v>
+        <v>-1.3296738050992951</v>
       </c>
       <c r="H49" s="12">
         <f t="shared" si="2"/>
-        <v>-1.232329098824392E-2</v>
+        <v>-1.3296738050992952E-2</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B50" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="10">
-        <v>0.18185644962413716</v>
-      </c>
-      <c r="D50" s="10">
-        <f t="shared" si="0"/>
-        <v>1.8185644962413717E-3</v>
-      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
       <c r="F50" s="11" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G50" s="10">
-        <v>-1.163752003193627</v>
+        <v>-1.2528405462132017</v>
       </c>
       <c r="H50" s="12">
         <f t="shared" si="2"/>
-        <v>-1.163752003193627E-2</v>
+        <v>-1.2528405462132018E-2</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B51" s="9"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
       <c r="F51" s="11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G51" s="10">
-        <v>-1.1222439521141796</v>
+        <v>-1.2159826774604667</v>
       </c>
       <c r="H51" s="12">
         <f t="shared" si="2"/>
-        <v>-1.1222439521141795E-2</v>
+        <v>-1.2159826774604667E-2</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F52" s="11" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G52" s="10">
-        <v>-1.1188912213466502</v>
+        <v>-1.2100582487518343</v>
       </c>
       <c r="H52" s="12">
         <f t="shared" si="2"/>
-        <v>-1.1188912213466502E-2</v>
+        <v>-1.2100582487518344E-2</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F53" s="11" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G53" s="10">
-        <v>-1.0025669067929244</v>
+        <v>-1.179837500021484</v>
       </c>
       <c r="H53" s="12">
         <f t="shared" si="2"/>
-        <v>-1.0025669067929243E-2</v>
+        <v>-1.179837500021484E-2</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="F54" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G54" s="10">
-        <v>-0.98530667336568545</v>
+        <v>-1.1528153265621626</v>
       </c>
       <c r="H54" s="12">
         <f t="shared" si="2"/>
-        <v>-9.8530667336568546E-3</v>
+        <v>-1.1528153265621626E-2</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="D55" s="1"/>
       <c r="F55" s="11" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G55" s="10">
-        <v>-0.94970027971638638</v>
+        <v>-1.1352402338532157</v>
       </c>
       <c r="H55" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4970027971638636E-3</v>
+        <v>-1.1352402338532156E-2</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D56" s="1"/>
       <c r="F56" s="11" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G56" s="10">
-        <v>-0.94896359570984901</v>
+        <v>-1.0260339956228759</v>
       </c>
       <c r="H56" s="12">
         <f t="shared" si="2"/>
-        <v>-9.4896359570984905E-3</v>
+        <v>-1.026033995622876E-2</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D57" s="1"/>
       <c r="F57" s="11" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G57" s="10">
-        <v>-0.85141844786647047</v>
+        <v>-0.97481737466847596</v>
       </c>
       <c r="H57" s="12">
         <f t="shared" si="2"/>
-        <v>-8.5141844786647044E-3</v>
+        <v>-9.7481737466847598E-3</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D58" s="1"/>
       <c r="F58" s="11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G58" s="10">
-        <v>-0.81507946289955924</v>
+        <v>-0.88649243676744327</v>
       </c>
       <c r="H58" s="12">
         <f t="shared" si="2"/>
-        <v>-8.1507946289955929E-3</v>
+        <v>-8.8649243676744323E-3</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D59" s="1"/>
       <c r="F59" s="11" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G59" s="10">
-        <v>-0.79425954506813967</v>
+        <v>-0.86847300496580326</v>
       </c>
       <c r="H59" s="12">
         <f t="shared" si="2"/>
-        <v>-7.9425954506813969E-3</v>
+        <v>-8.6847300496580328E-3</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D60" s="1"/>
       <c r="F60" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G60" s="10">
-        <v>-0.77839123514436381</v>
+        <v>-0.86442308626370223</v>
       </c>
       <c r="H60" s="12">
         <f t="shared" si="2"/>
-        <v>-7.7839123514436385E-3</v>
+        <v>-8.6442308626370219E-3</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D61" s="1"/>
       <c r="F61" s="11" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G61" s="10">
-        <v>-0.74874311445534492</v>
+        <v>-0.82620305414216078</v>
       </c>
       <c r="H61" s="12">
         <f t="shared" si="2"/>
-        <v>-7.4874311445534492E-3</v>
+        <v>-8.2620305414216073E-3</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D62" s="1"/>
       <c r="F62" s="11" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G62" s="10">
-        <v>-0.72710233964849313</v>
+        <v>-0.77647961517393482</v>
       </c>
       <c r="H62" s="12">
         <f t="shared" si="2"/>
-        <v>-7.2710233964849314E-3</v>
+        <v>-7.7647961517393485E-3</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D63" s="1"/>
       <c r="F63" s="11" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G63" s="10">
-        <v>-0.69924954516799831</v>
+        <v>-0.73647452378621547</v>
       </c>
       <c r="H63" s="12">
         <f t="shared" si="2"/>
-        <v>-6.992495451679983E-3</v>
+        <v>-7.3647452378621551E-3</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="D64" s="1"/>
       <c r="F64" s="11" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G64" s="10">
-        <v>-0.69769432337641968</v>
+        <v>-0.71670028913639117</v>
       </c>
       <c r="H64" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9769432337641966E-3</v>
+        <v>-7.1670028913639119E-3</v>
       </c>
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D65" s="1"/>
       <c r="F65" s="11" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G65" s="10">
-        <v>-0.69166169990066484</v>
+        <v>-0.69037928734543907</v>
       </c>
       <c r="H65" s="12">
         <f t="shared" si="2"/>
-        <v>-6.9166169990066487E-3</v>
+        <v>-6.903792873454391E-3</v>
       </c>
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D66" s="1"/>
       <c r="F66" s="11" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G66" s="10">
-        <v>-0.6899591413077788</v>
+        <v>-0.68770443956660965</v>
       </c>
       <c r="H66" s="12">
         <f t="shared" si="2"/>
-        <v>-6.8995914130777882E-3</v>
+        <v>-6.8770443956660968E-3</v>
       </c>
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D67" s="1"/>
       <c r="F67" s="11" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G67" s="10">
-        <v>-0.60217103207357514</v>
+        <v>-0.68305945484547959</v>
       </c>
       <c r="H67" s="12">
         <f t="shared" si="2"/>
-        <v>-6.0217103207357518E-3</v>
+        <v>-6.8305945484547961E-3</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D68" s="1"/>
       <c r="F68" s="11" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G68" s="10">
-        <v>-0.58918145132830757</v>
+        <v>-0.62084920605031768</v>
       </c>
       <c r="H68" s="12">
         <f t="shared" si="2"/>
-        <v>-5.8918145132830753E-3</v>
+        <v>-6.2084920605031766E-3</v>
       </c>
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D69" s="1"/>
       <c r="F69" s="11" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G69" s="10">
-        <v>-0.58261336771817163</v>
+        <v>-0.60592848946123645</v>
       </c>
       <c r="H69" s="12">
         <f t="shared" si="2"/>
-        <v>-5.8261336771817159E-3</v>
+        <v>-6.0592848946123649E-3</v>
       </c>
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D70" s="1"/>
       <c r="F70" s="11" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G70" s="10">
-        <v>-0.57868438634997299</v>
+        <v>-0.58835131488866599</v>
       </c>
       <c r="H70" s="12">
         <f t="shared" si="2"/>
-        <v>-5.7868438634997299E-3</v>
+        <v>-5.8835131488866599E-3</v>
       </c>
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D71" s="1"/>
       <c r="F71" s="11" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G71" s="10">
-        <v>-0.55286020134673897</v>
+        <v>-0.52620352200220677</v>
       </c>
       <c r="H71" s="12">
         <f t="shared" si="2"/>
-        <v>-5.52860201346739E-3</v>
+        <v>-5.2620352200220674E-3</v>
       </c>
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D72" s="1"/>
       <c r="F72" s="11" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G72" s="10">
-        <v>-0.54892235248586918</v>
+        <v>-0.51512245588926087</v>
       </c>
       <c r="H72" s="12">
         <f t="shared" si="2"/>
-        <v>-5.4892235248586918E-3</v>
+        <v>-5.1512245588926087E-3</v>
       </c>
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D73" s="1"/>
       <c r="F73" s="11" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G73" s="10">
-        <v>-0.54509807574267388</v>
+        <v>-0.50420585700256559</v>
       </c>
       <c r="H73" s="12">
         <f t="shared" si="2"/>
-        <v>-5.4509807574267388E-3</v>
+        <v>-5.0420585700256563E-3</v>
       </c>
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D74" s="1"/>
       <c r="F74" s="11" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G74" s="10">
-        <v>-0.53861150485363163</v>
+        <v>-0.5036617966423107</v>
       </c>
       <c r="H74" s="12">
         <f t="shared" si="2"/>
-        <v>-5.3861150485363159E-3</v>
+        <v>-5.0366179664231066E-3</v>
       </c>
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D75" s="1"/>
       <c r="F75" s="11" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G75" s="10">
-        <v>-0.50531338775814905</v>
+        <v>-0.44731997442431104</v>
       </c>
       <c r="H75" s="12">
         <f t="shared" ref="H75:H106" si="3">IF(F75="","",G75/100)</f>
-        <v>-5.0531338775814906E-3</v>
+        <v>-4.4731997442431105E-3</v>
       </c>
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D76" s="1"/>
       <c r="F76" s="11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="G76" s="10">
-        <v>-0.48493588959954442</v>
+        <v>-0.44044253794432919</v>
       </c>
       <c r="H76" s="12">
         <f t="shared" si="3"/>
-        <v>-4.8493588959954443E-3</v>
+        <v>-4.4044253794432919E-3</v>
       </c>
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D77" s="1"/>
       <c r="F77" s="11" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G77" s="10">
-        <v>-0.44717142107998376</v>
+        <v>-0.41983486389059421</v>
       </c>
       <c r="H77" s="12">
         <f t="shared" si="3"/>
-        <v>-4.4717142107998376E-3</v>
+        <v>-4.1983486389059422E-3</v>
       </c>
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D78" s="1"/>
       <c r="F78" s="11" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G78" s="10">
-        <v>-0.43447780995549073</v>
+        <v>-0.36020543203393712</v>
       </c>
       <c r="H78" s="12">
         <f t="shared" si="3"/>
-        <v>-4.3447780995549074E-3</v>
+        <v>-3.6020543203393713E-3</v>
       </c>
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D79" s="1"/>
       <c r="F79" s="11" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G79" s="10">
-        <v>-0.38811276029405428</v>
+        <v>-0.32502367168442103</v>
       </c>
       <c r="H79" s="12">
         <f t="shared" si="3"/>
-        <v>-3.8811276029405428E-3</v>
+        <v>-3.2502367168442104E-3</v>
       </c>
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D80" s="1"/>
       <c r="F80" s="11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G80" s="10">
-        <v>-0.3726406908697204</v>
+        <v>-0.28055145612446619</v>
       </c>
       <c r="H80" s="12">
         <f t="shared" si="3"/>
-        <v>-3.7264069086972041E-3</v>
+        <v>-2.8055145612446621E-3</v>
       </c>
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D81" s="1"/>
       <c r="F81" s="11" t="s">
-        <v>194</v>
+        <v>14</v>
       </c>
       <c r="G81" s="10">
-        <v>-0.34666303003179116</v>
+        <v>-0.22336106629355884</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="3"/>
-        <v>-3.4666303003179117E-3</v>
+        <v>-2.2336106629355884E-3</v>
       </c>
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
-      <c r="F82" s="11" t="s">
-        <v>195</v>
-      </c>
-      <c r="G82" s="10">
-        <v>-0.34602859503690198</v>
-      </c>
-      <c r="H82" s="12">
-        <f t="shared" si="3"/>
-        <v>-3.4602859503690196E-3</v>
-      </c>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="13"/>
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
-      <c r="F83" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="G83" s="10">
-        <v>-0.26711125262511992</v>
-      </c>
-      <c r="H83" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.6711125262511991E-3</v>
-      </c>
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
-      <c r="F84" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="G84" s="10">
-        <v>-0.24576392361420543</v>
-      </c>
-      <c r="H84" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.4576392361420544E-3</v>
-      </c>
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
-      <c r="F85" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G85" s="10">
-        <v>-0.20520428498169269</v>
-      </c>
-      <c r="H85" s="12">
-        <f t="shared" si="3"/>
-        <v>-2.0520428498169269E-3</v>
+      <c r="G85" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D86" s="1"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="13"/>
     </row>
     <row r="87" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D87" s="1"/>
+      <c r="H87" s="1"/>
     </row>
     <row r="88" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D88" s="1"/>
+      <c r="H88" s="1"/>
     </row>
     <row r="89" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D89" s="1"/>
-      <c r="G89" t="s">
-        <v>5</v>
-      </c>
+      <c r="H89" s="1"/>
     </row>
     <row r="90" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D90" s="1"/>
+      <c r="H90" s="1"/>
     </row>
     <row r="91" spans="4:8" x14ac:dyDescent="0.2">
       <c r="D91" s="1"/>
@@ -5019,7 +4886,6 @@
       <c r="H178" s="1"/>
     </row>
     <row r="179" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D179" s="1"/>
       <c r="H179" s="1"/>
     </row>
     <row r="180" spans="4:8" x14ac:dyDescent="0.2">
@@ -5111,18 +4977,6 @@
     </row>
     <row r="209" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H209" s="1"/>
-    </row>
-    <row r="210" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H210" s="1"/>
-    </row>
-    <row r="211" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H211" s="1"/>
-    </row>
-    <row r="212" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H212" s="1"/>
-    </row>
-    <row r="213" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H213" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
